--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58DF678D-BEA7-47E0-97B4-73A3379B03D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C2C3176-B459-4A0F-8CC2-E3F347B90B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -781,18 +781,18 @@
     <t>solar resource -- CF class spv-BRA_22 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-BRA_22_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-BRA_22 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_spv-BRA_22_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-BRA_22 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-BRA_22_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-BRA_22 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_spv-BRA_22_c5</t>
   </si>
   <si>
@@ -919,18 +919,18 @@
     <t>solar resource -- CF class spv-BRA_18 -- cost class 5</t>
   </si>
   <si>
+    <t>e_spv-BRA_17_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-BRA_17 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-BRA_17_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-BRA_17 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-BRA_17_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-BRA_17 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-BRA_17_c2</t>
   </si>
   <si>
@@ -1474,18 +1474,18 @@
     <t>onshore wind resource -- CF class won-BRA_36 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-BRA_36_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_36 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-BRA_36_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_36 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-BRA_36_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_36 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-BRA_35_c1</t>
   </si>
   <si>
@@ -1882,18 +1882,18 @@
     <t>onshore wind resource -- CF class won-BRA_22 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-BRA_22_c3</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_22 -- cost class 3</t>
+  </si>
+  <si>
     <t>e_won-BRA_22_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_22 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-BRA_22_c3</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_22 -- cost class 3</t>
-  </si>
-  <si>
     <t>e_won-BRA_22_c4</t>
   </si>
   <si>
@@ -2008,18 +2008,18 @@
     <t>onshore wind resource -- CF class won-BRA_18 -- cost class 2</t>
   </si>
   <si>
+    <t>e_won-BRA_18_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_18 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-BRA_18_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_18 -- cost class 1</t>
   </si>
   <si>
-    <t>e_won-BRA_18_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_18 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-BRA_18_c5</t>
   </si>
   <si>
@@ -2068,18 +2068,18 @@
     <t>onshore wind resource -- CF class won-BRA_16 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-BRA_16_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_16 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-BRA_16_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_16 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-BRA_16_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_16 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-BRA_16_c4</t>
   </si>
   <si>
@@ -2302,18 +2302,18 @@
     <t>onshore wind resource -- CF class won-BRA_8 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-BRA_8_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_8 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-BRA_8_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_8 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-BRA_8_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_8 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-BRA_8_c1</t>
   </si>
   <si>
@@ -2398,18 +2398,18 @@
     <t>onshore wind resource -- CF class won-BRA_5 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-BRA_5_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_5 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-BRA_5_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_5 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-BRA_5_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_5 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_won-BRA_5_c1</t>
   </si>
   <si>
@@ -2422,16 +2422,16 @@
     <t>onshore wind resource -- CF class won-BRA_4 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-BRA_4_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-BRA_4 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-BRA_4_c1</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-BRA_4 -- cost class 1</t>
-  </si>
-  <si>
-    <t>e_won-BRA_4_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-BRA_4 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-BRA_4_c4</t>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F652E0-9A9F-4EC0-8E30-B33D4EFFD488}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BF348C-8707-4031-88A8-91860342D3A5}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8847,7 +8847,7 @@
         <v>297</v>
       </c>
       <c r="L11">
-        <v>0.18675</v>
+        <v>9.675414405893773E-2</v>
       </c>
       <c r="M11">
         <v>0.2509002810186321</v>
@@ -8923,10 +8923,10 @@
         <v>297</v>
       </c>
       <c r="L13">
-        <v>2.2499999999999999E-2</v>
+        <v>1.0929594088366603E-2</v>
       </c>
       <c r="M13">
-        <v>0.24553205567337938</v>
+        <v>0.24553205567337943</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -8961,10 +8961,10 @@
         <v>297</v>
       </c>
       <c r="L14">
-        <v>0.16500000000000001</v>
+        <v>6.7601525093101619E-2</v>
       </c>
       <c r="M14">
-        <v>0.24525855344641684</v>
+        <v>0.24525855344641681</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -8999,10 +8999,10 @@
         <v>297</v>
       </c>
       <c r="L15">
-        <v>3.5842499999999999</v>
+        <v>1.9266262187488834</v>
       </c>
       <c r="M15">
-        <v>0.23932310300741186</v>
+        <v>0.23923877152069231</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -9037,10 +9037,10 @@
         <v>297</v>
       </c>
       <c r="L16">
-        <v>9.5737500000000004</v>
+        <v>5.6627809777390459</v>
       </c>
       <c r="M16">
-        <v>0.23823641414454585</v>
+        <v>0.2380779857711402</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -9075,10 +9075,10 @@
         <v>297</v>
       </c>
       <c r="L17">
-        <v>17.611499999999999</v>
+        <v>10.718640937029134</v>
       </c>
       <c r="M17">
-        <v>0.23724470469068157</v>
+        <v>0.23724219240738095</v>
       </c>
       <c r="N17">
         <v>2</v>
@@ -9113,10 +9113,10 @@
         <v>297</v>
       </c>
       <c r="L18">
-        <v>6.9314999999999998</v>
+        <v>3.512932908909574</v>
       </c>
       <c r="M18">
-        <v>0.23662689378873783</v>
+        <v>0.23668558637934017</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -9151,10 +9151,10 @@
         <v>297</v>
       </c>
       <c r="L19">
-        <v>12.672000000000001</v>
+        <v>8.7820192502944678</v>
       </c>
       <c r="M19">
-        <v>0.2363988121960755</v>
+        <v>0.23635255349931711</v>
       </c>
       <c r="N19">
         <v>3</v>
@@ -9189,10 +9189,10 @@
         <v>297</v>
       </c>
       <c r="L20">
-        <v>40.362000000000002</v>
+        <v>22.681341870782674</v>
       </c>
       <c r="M20">
-        <v>0.23164874064696186</v>
+        <v>0.23119402616510437</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -9227,10 +9227,10 @@
         <v>297</v>
       </c>
       <c r="L21">
-        <v>41.046750000000003</v>
+        <v>21.507460017618097</v>
       </c>
       <c r="M21">
-        <v>0.23118364143958967</v>
+        <v>0.23116147704017584</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -9265,10 +9265,10 @@
         <v>297</v>
       </c>
       <c r="L22">
-        <v>42.548250000000003</v>
+        <v>25.625992291396159</v>
       </c>
       <c r="M22">
-        <v>0.2299970372294057</v>
+        <v>0.23002512652795667</v>
       </c>
       <c r="N22">
         <v>4</v>
@@ -9303,10 +9303,10 @@
         <v>297</v>
       </c>
       <c r="L23">
-        <v>46.728000000000002</v>
+        <v>27.546429654523866</v>
       </c>
       <c r="M23">
-        <v>0.2294326295414908</v>
+        <v>0.22954436869068409</v>
       </c>
       <c r="N23">
         <v>3</v>
@@ -9341,10 +9341,10 @@
         <v>297</v>
       </c>
       <c r="L24">
-        <v>26.201250000000002</v>
+        <v>15.147876916331697</v>
       </c>
       <c r="M24">
-        <v>0.22904575285965165</v>
+        <v>0.22928344504072032</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -9379,10 +9379,10 @@
         <v>297</v>
       </c>
       <c r="L25">
-        <v>45.667499999999997</v>
+        <v>34.05814277874812</v>
       </c>
       <c r="M25">
-        <v>0.22086600598438846</v>
+        <v>0.22087742016669751</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -9417,10 +9417,10 @@
         <v>297</v>
       </c>
       <c r="L26">
-        <v>62.344499999999996</v>
+        <v>39.014597357775621</v>
       </c>
       <c r="M26">
-        <v>0.22002568119830601</v>
+        <v>0.21989025074658686</v>
       </c>
       <c r="N26">
         <v>3</v>
@@ -9455,13 +9455,13 @@
         <v>297</v>
       </c>
       <c r="L27">
-        <v>70.865250000000003</v>
+        <v>44.254635948811874</v>
       </c>
       <c r="M27">
-        <v>0.21902872520060865</v>
+        <v>0.2189912646729488</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -9493,13 +9493,13 @@
         <v>297</v>
       </c>
       <c r="L28">
-        <v>62.658749999999998</v>
+        <v>46.293561461418811</v>
       </c>
       <c r="M28">
-        <v>0.21888890503209807</v>
+        <v>0.21861873283353284</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="2:14">
@@ -9531,10 +9531,10 @@
         <v>297</v>
       </c>
       <c r="L29">
-        <v>43.186500000000002</v>
+        <v>26.316005466845709</v>
       </c>
       <c r="M29">
-        <v>0.21873766280298224</v>
+        <v>0.21861396851812617</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -9569,10 +9569,10 @@
         <v>297</v>
       </c>
       <c r="L30">
-        <v>74.988</v>
+        <v>58.463998201497944</v>
       </c>
       <c r="M30">
-        <v>0.21161152777669778</v>
+        <v>0.21158695172219877</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -9607,10 +9607,10 @@
         <v>297</v>
       </c>
       <c r="L31">
-        <v>88.992750000000001</v>
+        <v>73.810938794504509</v>
       </c>
       <c r="M31">
-        <v>0.21041702416509489</v>
+        <v>0.21033544880723226</v>
       </c>
       <c r="N31">
         <v>3</v>
@@ -9645,10 +9645,10 @@
         <v>297</v>
       </c>
       <c r="L32">
-        <v>98.313749999999999</v>
+        <v>70.014831327549786</v>
       </c>
       <c r="M32">
-        <v>0.20968387807630626</v>
+        <v>0.20971598341683259</v>
       </c>
       <c r="N32">
         <v>4</v>
@@ -9683,10 +9683,10 @@
         <v>297</v>
       </c>
       <c r="L33">
-        <v>61.298999999999999</v>
+        <v>49.059159381090566</v>
       </c>
       <c r="M33">
-        <v>0.20932545794315321</v>
+        <v>0.20916043769634082</v>
       </c>
       <c r="N33">
         <v>2</v>
@@ -9721,10 +9721,10 @@
         <v>297</v>
       </c>
       <c r="L34">
-        <v>115.902</v>
+        <v>78.57251718603159</v>
       </c>
       <c r="M34">
-        <v>0.20731661573958274</v>
+        <v>0.20723398780220204</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -9759,10 +9759,10 @@
         <v>297</v>
       </c>
       <c r="L35">
-        <v>62.902500000000003</v>
+        <v>56.173247894720831</v>
       </c>
       <c r="M35">
-        <v>0.20155131686133662</v>
+        <v>0.20144086551750767</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -9797,10 +9797,10 @@
         <v>297</v>
       </c>
       <c r="L36">
-        <v>174.36449999999999</v>
+        <v>144.5127788289449</v>
       </c>
       <c r="M36">
-        <v>0.20060099842101647</v>
+        <v>0.20039243885616928</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -9835,10 +9835,10 @@
         <v>297</v>
       </c>
       <c r="L37">
-        <v>182.27625</v>
+        <v>130.29343895452624</v>
       </c>
       <c r="M37">
-        <v>0.20010662875885449</v>
+        <v>0.20023879043138662</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -9873,10 +9873,10 @@
         <v>297</v>
       </c>
       <c r="L38">
-        <v>129.40350000000001</v>
+        <v>116.04676348331648</v>
       </c>
       <c r="M38">
-        <v>0.20002791792163191</v>
+        <v>0.19986775544574151</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -9911,10 +9911,10 @@
         <v>297</v>
       </c>
       <c r="L39">
-        <v>169.16325000000001</v>
+        <v>137.36467075305919</v>
       </c>
       <c r="M39">
-        <v>0.19926453304830602</v>
+        <v>0.1991417433192304</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -9949,10 +9949,10 @@
         <v>297</v>
       </c>
       <c r="L40">
-        <v>83.121750000000006</v>
+        <v>73.144150230326332</v>
       </c>
       <c r="M40">
-        <v>0.19233918777602857</v>
+        <v>0.19246976833006127</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -9987,10 +9987,10 @@
         <v>297</v>
       </c>
       <c r="L41">
-        <v>106.032</v>
+        <v>85.393486645713551</v>
       </c>
       <c r="M41">
-        <v>0.19100798535889857</v>
+        <v>0.19065785667609689</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -10025,10 +10025,10 @@
         <v>297</v>
       </c>
       <c r="L42">
-        <v>88.896749999999997</v>
+        <v>67.888894100382686</v>
       </c>
       <c r="M42">
-        <v>0.1902810220251446</v>
+        <v>0.19017042388075728</v>
       </c>
       <c r="N42">
         <v>3</v>
@@ -10063,10 +10063,10 @@
         <v>297</v>
       </c>
       <c r="L43">
-        <v>73.164749999999998</v>
+        <v>71.572221990025227</v>
       </c>
       <c r="M43">
-        <v>0.18982105897633786</v>
+        <v>0.18977645647302857</v>
       </c>
       <c r="N43">
         <v>5</v>
@@ -10101,10 +10101,10 @@
         <v>297</v>
       </c>
       <c r="L44">
-        <v>76.660499999999999</v>
+        <v>69.710247669542099</v>
       </c>
       <c r="M44">
-        <v>0.1890868051373899</v>
+        <v>0.18909066036225713</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -10139,10 +10139,10 @@
         <v>297</v>
       </c>
       <c r="L45">
-        <v>40.175249999999998</v>
+        <v>37.919089703819211</v>
       </c>
       <c r="M45">
-        <v>0.18129522702625309</v>
+        <v>0.18133223084209096</v>
       </c>
       <c r="N45">
         <v>2</v>
@@ -10177,10 +10177,10 @@
         <v>297</v>
       </c>
       <c r="L46">
-        <v>17.487749999999998</v>
+        <v>16.810332840556537</v>
       </c>
       <c r="M46">
-        <v>0.18119484365966679</v>
+        <v>0.18132091732690964</v>
       </c>
       <c r="N46">
         <v>4</v>
@@ -10215,10 +10215,10 @@
         <v>297</v>
       </c>
       <c r="L47">
-        <v>67.797749999999994</v>
+        <v>62.186485506174868</v>
       </c>
       <c r="M47">
-        <v>0.18063610417267537</v>
+        <v>0.18071357240916414</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -10253,10 +10253,10 @@
         <v>297</v>
       </c>
       <c r="L48">
-        <v>39.508499999999998</v>
+        <v>35.233977803274506</v>
       </c>
       <c r="M48">
-        <v>0.18024950622638164</v>
+        <v>0.18021595689272221</v>
       </c>
       <c r="N48">
         <v>3</v>
@@ -10291,10 +10291,10 @@
         <v>297</v>
       </c>
       <c r="L49">
-        <v>21.18</v>
+        <v>21.142866664160429</v>
       </c>
       <c r="M49">
-        <v>0.17931321763509145</v>
+        <v>0.17931533610379399</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -10329,13 +10329,13 @@
         <v>297</v>
       </c>
       <c r="L50">
-        <v>3.6539999999999999</v>
+        <v>17.087869952488681</v>
       </c>
       <c r="M50">
-        <v>0.17250956376973944</v>
+        <v>0.17260823037661066</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:14">
@@ -10367,13 +10367,13 @@
         <v>297</v>
       </c>
       <c r="L51">
-        <v>20.751750000000001</v>
+        <v>3.6539999999999999</v>
       </c>
       <c r="M51">
-        <v>0.17250105163269647</v>
+        <v>0.17250956376973944</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="2:14">
@@ -10405,10 +10405,10 @@
         <v>297</v>
       </c>
       <c r="L52">
-        <v>10.106249999999999</v>
+        <v>8.9326894887680304</v>
       </c>
       <c r="M52">
-        <v>0.17131411772085359</v>
+        <v>0.1713361657962669</v>
       </c>
       <c r="N52">
         <v>2</v>
@@ -10443,10 +10443,10 @@
         <v>297</v>
       </c>
       <c r="L53">
-        <v>1.9417500000000001</v>
+        <v>1.9393772345594256</v>
       </c>
       <c r="M53">
-        <v>0.17127251204639216</v>
+        <v>0.17126812287478294</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -10481,10 +10481,10 @@
         <v>297</v>
       </c>
       <c r="L54">
-        <v>6.9989999999999997</v>
+        <v>6.9978028864995911</v>
       </c>
       <c r="M54">
-        <v>0.17051485985637715</v>
+        <v>0.1705148997972831</v>
       </c>
       <c r="N54">
         <v>3</v>
@@ -10595,10 +10595,10 @@
         <v>297</v>
       </c>
       <c r="L57">
-        <v>3.2715000000000001</v>
+        <v>2.3912871754147842</v>
       </c>
       <c r="M57">
-        <v>0.16086680077507476</v>
+        <v>0.1609725985645156</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -10671,10 +10671,10 @@
         <v>297</v>
       </c>
       <c r="L59">
-        <v>0.31424999999999997</v>
+        <v>0.30866280052937284</v>
       </c>
       <c r="M59">
-        <v>0.15864399626038275</v>
+        <v>0.15861383642938454</v>
       </c>
       <c r="N59">
         <v>2</v>
@@ -10747,10 +10747,10 @@
         <v>297</v>
       </c>
       <c r="L61">
-        <v>9.5250000000000001E-2</v>
+        <v>9.2584045393858477E-2</v>
       </c>
       <c r="M61">
-        <v>0.15274110566958982</v>
+        <v>0.15274487557442543</v>
       </c>
       <c r="N61">
         <v>2</v>
@@ -10823,10 +10823,10 @@
         <v>297</v>
       </c>
       <c r="L63">
-        <v>0.24</v>
+        <v>0.1495867211342399</v>
       </c>
       <c r="M63">
-        <v>0.1512927886179273</v>
+        <v>0.15140574682681396</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -10861,7 +10861,7 @@
         <v>297</v>
       </c>
       <c r="L64">
-        <v>0.13950000000000001</v>
+        <v>0.12739587699673252</v>
       </c>
       <c r="M64">
         <v>0.14928828021448251</v>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8573628F-7249-4CD8-AE15-B1E681F034EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC627863-8385-4420-B742-E646B908FC34}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10997,7 +10997,7 @@
         <v>804</v>
       </c>
       <c r="L11">
-        <v>0.16500000000000001</v>
+        <v>9.7398474906898388E-2</v>
       </c>
       <c r="M11">
         <v>0.7191696570031374</v>
@@ -11071,7 +11071,7 @@
         <v>804</v>
       </c>
       <c r="L12">
-        <v>0.71099999999999997</v>
+        <v>0.43757129990993693</v>
       </c>
       <c r="M12">
         <v>0.71494200599841473</v>
@@ -11145,7 +11145,7 @@
         <v>804</v>
       </c>
       <c r="L13">
-        <v>0.32174999999999998</v>
+        <v>0.17620783693224129</v>
       </c>
       <c r="M13">
         <v>0.65905157997063557</v>
@@ -11219,7 +11219,7 @@
         <v>804</v>
       </c>
       <c r="L14">
-        <v>2.2499999999999999E-2</v>
+        <v>1.1570405911633396E-2</v>
       </c>
       <c r="M14">
         <v>0.63200140032601226</v>
@@ -11293,7 +11293,7 @@
         <v>804</v>
       </c>
       <c r="L15">
-        <v>0.1875</v>
+        <v>9.1899232937238826E-2</v>
       </c>
       <c r="M15">
         <v>0.60031961262251998</v>
@@ -11367,7 +11367,7 @@
         <v>804</v>
       </c>
       <c r="L16">
-        <v>0.48375000000000001</v>
+        <v>0.24696498099564293</v>
       </c>
       <c r="M16">
         <v>0.58089980183314383</v>
@@ -11441,7 +11441,7 @@
         <v>804</v>
       </c>
       <c r="L17">
-        <v>0.23025000000000001</v>
+        <v>0.11273825528143006</v>
       </c>
       <c r="M17">
         <v>0.56457397346434446</v>
@@ -11515,7 +11515,7 @@
         <v>804</v>
       </c>
       <c r="L18">
-        <v>0.19800000000000001</v>
+        <v>9.8366964416459216E-2</v>
       </c>
       <c r="M18">
         <v>0.55267182256682024</v>
@@ -11589,7 +11589,7 @@
         <v>804</v>
       </c>
       <c r="L19">
-        <v>0.76275000000000004</v>
+        <v>0.41373531514830508</v>
       </c>
       <c r="M19">
         <v>0.53193793087411478</v>
@@ -11663,7 +11663,7 @@
         <v>804</v>
       </c>
       <c r="L20">
-        <v>0.13725000000000001</v>
+        <v>7.8685874089490113E-2</v>
       </c>
       <c r="M20">
         <v>0.52747452162553121</v>
@@ -11737,7 +11737,7 @@
         <v>804</v>
       </c>
       <c r="L21">
-        <v>3.0000000000000001E-3</v>
+        <v>1.9933514482280167E-3</v>
       </c>
       <c r="M21">
         <v>0.5201606594153787</v>
@@ -11811,7 +11811,7 @@
         <v>804</v>
       </c>
       <c r="L22">
-        <v>0.20549999999999999</v>
+        <v>0.10150759468372139</v>
       </c>
       <c r="M22">
         <v>0.51423128005084473</v>
@@ -11885,7 +11885,7 @@
         <v>804</v>
       </c>
       <c r="L23">
-        <v>0.48</v>
+        <v>0.27187941592086667</v>
       </c>
       <c r="M23">
         <v>0.51367633290031955</v>
@@ -11959,7 +11959,7 @@
         <v>804</v>
       </c>
       <c r="L24">
-        <v>0.11475</v>
+        <v>4.8150668647845472E-2</v>
       </c>
       <c r="M24">
         <v>0.51276676736459725</v>
@@ -12033,7 +12033,7 @@
         <v>804</v>
       </c>
       <c r="L25">
-        <v>0.20924999999999999</v>
+        <v>0.10626089807026223</v>
       </c>
       <c r="M25">
         <v>0.51082960266199562</v>
@@ -12107,7 +12107,7 @@
         <v>804</v>
       </c>
       <c r="L26">
-        <v>2.3595000000000002</v>
+        <v>1.4437561073655423</v>
       </c>
       <c r="M26">
         <v>0.50968993081838243</v>
@@ -12181,7 +12181,7 @@
         <v>804</v>
       </c>
       <c r="L27">
-        <v>7.9500000000000001E-2</v>
+        <v>3.8487520958083832E-2</v>
       </c>
       <c r="M27">
         <v>0.4991687459873973</v>
@@ -12255,7 +12255,7 @@
         <v>804</v>
       </c>
       <c r="L28">
-        <v>9.0749999999999997E-2</v>
+        <v>5.1364672364672362E-2</v>
       </c>
       <c r="M28">
         <v>0.49763899641751419</v>
@@ -12329,7 +12329,7 @@
         <v>804</v>
       </c>
       <c r="L29">
-        <v>1.9732499999999999</v>
+        <v>1.1778242912674908</v>
       </c>
       <c r="M29">
         <v>0.49688520582565188</v>
@@ -12403,7 +12403,7 @@
         <v>804</v>
       </c>
       <c r="L30">
-        <v>3.7499999999999999E-2</v>
+        <v>2.2315534497444632E-2</v>
       </c>
       <c r="M30">
         <v>0.49199195783716826</v>
@@ -12551,7 +12551,7 @@
         <v>804</v>
       </c>
       <c r="L32">
-        <v>8.6249999999999993E-2</v>
+        <v>5.2061911115952285E-2</v>
       </c>
       <c r="M32">
         <v>0.48871615741329361</v>
@@ -12625,7 +12625,7 @@
         <v>804</v>
       </c>
       <c r="L33">
-        <v>0.51749999999999996</v>
+        <v>0.3282007550233651</v>
       </c>
       <c r="M33">
         <v>0.48558148622467689</v>
@@ -12699,10 +12699,10 @@
         <v>804</v>
       </c>
       <c r="L34">
-        <v>0.24525</v>
+        <v>0.15269232685600401</v>
       </c>
       <c r="M34">
-        <v>0.48286546881727738</v>
+        <v>0.48286546881727732</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -12773,7 +12773,7 @@
         <v>804</v>
       </c>
       <c r="L35">
-        <v>0.03</v>
+        <v>1.7168608600240345E-2</v>
       </c>
       <c r="M35">
         <v>0.47992193265827882</v>
@@ -12847,10 +12847,10 @@
         <v>804</v>
       </c>
       <c r="L36">
-        <v>7.9500000000000001E-2</v>
+        <v>4.780380942103276E-2</v>
       </c>
       <c r="M36">
-        <v>0.47901478939388781</v>
+        <v>0.47901478939388786</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -12921,7 +12921,7 @@
         <v>804</v>
       </c>
       <c r="L37">
-        <v>2.2807499999999998</v>
+        <v>1.5173877380341625</v>
       </c>
       <c r="M37">
         <v>0.4701360302477815</v>
@@ -12995,10 +12995,10 @@
         <v>804</v>
       </c>
       <c r="L38">
-        <v>0.111</v>
+        <v>7.0740646587455103E-2</v>
       </c>
       <c r="M38">
-        <v>0.4682564160918517</v>
+        <v>0.46825641609185176</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -13069,7 +13069,7 @@
         <v>804</v>
       </c>
       <c r="L39">
-        <v>2.7E-2</v>
+        <v>1.4911879503602883E-2</v>
       </c>
       <c r="M39">
         <v>0.46224696285045208</v>
@@ -13143,7 +13143,7 @@
         <v>804</v>
       </c>
       <c r="L40">
-        <v>2.8102499999999999</v>
+        <v>1.8821979944728573</v>
       </c>
       <c r="M40">
         <v>0.45140716122873509</v>
@@ -13217,10 +13217,10 @@
         <v>804</v>
       </c>
       <c r="L41">
-        <v>6.8250000000000005E-2</v>
+        <v>3.9815773638218824E-2</v>
       </c>
       <c r="M41">
-        <v>0.44581658447224271</v>
+        <v>0.44581658447224276</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -13291,7 +13291,7 @@
         <v>804</v>
       </c>
       <c r="L42">
-        <v>2.2845</v>
+        <v>1.4751660481650422</v>
       </c>
       <c r="M42">
         <v>0.44578897053974548</v>
@@ -13365,7 +13365,7 @@
         <v>804</v>
       </c>
       <c r="L43">
-        <v>0.44174999999999998</v>
+        <v>0.18580058405489297</v>
       </c>
       <c r="M43">
         <v>0.44023779981200739</v>
@@ -13439,7 +13439,7 @@
         <v>804</v>
       </c>
       <c r="L44">
-        <v>0.2205</v>
+        <v>0.12472962181708601</v>
       </c>
       <c r="M44">
         <v>0.43973222817450658</v>
@@ -13513,7 +13513,7 @@
         <v>804</v>
       </c>
       <c r="L45">
-        <v>0.56399999999999995</v>
+        <v>0.24684620229248011</v>
       </c>
       <c r="M45">
         <v>0.43767251031908422</v>
@@ -13587,7 +13587,7 @@
         <v>804</v>
       </c>
       <c r="L46">
-        <v>1.49325</v>
+        <v>0.82329252858282376</v>
       </c>
       <c r="M46">
         <v>0.43730618239424862</v>
@@ -13661,10 +13661,10 @@
         <v>804</v>
       </c>
       <c r="L47">
-        <v>3.0615000000000001</v>
+        <v>1.8322330425769342</v>
       </c>
       <c r="M47">
-        <v>0.43559103237274016</v>
+        <v>0.43559116617442661</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -13735,10 +13735,10 @@
         <v>804</v>
       </c>
       <c r="L48">
-        <v>2.3730000000000002</v>
+        <v>1.6333334672098223</v>
       </c>
       <c r="M48">
-        <v>0.43351725225935694</v>
+        <v>0.43351725225935689</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -13809,10 +13809,10 @@
         <v>804</v>
       </c>
       <c r="L49">
-        <v>1.4999999999999999E-2</v>
+        <v>8.6840847538633102E-3</v>
       </c>
       <c r="M49">
-        <v>0.43251741216306833</v>
+        <v>0.43251741216306838</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -13883,7 +13883,7 @@
         <v>804</v>
       </c>
       <c r="L50">
-        <v>1.7535000000000001</v>
+        <v>1.204412539046676</v>
       </c>
       <c r="M50">
         <v>0.42745275386001841</v>
@@ -13957,10 +13957,10 @@
         <v>804</v>
       </c>
       <c r="L51">
-        <v>0.51975000000000005</v>
+        <v>0.32094470591435881</v>
       </c>
       <c r="M51">
-        <v>0.42681353019096763</v>
+        <v>0.42681353019096768</v>
       </c>
       <c r="N51">
         <v>2</v>
@@ -14031,7 +14031,7 @@
         <v>804</v>
       </c>
       <c r="L52">
-        <v>3.5542500000000001</v>
+        <v>2.0705126313131279</v>
       </c>
       <c r="M52">
         <v>0.42627854825613187</v>
@@ -14105,10 +14105,10 @@
         <v>804</v>
       </c>
       <c r="L53">
-        <v>6.7499999999999999E-3</v>
+        <v>2.7117662395709178E-3</v>
       </c>
       <c r="M53">
-        <v>0.42492179359308618</v>
+        <v>0.42492179359308624</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -14179,7 +14179,7 @@
         <v>804</v>
       </c>
       <c r="L54">
-        <v>0.126</v>
+        <v>5.8824467846739864E-2</v>
       </c>
       <c r="M54">
         <v>0.42122179357411937</v>
@@ -14253,10 +14253,10 @@
         <v>804</v>
       </c>
       <c r="L55">
-        <v>2.0992500000000001</v>
+        <v>1.3140340423210619</v>
       </c>
       <c r="M55">
-        <v>0.41884304195979666</v>
+        <v>0.41874619281978304</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -14327,7 +14327,7 @@
         <v>804</v>
       </c>
       <c r="L56">
-        <v>1.44075</v>
+        <v>0.73222198698030228</v>
       </c>
       <c r="M56">
         <v>0.41589632149504963</v>
@@ -14401,10 +14401,10 @@
         <v>804</v>
       </c>
       <c r="L57">
-        <v>3.4409999999999998</v>
+        <v>1.9769905787819222</v>
       </c>
       <c r="M57">
-        <v>0.4157160061887139</v>
+        <v>0.4157248242625895</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -14475,7 +14475,7 @@
         <v>804</v>
       </c>
       <c r="L58">
-        <v>0.87</v>
+        <v>0.49617743254292718</v>
       </c>
       <c r="M58">
         <v>0.41280531453440872</v>
@@ -14549,7 +14549,7 @@
         <v>804</v>
       </c>
       <c r="L59">
-        <v>3.1829999999999998</v>
+        <v>1.9304554204124802</v>
       </c>
       <c r="M59">
         <v>0.41227621428626549</v>
@@ -14623,7 +14623,7 @@
         <v>804</v>
       </c>
       <c r="L60">
-        <v>2.2334999999999998</v>
+        <v>1.2745920573055001</v>
       </c>
       <c r="M60">
         <v>0.4096764321113423</v>
@@ -14697,7 +14697,7 @@
         <v>804</v>
       </c>
       <c r="L61">
-        <v>0.06</v>
+        <v>3.3467082214841438E-2</v>
       </c>
       <c r="M61">
         <v>0.40785739154057549</v>
@@ -14771,10 +14771,10 @@
         <v>804</v>
       </c>
       <c r="L62">
-        <v>5.9512499999999999</v>
+        <v>3.79008166492638</v>
       </c>
       <c r="M62">
-        <v>0.40760871544679134</v>
+        <v>0.40760866605135476</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -14845,7 +14845,7 @@
         <v>804</v>
       </c>
       <c r="L63">
-        <v>0.55274999999999996</v>
+        <v>0.2218954495137187</v>
       </c>
       <c r="M63">
         <v>0.4027192620583317</v>
@@ -14919,10 +14919,10 @@
         <v>804</v>
       </c>
       <c r="L64">
-        <v>1.25475</v>
+        <v>0.63429674892825172</v>
       </c>
       <c r="M64">
-        <v>0.40237335602262053</v>
+        <v>0.40237427076191407</v>
       </c>
       <c r="N64">
         <v>2</v>
@@ -14993,7 +14993,7 @@
         <v>804</v>
       </c>
       <c r="L65">
-        <v>0.3</v>
+        <v>0.1289176682938836</v>
       </c>
       <c r="M65">
         <v>0.40200024067814899</v>
@@ -15067,10 +15067,10 @@
         <v>804</v>
       </c>
       <c r="L66">
-        <v>4.3027499999999996</v>
+        <v>2.5591288683511593</v>
       </c>
       <c r="M66">
-        <v>0.39837258475711784</v>
+        <v>0.39875036267177777</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -15141,7 +15141,7 @@
         <v>804</v>
       </c>
       <c r="L67">
-        <v>4.2000000000000003E-2</v>
+        <v>1.7127849126460717E-2</v>
       </c>
       <c r="M67">
         <v>0.39536388538264639</v>
@@ -15215,7 +15215,7 @@
         <v>804</v>
       </c>
       <c r="L68">
-        <v>5.7809999999999997</v>
+        <v>3.0008174583681289</v>
       </c>
       <c r="M68">
         <v>0.39457090034177461</v>
@@ -15289,10 +15289,10 @@
         <v>804</v>
       </c>
       <c r="L69">
-        <v>2.1629999999999998</v>
+        <v>1.2105806124092169</v>
       </c>
       <c r="M69">
-        <v>0.39134180722122569</v>
+        <v>0.39133665464571071</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -15363,7 +15363,7 @@
         <v>804</v>
       </c>
       <c r="L70">
-        <v>4.1760000000000002</v>
+        <v>2.2321996074582922</v>
       </c>
       <c r="M70">
         <v>0.39115351459958941</v>
@@ -15437,7 +15437,7 @@
         <v>804</v>
       </c>
       <c r="L71">
-        <v>0.42149999999999999</v>
+        <v>0.23346904773419744</v>
       </c>
       <c r="M71">
         <v>0.39017953122356952</v>
@@ -15511,7 +15511,7 @@
         <v>804</v>
       </c>
       <c r="L72">
-        <v>3.1237499999999998</v>
+        <v>1.7565111987650552</v>
       </c>
       <c r="M72">
         <v>0.39011040101959582</v>
@@ -15585,7 +15585,7 @@
         <v>804</v>
       </c>
       <c r="L73">
-        <v>1.1265000000000001</v>
+        <v>0.73465356632411616</v>
       </c>
       <c r="M73">
         <v>0.3821280816273106</v>
@@ -15659,7 +15659,7 @@
         <v>804</v>
       </c>
       <c r="L74">
-        <v>5.2500000000000003E-3</v>
+        <v>2.3998098626104025E-3</v>
       </c>
       <c r="M74">
         <v>0.38023778067157149</v>
@@ -15733,7 +15733,7 @@
         <v>804</v>
       </c>
       <c r="L75">
-        <v>1.01475</v>
+        <v>0.5577856724575444</v>
       </c>
       <c r="M75">
         <v>0.37958017434708069</v>
@@ -15807,7 +15807,7 @@
         <v>804</v>
       </c>
       <c r="L76">
-        <v>2.9820000000000002</v>
+        <v>1.5771994961728515</v>
       </c>
       <c r="M76">
         <v>0.37919883015963801</v>
@@ -15881,7 +15881,7 @@
         <v>804</v>
       </c>
       <c r="L77">
-        <v>4.6732500000000003</v>
+        <v>2.3566909382631192</v>
       </c>
       <c r="M77">
         <v>0.37600176811186109</v>
@@ -15955,10 +15955,10 @@
         <v>804</v>
       </c>
       <c r="L78">
-        <v>2.8784999999999998</v>
+        <v>1.7406424458328442</v>
       </c>
       <c r="M78">
-        <v>0.37358861916362623</v>
+        <v>0.37362852416084857</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -16029,7 +16029,7 @@
         <v>804</v>
       </c>
       <c r="L79">
-        <v>1.125E-2</v>
+        <v>3.6574074074074074E-3</v>
       </c>
       <c r="M79">
         <v>0.37050476120479747</v>
@@ -16103,10 +16103,10 @@
         <v>804</v>
       </c>
       <c r="L80">
-        <v>6.4747500000000002</v>
+        <v>3.295532422269043</v>
       </c>
       <c r="M80">
-        <v>0.37018716763962745</v>
+        <v>0.37019316405664326</v>
       </c>
       <c r="N80">
         <v>3</v>
@@ -16177,7 +16177,7 @@
         <v>804</v>
       </c>
       <c r="L81">
-        <v>3.0000000000000001E-3</v>
+        <v>9.96495825461637E-4</v>
       </c>
       <c r="M81">
         <v>0.36908471448379471</v>
@@ -16251,10 +16251,10 @@
         <v>804</v>
       </c>
       <c r="L82">
-        <v>0.93974999999999997</v>
+        <v>0.51243155036666865</v>
       </c>
       <c r="M82">
-        <v>0.36639877938962556</v>
+        <v>0.36640362809288762</v>
       </c>
       <c r="N82">
         <v>2</v>
@@ -16325,10 +16325,10 @@
         <v>804</v>
       </c>
       <c r="L83">
-        <v>0.42</v>
+        <v>0.15354120957401338</v>
       </c>
       <c r="M83">
-        <v>0.36441102193788871</v>
+        <v>0.36438735151163104</v>
       </c>
       <c r="N83">
         <v>5</v>
@@ -16399,10 +16399,10 @@
         <v>804</v>
       </c>
       <c r="L84">
-        <v>3.1815000000000002</v>
+        <v>1.933209740197273</v>
       </c>
       <c r="M84">
-        <v>0.36151552005714832</v>
+        <v>0.3615152561679234</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -16473,10 +16473,10 @@
         <v>804</v>
       </c>
       <c r="L85">
-        <v>5.2320000000000002</v>
+        <v>2.7101889671130204</v>
       </c>
       <c r="M85">
-        <v>0.35944877599053376</v>
+        <v>0.35973332891280696</v>
       </c>
       <c r="N85">
         <v>3</v>
@@ -16547,13 +16547,13 @@
         <v>804</v>
       </c>
       <c r="L86">
-        <v>0.10875</v>
+        <v>3.4575767361981664</v>
       </c>
       <c r="M86">
-        <v>0.35889634925967584</v>
+        <v>0.35898831135479436</v>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P86" t="s">
         <v>182</v>
@@ -16621,13 +16621,13 @@
         <v>804</v>
       </c>
       <c r="L87">
-        <v>5.3842499999999998</v>
+        <v>4.8331881592320644E-2</v>
       </c>
       <c r="M87">
-        <v>0.3587834375638449</v>
+        <v>0.35889654721421277</v>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P87" t="s">
         <v>182</v>
@@ -16695,10 +16695,10 @@
         <v>804</v>
       </c>
       <c r="L88">
-        <v>8.1329999999999991</v>
+        <v>4.8872709073901932</v>
       </c>
       <c r="M88">
-        <v>0.35132366056444975</v>
+        <v>0.35130800052253713</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -16769,7 +16769,7 @@
         <v>804</v>
       </c>
       <c r="L89">
-        <v>4.6612499999999999</v>
+        <v>2.7609107730710458</v>
       </c>
       <c r="M89">
         <v>0.3499932515005244</v>
@@ -16843,7 +16843,7 @@
         <v>804</v>
       </c>
       <c r="L90">
-        <v>2.3302499999999999</v>
+        <v>1.0189103761562657</v>
       </c>
       <c r="M90">
         <v>0.34652234123519837</v>
@@ -16917,7 +16917,7 @@
         <v>804</v>
       </c>
       <c r="L91">
-        <v>0.16125</v>
+        <v>5.3900478641741176E-2</v>
       </c>
       <c r="M91">
         <v>0.34598632210742603</v>
@@ -16991,10 +16991,10 @@
         <v>804</v>
       </c>
       <c r="L92">
-        <v>3.15225</v>
+        <v>1.8213320851645813</v>
       </c>
       <c r="M92">
-        <v>0.34592439814125542</v>
+        <v>0.34592439814125536</v>
       </c>
       <c r="N92">
         <v>3</v>
@@ -17065,10 +17065,10 @@
         <v>804</v>
       </c>
       <c r="L93">
-        <v>4.6057499999999996</v>
+        <v>2.5172949114250192</v>
       </c>
       <c r="M93">
-        <v>0.34399941887788849</v>
+        <v>0.34399214123132765</v>
       </c>
       <c r="N93">
         <v>2</v>
@@ -17139,10 +17139,10 @@
         <v>804</v>
       </c>
       <c r="L94">
-        <v>4.65E-2</v>
+        <v>1.4648842407531936E-2</v>
       </c>
       <c r="M94">
-        <v>0.34211437700458169</v>
+        <v>0.34209998385531665</v>
       </c>
       <c r="N94">
         <v>5</v>
@@ -17213,10 +17213,10 @@
         <v>804</v>
       </c>
       <c r="L95">
-        <v>6.3345000000000002</v>
+        <v>2.9990126470674681</v>
       </c>
       <c r="M95">
-        <v>0.34066600883238901</v>
+        <v>0.3407303535830376</v>
       </c>
       <c r="N95">
         <v>3</v>
@@ -17287,10 +17287,10 @@
         <v>804</v>
       </c>
       <c r="L96">
-        <v>4.0462499999999997</v>
+        <v>2.4108310694232142</v>
       </c>
       <c r="M96">
-        <v>0.34024565408007856</v>
+        <v>0.34019944626648557</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -17361,10 +17361,10 @@
         <v>804</v>
       </c>
       <c r="L97">
-        <v>0.84824999999999995</v>
+        <v>0.37336913797068721</v>
       </c>
       <c r="M97">
-        <v>0.33598999566171778</v>
+        <v>0.33597551605507514</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -17435,10 +17435,10 @@
         <v>804</v>
       </c>
       <c r="L98">
-        <v>3.9165000000000001</v>
+        <v>2.2692398901185427</v>
       </c>
       <c r="M98">
-        <v>0.3336371219076687</v>
+        <v>0.33363512198847051</v>
       </c>
       <c r="N98">
         <v>2</v>
@@ -17509,7 +17509,7 @@
         <v>804</v>
       </c>
       <c r="L99">
-        <v>2.2357499999999999</v>
+        <v>1.4515636262280183</v>
       </c>
       <c r="M99">
         <v>0.33076168208006679</v>
@@ -17583,10 +17583,10 @@
         <v>804</v>
       </c>
       <c r="L100">
-        <v>7.35</v>
+        <v>4.4025865463278082</v>
       </c>
       <c r="M100">
-        <v>0.32845198316322927</v>
+        <v>0.32841368448459896</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         <v>804</v>
       </c>
       <c r="L101">
-        <v>2.7570000000000001</v>
+        <v>1.5504845208117317</v>
       </c>
       <c r="M101">
         <v>0.32830234167954908</v>
@@ -17731,7 +17731,7 @@
         <v>804</v>
       </c>
       <c r="L102">
-        <v>3.0517500000000002</v>
+        <v>1.5664629679918325</v>
       </c>
       <c r="M102">
         <v>0.32669902880814938</v>
@@ -17805,10 +17805,10 @@
         <v>804</v>
       </c>
       <c r="L103">
-        <v>2.0910000000000002</v>
+        <v>0.8909343046109206</v>
       </c>
       <c r="M103">
-        <v>0.32200791025765313</v>
+        <v>0.32204753446078982</v>
       </c>
       <c r="N103">
         <v>4</v>
@@ -17879,10 +17879,10 @@
         <v>804</v>
       </c>
       <c r="L104">
-        <v>8.9954999999999998</v>
+        <v>4.7571826711999234</v>
       </c>
       <c r="M104">
-        <v>0.321722531364808</v>
+        <v>0.32159491657161282</v>
       </c>
       <c r="N104">
         <v>3</v>
@@ -17953,10 +17953,10 @@
         <v>804</v>
       </c>
       <c r="L105">
-        <v>1.1835</v>
+        <v>0.43581570479147785</v>
       </c>
       <c r="M105">
-        <v>0.32152543947842899</v>
+        <v>0.32151572315137106</v>
       </c>
       <c r="N105">
         <v>5</v>
@@ -18027,10 +18027,10 @@
         <v>804</v>
       </c>
       <c r="L106">
-        <v>7.28925</v>
+        <v>4.1790301881767649</v>
       </c>
       <c r="M106">
-        <v>0.3197992070574347</v>
+        <v>0.31980072625039729</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -18101,10 +18101,10 @@
         <v>804</v>
       </c>
       <c r="L107">
-        <v>8.8897499999999994</v>
+        <v>5.6646693835038624</v>
       </c>
       <c r="M107">
-        <v>0.31828991868890427</v>
+        <v>0.31823526013130077</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -18175,10 +18175,10 @@
         <v>804</v>
       </c>
       <c r="L108">
-        <v>6.9022500000000004</v>
+        <v>3.847989483952559</v>
       </c>
       <c r="M108">
-        <v>0.31108791892590437</v>
+        <v>0.31097614343980012</v>
       </c>
       <c r="N108">
         <v>2</v>
@@ -18249,10 +18249,10 @@
         <v>804</v>
       </c>
       <c r="L109">
-        <v>0.84299999999999997</v>
+        <v>0.30073405265474368</v>
       </c>
       <c r="M109">
-        <v>0.31095807318708885</v>
+        <v>0.31095779695468823</v>
       </c>
       <c r="N109">
         <v>5</v>
@@ -18323,10 +18323,10 @@
         <v>804</v>
       </c>
       <c r="L110">
-        <v>5.0490000000000004</v>
+        <v>2.3245358721567073</v>
       </c>
       <c r="M110">
-        <v>0.31056897549360329</v>
+        <v>0.31062575099279077</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -18397,10 +18397,10 @@
         <v>804</v>
       </c>
       <c r="L111">
-        <v>0.2235</v>
+        <v>8.6993697467428757E-2</v>
       </c>
       <c r="M111">
-        <v>0.30938898991155306</v>
+        <v>0.30933409324147326</v>
       </c>
       <c r="N111">
         <v>4</v>
@@ -18471,10 +18471,10 @@
         <v>804</v>
       </c>
       <c r="L112">
-        <v>6.0164999999999997</v>
+        <v>3.690679009118111</v>
       </c>
       <c r="M112">
-        <v>0.30882565752233126</v>
+        <v>0.30879241688360148</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -18545,10 +18545,10 @@
         <v>804</v>
       </c>
       <c r="L113">
-        <v>4.5082500000000003</v>
+        <v>2.4930897512525561</v>
       </c>
       <c r="M113">
-        <v>0.30102596152929756</v>
+        <v>0.30101575303543215</v>
       </c>
       <c r="N113">
         <v>3</v>
@@ -18619,10 +18619,10 @@
         <v>804</v>
       </c>
       <c r="L114">
-        <v>4.6267500000000004</v>
+        <v>2.6905002792932944</v>
       </c>
       <c r="M114">
-        <v>0.30053832502716887</v>
+        <v>0.30041979776435812</v>
       </c>
       <c r="N114">
         <v>4</v>
@@ -18693,10 +18693,10 @@
         <v>804</v>
       </c>
       <c r="L115">
-        <v>6.2024999999999997</v>
+        <v>3.6004221032584569</v>
       </c>
       <c r="M115">
-        <v>0.29912356704190535</v>
+        <v>0.29910281009329681</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -18767,10 +18767,10 @@
         <v>804</v>
       </c>
       <c r="L116">
-        <v>2.0295000000000001</v>
+        <v>0.99431642548015509</v>
       </c>
       <c r="M116">
-        <v>0.29905278333335766</v>
+        <v>0.29903626261444549</v>
       </c>
       <c r="N116">
         <v>5</v>
@@ -18841,10 +18841,10 @@
         <v>804</v>
       </c>
       <c r="L117">
-        <v>10.59525</v>
+        <v>6.1657447284388454</v>
       </c>
       <c r="M117">
-        <v>0.29893209607588889</v>
+        <v>0.2989172821821145</v>
       </c>
       <c r="N117">
         <v>2</v>
@@ -18915,10 +18915,10 @@
         <v>804</v>
       </c>
       <c r="L118">
-        <v>3.4747499999999998</v>
+        <v>2.0094738201721833</v>
       </c>
       <c r="M118">
-        <v>0.29324116946833584</v>
+        <v>0.29303475634729742</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -18989,10 +18989,10 @@
         <v>804</v>
       </c>
       <c r="L119">
-        <v>2.8260000000000001</v>
+        <v>1.5272709616368749</v>
       </c>
       <c r="M119">
-        <v>0.29016619688788708</v>
+        <v>0.29016255889546411</v>
       </c>
       <c r="N119">
         <v>3</v>
@@ -19063,10 +19063,10 @@
         <v>804</v>
       </c>
       <c r="L120">
-        <v>10.982250000000001</v>
+        <v>6.0663438137814643</v>
       </c>
       <c r="M120">
-        <v>0.28987437207732181</v>
+        <v>0.28985862873073293</v>
       </c>
       <c r="N120">
         <v>2</v>
@@ -19137,10 +19137,10 @@
         <v>804</v>
       </c>
       <c r="L121">
-        <v>12.807</v>
+        <v>8.0581975683936893</v>
       </c>
       <c r="M121">
-        <v>0.28954414736061107</v>
+        <v>0.28931363591494424</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -19211,10 +19211,10 @@
         <v>804</v>
       </c>
       <c r="L122">
-        <v>1.21875</v>
+        <v>0.47384898931153535</v>
       </c>
       <c r="M122">
-        <v>0.28631576681292398</v>
+        <v>0.28631414726570209</v>
       </c>
       <c r="N122">
         <v>5</v>
@@ -19285,10 +19285,10 @@
         <v>804</v>
       </c>
       <c r="L123">
-        <v>5.1494999999999997</v>
+        <v>2.896492148943449</v>
       </c>
       <c r="M123">
-        <v>0.28438273918250956</v>
+        <v>0.28440602294780448</v>
       </c>
       <c r="N123">
         <v>2</v>
@@ -19359,10 +19359,10 @@
         <v>804</v>
       </c>
       <c r="L124">
-        <v>4.4677499999999997</v>
+        <v>2.2814287959259865</v>
       </c>
       <c r="M124">
-        <v>0.28105723402160865</v>
+        <v>0.28106182430546611</v>
       </c>
       <c r="N124">
         <v>3</v>
@@ -19433,10 +19433,10 @@
         <v>804</v>
       </c>
       <c r="L125">
-        <v>5.4165000000000001</v>
+        <v>3.129484983818783</v>
       </c>
       <c r="M125">
-        <v>0.28069386457827655</v>
+        <v>0.28067166073141731</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -19507,10 +19507,10 @@
         <v>804</v>
       </c>
       <c r="L126">
-        <v>4.2862499999999999</v>
+        <v>1.7982764958683246</v>
       </c>
       <c r="M126">
-        <v>0.2772353254112162</v>
+        <v>0.27704478722363707</v>
       </c>
       <c r="N126">
         <v>4</v>
@@ -19581,10 +19581,10 @@
         <v>804</v>
       </c>
       <c r="L127">
-        <v>0.498</v>
+        <v>0.18393091727789446</v>
       </c>
       <c r="M127">
-        <v>0.27672533955697476</v>
+        <v>0.27672153724779708</v>
       </c>
       <c r="N127">
         <v>5</v>
@@ -19655,10 +19655,10 @@
         <v>804</v>
       </c>
       <c r="L128">
-        <v>6.3862500000000004</v>
+        <v>3.4018968391307434</v>
       </c>
       <c r="M128">
-        <v>0.2715674855166656</v>
+        <v>0.27147260213715657</v>
       </c>
       <c r="N128">
         <v>3</v>
@@ -19729,10 +19729,10 @@
         <v>804</v>
       </c>
       <c r="L129">
-        <v>2.0114999999999998</v>
+        <v>0.67763885184540795</v>
       </c>
       <c r="M129">
-        <v>0.27052875880079713</v>
+        <v>0.27051230463264214</v>
       </c>
       <c r="N129">
         <v>5</v>
@@ -19803,10 +19803,10 @@
         <v>804</v>
       </c>
       <c r="L130">
-        <v>10.4475</v>
+        <v>6.0093893145949382</v>
       </c>
       <c r="M130">
-        <v>0.26980068929416023</v>
+        <v>0.2698000482652832</v>
       </c>
       <c r="N130">
         <v>1</v>
@@ -19877,10 +19877,10 @@
         <v>804</v>
       </c>
       <c r="L131">
-        <v>9.2662499999999994</v>
+        <v>4.9249364135526257</v>
       </c>
       <c r="M131">
-        <v>0.26817077486189622</v>
+        <v>0.26814164018433323</v>
       </c>
       <c r="N131">
         <v>2</v>
@@ -19951,10 +19951,10 @@
         <v>804</v>
       </c>
       <c r="L132">
-        <v>4.9859999999999998</v>
+        <v>2.4101467924726094</v>
       </c>
       <c r="M132">
-        <v>0.26734609943617488</v>
+        <v>0.26733022626316438</v>
       </c>
       <c r="N132">
         <v>4</v>
@@ -20025,10 +20025,10 @@
         <v>804</v>
       </c>
       <c r="L133">
-        <v>4.2104999999999997</v>
+        <v>2.2039133433674141</v>
       </c>
       <c r="M133">
-        <v>0.26236461061506255</v>
+        <v>0.26235378789367603</v>
       </c>
       <c r="N133">
         <v>3</v>
@@ -20099,10 +20099,10 @@
         <v>804</v>
       </c>
       <c r="L134">
-        <v>6.4515000000000002</v>
+        <v>4.5916478260064322</v>
       </c>
       <c r="M134">
-        <v>0.25977233953146678</v>
+        <v>0.25942481159954706</v>
       </c>
       <c r="N134">
         <v>2</v>
@@ -20173,10 +20173,10 @@
         <v>804</v>
       </c>
       <c r="L135">
-        <v>6.7065000000000001</v>
+        <v>4.0060770481123287</v>
       </c>
       <c r="M135">
-        <v>0.25870366037437853</v>
+        <v>0.2586560774208444</v>
       </c>
       <c r="N135">
         <v>1</v>
@@ -20247,10 +20247,10 @@
         <v>804</v>
       </c>
       <c r="L136">
-        <v>5.0692500000000003</v>
+        <v>2.2022678923833694</v>
       </c>
       <c r="M136">
-        <v>0.25830170258148649</v>
+        <v>0.25824166381846347</v>
       </c>
       <c r="N136">
         <v>4</v>
@@ -20321,10 +20321,10 @@
         <v>804</v>
       </c>
       <c r="L137">
-        <v>0.38550000000000001</v>
+        <v>0.13683936706105471</v>
       </c>
       <c r="M137">
-        <v>0.25782023334208759</v>
+        <v>0.25781933874316371</v>
       </c>
       <c r="N137">
         <v>5</v>
@@ -20395,10 +20395,10 @@
         <v>804</v>
       </c>
       <c r="L138">
-        <v>14.199</v>
+        <v>8.9946572804857894</v>
       </c>
       <c r="M138">
-        <v>0.25266161738319426</v>
+        <v>0.25263887434809768</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -20469,10 +20469,10 @@
         <v>804</v>
       </c>
       <c r="L139">
-        <v>2.8319999999999999</v>
+        <v>1.0266178643710517</v>
       </c>
       <c r="M139">
-        <v>0.25129770050834227</v>
+        <v>0.25137607245089544</v>
       </c>
       <c r="N139">
         <v>5</v>
@@ -20543,10 +20543,10 @@
         <v>804</v>
       </c>
       <c r="L140">
-        <v>4.3732499999999996</v>
+        <v>2.1066277142799832</v>
       </c>
       <c r="M140">
-        <v>0.2501687621497215</v>
+        <v>0.2501659476474381</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -20617,10 +20617,10 @@
         <v>804</v>
       </c>
       <c r="L141">
-        <v>7.7024999999999997</v>
+        <v>3.8609228955867123</v>
       </c>
       <c r="M141">
-        <v>0.24998246913333699</v>
+        <v>0.24939127733540964</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -20691,10 +20691,10 @@
         <v>804</v>
       </c>
       <c r="L142">
-        <v>9.2279999999999998</v>
+        <v>4.9364878688650951</v>
       </c>
       <c r="M142">
-        <v>0.24888197219353206</v>
+        <v>0.24887372340308392</v>
       </c>
       <c r="N142">
         <v>2</v>
@@ -20765,10 +20765,10 @@
         <v>804</v>
       </c>
       <c r="L143">
-        <v>7.4842500000000003</v>
+        <v>3.7693651077342993</v>
       </c>
       <c r="M143">
-        <v>0.24295794232029405</v>
+        <v>0.24305244123332959</v>
       </c>
       <c r="N143">
         <v>2</v>
@@ -20839,10 +20839,10 @@
         <v>804</v>
       </c>
       <c r="L144">
-        <v>4.4467499999999998</v>
+        <v>1.7935471881954055</v>
       </c>
       <c r="M144">
-        <v>0.24285321373681426</v>
+        <v>0.24285845305661427</v>
       </c>
       <c r="N144">
         <v>4</v>
@@ -20913,10 +20913,10 @@
         <v>804</v>
       </c>
       <c r="L145">
-        <v>0.80100000000000005</v>
+        <v>0.26679190256916285</v>
       </c>
       <c r="M145">
-        <v>0.24280802115775624</v>
+        <v>0.24282327562791639</v>
       </c>
       <c r="N145">
         <v>5</v>
@@ -20987,10 +20987,10 @@
         <v>804</v>
       </c>
       <c r="L146">
-        <v>8.0122499999999999</v>
+        <v>3.7660385901929665</v>
       </c>
       <c r="M146">
-        <v>0.23952822043776656</v>
+        <v>0.23974689274236355</v>
       </c>
       <c r="N146">
         <v>3</v>
@@ -21061,10 +21061,10 @@
         <v>804</v>
       </c>
       <c r="L147">
-        <v>4.8810000000000002</v>
+        <v>3.084778883914066</v>
       </c>
       <c r="M147">
-        <v>0.23850115472963351</v>
+        <v>0.23848971833924495</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -21135,10 +21135,10 @@
         <v>804</v>
       </c>
       <c r="L148">
-        <v>3.69225</v>
+        <v>2.3762014299455796</v>
       </c>
       <c r="M148">
-        <v>0.23195576721170721</v>
+        <v>0.23155863007802063</v>
       </c>
       <c r="N148">
         <v>1</v>
@@ -21209,10 +21209,10 @@
         <v>804</v>
       </c>
       <c r="L149">
-        <v>8.2859999999999996</v>
+        <v>3.9683857768697415</v>
       </c>
       <c r="M149">
-        <v>0.22969919429336885</v>
+        <v>0.22968240471305368</v>
       </c>
       <c r="N149">
         <v>3</v>
@@ -21283,10 +21283,10 @@
         <v>804</v>
       </c>
       <c r="L150">
-        <v>6.8339999999999996</v>
+        <v>3.0997954505702627</v>
       </c>
       <c r="M150">
-        <v>0.22955996349490349</v>
+        <v>0.22965945187865039</v>
       </c>
       <c r="N150">
         <v>4</v>
@@ -21357,10 +21357,10 @@
         <v>804</v>
       </c>
       <c r="L151">
-        <v>3.48075</v>
+        <v>1.8924068097431741</v>
       </c>
       <c r="M151">
-        <v>0.22933285326536251</v>
+        <v>0.22936484009710512</v>
       </c>
       <c r="N151">
         <v>2</v>
@@ -21431,10 +21431,10 @@
         <v>804</v>
       </c>
       <c r="L152">
-        <v>3.9554999999999998</v>
+        <v>1.5690624660767625</v>
       </c>
       <c r="M152">
-        <v>0.227428691918485</v>
+        <v>0.22738607252081819</v>
       </c>
       <c r="N152">
         <v>5</v>
@@ -21505,10 +21505,10 @@
         <v>804</v>
       </c>
       <c r="L153">
-        <v>5.2417499999999997</v>
+        <v>1.88748560300502</v>
       </c>
       <c r="M153">
-        <v>0.22159131145743341</v>
+        <v>0.22148841968075822</v>
       </c>
       <c r="N153">
         <v>5</v>
@@ -21579,13 +21579,13 @@
         <v>804</v>
       </c>
       <c r="L154">
-        <v>6.2632500000000002</v>
+        <v>2.8787677843141766</v>
       </c>
       <c r="M154">
-        <v>0.22050603983846606</v>
+        <v>0.22053202007202716</v>
       </c>
       <c r="N154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P154" t="s">
         <v>182</v>
@@ -21653,13 +21653,13 @@
         <v>804</v>
       </c>
       <c r="L155">
-        <v>6.1829999999999998</v>
+        <v>3.6969196549641321</v>
       </c>
       <c r="M155">
-        <v>0.22046791375489233</v>
+        <v>0.22051895282124587</v>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P155" t="s">
         <v>182</v>
@@ -21727,10 +21727,10 @@
         <v>804</v>
       </c>
       <c r="L156">
-        <v>1.1977500000000001</v>
+        <v>0.49581063402940323</v>
       </c>
       <c r="M156">
-        <v>0.22029655255769542</v>
+        <v>0.22030030883736867</v>
       </c>
       <c r="N156">
         <v>4</v>
@@ -21801,10 +21801,10 @@
         <v>804</v>
       </c>
       <c r="L157">
-        <v>6.9779999999999998</v>
+        <v>3.6299606577739012</v>
       </c>
       <c r="M157">
-        <v>0.21775983358021547</v>
+        <v>0.21791087841016241</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -21875,10 +21875,10 @@
         <v>804</v>
       </c>
       <c r="L158">
-        <v>3.8490000000000002</v>
+        <v>2.5608098938482606</v>
       </c>
       <c r="M158">
-        <v>0.21145287347982455</v>
+        <v>0.2112679750647416</v>
       </c>
       <c r="N158">
         <v>1</v>
@@ -21949,10 +21949,10 @@
         <v>804</v>
       </c>
       <c r="L159">
-        <v>4.5255000000000001</v>
+        <v>1.7726081831160889</v>
       </c>
       <c r="M159">
-        <v>0.21114782862539799</v>
+        <v>0.2111892141926173</v>
       </c>
       <c r="N159">
         <v>5</v>
@@ -22023,10 +22023,10 @@
         <v>804</v>
       </c>
       <c r="L160">
-        <v>4.9792500000000004</v>
+        <v>2.2107012297753181</v>
       </c>
       <c r="M160">
-        <v>0.21022274911723923</v>
+        <v>0.21021035171539998</v>
       </c>
       <c r="N160">
         <v>4</v>
@@ -22097,10 +22097,10 @@
         <v>804</v>
       </c>
       <c r="L161">
-        <v>4.9417499999999999</v>
+        <v>2.6893495542589045</v>
       </c>
       <c r="M161">
-        <v>0.20899073964524006</v>
+        <v>0.20916274803051785</v>
       </c>
       <c r="N161">
         <v>2</v>
@@ -22171,10 +22171,10 @@
         <v>804</v>
       </c>
       <c r="L162">
-        <v>3.0375000000000001</v>
+        <v>1.4646146869429781</v>
       </c>
       <c r="M162">
-        <v>0.2074045993526146</v>
+        <v>0.20753581990897332</v>
       </c>
       <c r="N162">
         <v>3</v>
@@ -22245,10 +22245,10 @@
         <v>804</v>
       </c>
       <c r="L163">
-        <v>4.6657500000000001</v>
+        <v>2.2507071499037417</v>
       </c>
       <c r="M163">
-        <v>0.20110330837846496</v>
+        <v>0.20109697447370189</v>
       </c>
       <c r="N163">
         <v>3</v>
@@ -22319,10 +22319,10 @@
         <v>804</v>
       </c>
       <c r="L164">
-        <v>6.8324999999999996</v>
+        <v>4.3924746781664341</v>
       </c>
       <c r="M164">
-        <v>0.20084769253816256</v>
+        <v>0.20059251908592146</v>
       </c>
       <c r="N164">
         <v>1</v>
@@ -22393,10 +22393,10 @@
         <v>804</v>
       </c>
       <c r="L165">
-        <v>8.7810000000000006</v>
+        <v>3.3752403267192528</v>
       </c>
       <c r="M165">
-        <v>0.20055490351476912</v>
+        <v>0.2005616561102444</v>
       </c>
       <c r="N165">
         <v>5</v>
@@ -22467,10 +22467,10 @@
         <v>804</v>
       </c>
       <c r="L166">
-        <v>9.5325000000000006</v>
+        <v>5.0373271607425112</v>
       </c>
       <c r="M166">
-        <v>0.19984892771826626</v>
+        <v>0.19972309512474795</v>
       </c>
       <c r="N166">
         <v>2</v>
@@ -22541,10 +22541,10 @@
         <v>804</v>
       </c>
       <c r="L167">
-        <v>7.5914999999999999</v>
+        <v>3.3561473262517927</v>
       </c>
       <c r="M167">
-        <v>0.19875468668752239</v>
+        <v>0.19883907779730217</v>
       </c>
       <c r="N167">
         <v>4</v>
@@ -22615,10 +22615,10 @@
         <v>804</v>
       </c>
       <c r="L168">
-        <v>9.2272499999999997</v>
+        <v>3.6668840500697204</v>
       </c>
       <c r="M168">
-        <v>0.19180102103899666</v>
+        <v>0.19183077219587086</v>
       </c>
       <c r="N168">
         <v>5</v>
@@ -22689,10 +22689,10 @@
         <v>804</v>
       </c>
       <c r="L169">
-        <v>12.27375</v>
+        <v>5.9755337472809327</v>
       </c>
       <c r="M169">
-        <v>0.19075830254303869</v>
+        <v>0.19085450335703938</v>
       </c>
       <c r="N169">
         <v>2</v>
@@ -22763,10 +22763,10 @@
         <v>804</v>
       </c>
       <c r="L170">
-        <v>9.9779999999999998</v>
+        <v>5.264045651819754</v>
       </c>
       <c r="M170">
-        <v>0.19070425173416936</v>
+        <v>0.19079542060577917</v>
       </c>
       <c r="N170">
         <v>4</v>
@@ -22837,10 +22837,10 @@
         <v>804</v>
       </c>
       <c r="L171">
-        <v>3.4140000000000001</v>
+        <v>2.1579768059685258</v>
       </c>
       <c r="M171">
-        <v>0.18979548207883565</v>
+        <v>0.18964556296488425</v>
       </c>
       <c r="N171">
         <v>1</v>
@@ -22911,10 +22911,10 @@
         <v>804</v>
       </c>
       <c r="L172">
-        <v>4.6710000000000003</v>
+        <v>2.354440792829037</v>
       </c>
       <c r="M172">
-        <v>0.18950327824317043</v>
+        <v>0.18944697471714339</v>
       </c>
       <c r="N172">
         <v>3</v>
@@ -22985,10 +22985,10 @@
         <v>804</v>
       </c>
       <c r="L173">
-        <v>6.8992500000000003</v>
+        <v>3.2441835661942187</v>
       </c>
       <c r="M173">
-        <v>0.18145695227634848</v>
+        <v>0.18141403538239878</v>
       </c>
       <c r="N173">
         <v>3</v>
@@ -23059,10 +23059,10 @@
         <v>804</v>
       </c>
       <c r="L174">
-        <v>4.218</v>
+        <v>2.3264998358534439</v>
       </c>
       <c r="M174">
-        <v>0.1808170965499869</v>
+        <v>0.18083028443639262</v>
       </c>
       <c r="N174">
         <v>2</v>
@@ -23133,13 +23133,13 @@
         <v>804</v>
       </c>
       <c r="L175">
-        <v>12.671250000000001</v>
+        <v>4.4736297558902312</v>
       </c>
       <c r="M175">
-        <v>0.17982022086607727</v>
+        <v>0.17974427699428858</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P175" t="s">
         <v>182</v>
@@ -23207,13 +23207,13 @@
         <v>804</v>
       </c>
       <c r="L176">
-        <v>10.506</v>
+        <v>7.2543596276102171</v>
       </c>
       <c r="M176">
-        <v>0.17973191394598587</v>
+        <v>0.17967800075243232</v>
       </c>
       <c r="N176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P176" t="s">
         <v>182</v>
@@ -23281,10 +23281,10 @@
         <v>804</v>
       </c>
       <c r="L177">
-        <v>8.8777500000000007</v>
+        <v>3.4598015064326955</v>
       </c>
       <c r="M177">
-        <v>0.1791354671886651</v>
+        <v>0.17900967876002397</v>
       </c>
       <c r="N177">
         <v>5</v>
@@ -23355,10 +23355,10 @@
         <v>804</v>
       </c>
       <c r="L178">
-        <v>1.1527499999999999</v>
+        <v>0.52998544898918021</v>
       </c>
       <c r="M178">
-        <v>0.17057059504062105</v>
+        <v>0.170591986262944</v>
       </c>
       <c r="N178">
         <v>3</v>
@@ -23429,10 +23429,10 @@
         <v>804</v>
       </c>
       <c r="L179">
-        <v>8.0939999999999994</v>
+        <v>3.9827053694545995</v>
       </c>
       <c r="M179">
-        <v>0.16946029732729992</v>
+        <v>0.16943011912130423</v>
       </c>
       <c r="N179">
         <v>1</v>
@@ -23503,10 +23503,10 @@
         <v>804</v>
       </c>
       <c r="L180">
-        <v>8.99925</v>
+        <v>4.3245977669154092</v>
       </c>
       <c r="M180">
-        <v>0.16929169976737052</v>
+        <v>0.16902136397396184</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -23577,10 +23577,10 @@
         <v>804</v>
       </c>
       <c r="L181">
-        <v>6.0262500000000001</v>
+        <v>3.182237767624652</v>
       </c>
       <c r="M181">
-        <v>0.16884905820813251</v>
+        <v>0.16877918571088454</v>
       </c>
       <c r="N181">
         <v>2</v>
@@ -23651,10 +23651,10 @@
         <v>804</v>
       </c>
       <c r="L182">
-        <v>6.3817500000000003</v>
+        <v>2.5689003198961768</v>
       </c>
       <c r="M182">
-        <v>0.16664180521022545</v>
+        <v>0.1665764752137722</v>
       </c>
       <c r="N182">
         <v>5</v>
@@ -23725,10 +23725,10 @@
         <v>804</v>
       </c>
       <c r="L183">
-        <v>9.9727499999999996</v>
+        <v>5.4344414586166305</v>
       </c>
       <c r="M183">
-        <v>0.1606635000190734</v>
+        <v>0.16087770748992311</v>
       </c>
       <c r="N183">
         <v>2</v>
@@ -23799,10 +23799,10 @@
         <v>804</v>
       </c>
       <c r="L184">
-        <v>8.2582500000000003</v>
+        <v>3.3808318447669268</v>
       </c>
       <c r="M184">
-        <v>0.16046227296844265</v>
+        <v>0.160589256217813</v>
       </c>
       <c r="N184">
         <v>5</v>
@@ -23873,13 +23873,13 @@
         <v>804</v>
       </c>
       <c r="L185">
-        <v>11.259</v>
+        <v>8.8013501002862071</v>
       </c>
       <c r="M185">
-        <v>0.16019704042513999</v>
+        <v>0.16029247229409299</v>
       </c>
       <c r="N185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P185" t="s">
         <v>182</v>
@@ -23947,13 +23947,13 @@
         <v>804</v>
       </c>
       <c r="L186">
-        <v>13.108499999999999</v>
+        <v>6.2230663602342684</v>
       </c>
       <c r="M186">
-        <v>0.16009631613363998</v>
+        <v>0.15990326224395754</v>
       </c>
       <c r="N186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P186" t="s">
         <v>182</v>
@@ -24021,10 +24021,10 @@
         <v>804</v>
       </c>
       <c r="L187">
-        <v>6.5722500000000004</v>
+        <v>3.5185550276992186</v>
       </c>
       <c r="M187">
-        <v>0.15784905955401335</v>
+        <v>0.15760365624400369</v>
       </c>
       <c r="N187">
         <v>4</v>
@@ -24095,10 +24095,10 @@
         <v>804</v>
       </c>
       <c r="L188">
-        <v>9.1530000000000005</v>
+        <v>4.6766545166679236</v>
       </c>
       <c r="M188">
-        <v>0.1527886338525076</v>
+        <v>0.15275634025212034</v>
       </c>
       <c r="N188">
         <v>2</v>
@@ -24169,10 +24169,10 @@
         <v>804</v>
       </c>
       <c r="L189">
-        <v>4.2262500000000003</v>
+        <v>2.1557796047944637</v>
       </c>
       <c r="M189">
-        <v>0.15243482387548507</v>
+        <v>0.15268745059158501</v>
       </c>
       <c r="N189">
         <v>3</v>
@@ -24243,10 +24243,10 @@
         <v>804</v>
       </c>
       <c r="L190">
-        <v>1.611</v>
+        <v>0.66243867433103065</v>
       </c>
       <c r="M190">
-        <v>0.15149391344047933</v>
+        <v>0.15149259435957305</v>
       </c>
       <c r="N190">
         <v>4</v>
@@ -24317,10 +24317,10 @@
         <v>804</v>
       </c>
       <c r="L191">
-        <v>6.0412499999999998</v>
+        <v>2.2463448845797349</v>
       </c>
       <c r="M191">
-        <v>0.14958304430800939</v>
+        <v>0.14962264220041899</v>
       </c>
       <c r="N191">
         <v>5</v>
@@ -24391,10 +24391,10 @@
         <v>804</v>
       </c>
       <c r="L192">
-        <v>8.4397500000000001</v>
+        <v>4.4779652217641122</v>
       </c>
       <c r="M192">
-        <v>0.1490508966991668</v>
+        <v>0.14910525633042043</v>
       </c>
       <c r="N192">
         <v>1</v>
@@ -24465,10 +24465,10 @@
         <v>804</v>
       </c>
       <c r="L193">
-        <v>8.1457499999999996</v>
+        <v>3.5677077875551606</v>
       </c>
       <c r="M193">
-        <v>0.14037627291260041</v>
+        <v>0.14023717339143832</v>
       </c>
       <c r="N193">
         <v>4</v>
@@ -24539,10 +24539,10 @@
         <v>804</v>
       </c>
       <c r="L194">
-        <v>8.0212500000000002</v>
+        <v>2.8927611242711664</v>
       </c>
       <c r="M194">
-        <v>0.13932490895174879</v>
+        <v>0.13931962379662036</v>
       </c>
       <c r="N194">
         <v>5</v>
@@ -24613,10 +24613,10 @@
         <v>804</v>
       </c>
       <c r="L195">
-        <v>10.08075</v>
+        <v>6.5424583704960728</v>
       </c>
       <c r="M195">
-        <v>0.13871415878303622</v>
+        <v>0.13856700866812632</v>
       </c>
       <c r="N195">
         <v>1</v>
@@ -24687,10 +24687,10 @@
         <v>804</v>
       </c>
       <c r="L196">
-        <v>13.468500000000001</v>
+        <v>6.4203801556278055</v>
       </c>
       <c r="M196">
-        <v>0.13842702323118133</v>
+        <v>0.13843064211651249</v>
       </c>
       <c r="N196">
         <v>2</v>
@@ -24761,10 +24761,10 @@
         <v>804</v>
       </c>
       <c r="L197">
-        <v>9.5820000000000007</v>
+        <v>4.0303121883543458</v>
       </c>
       <c r="M197">
-        <v>0.13789483126612326</v>
+        <v>0.13797856497490249</v>
       </c>
       <c r="N197">
         <v>3</v>
@@ -24835,10 +24835,10 @@
         <v>804</v>
       </c>
       <c r="L198">
-        <v>13.764749999999999</v>
+        <v>5.9233546731384319</v>
       </c>
       <c r="M198">
-        <v>0.13116778122721659</v>
+        <v>0.13128174871008391</v>
       </c>
       <c r="N198">
         <v>3</v>
@@ -24909,10 +24909,10 @@
         <v>804</v>
       </c>
       <c r="L199">
-        <v>24.93</v>
+        <v>14.249013385460204</v>
       </c>
       <c r="M199">
-        <v>0.13019902861937552</v>
+        <v>0.13036824781075027</v>
       </c>
       <c r="N199">
         <v>1</v>
@@ -24983,10 +24983,10 @@
         <v>804</v>
       </c>
       <c r="L200">
-        <v>10.523250000000001</v>
+        <v>3.85243446061838</v>
       </c>
       <c r="M200">
-        <v>0.12890646407694312</v>
+        <v>0.12900919416815351</v>
       </c>
       <c r="N200">
         <v>5</v>
@@ -25057,10 +25057,10 @@
         <v>804</v>
       </c>
       <c r="L201">
-        <v>19.30275</v>
+        <v>7.6025418044793396</v>
       </c>
       <c r="M201">
-        <v>0.12852967078791419</v>
+        <v>0.12850694566693649</v>
       </c>
       <c r="N201">
         <v>4</v>
@@ -25131,10 +25131,10 @@
         <v>804</v>
       </c>
       <c r="L202">
-        <v>13.13325</v>
+        <v>5.952874155779682</v>
       </c>
       <c r="M202">
-        <v>0.12761903454669157</v>
+        <v>0.12767290980412935</v>
       </c>
       <c r="N202">
         <v>2</v>
@@ -25205,10 +25205,10 @@
         <v>804</v>
       </c>
       <c r="L203">
-        <v>10.0275</v>
+        <v>3.9927518380426199</v>
       </c>
       <c r="M203">
-        <v>0.123825187547218</v>
+        <v>0.12381978841183013</v>
       </c>
       <c r="N203">
         <v>3</v>
@@ -25279,10 +25279,10 @@
         <v>804</v>
       </c>
       <c r="L204">
-        <v>12.984</v>
+        <v>7.527415993642907</v>
       </c>
       <c r="M204">
-        <v>0.12180621050577801</v>
+        <v>0.1216728534546056</v>
       </c>
       <c r="N204">
         <v>1</v>
@@ -25353,10 +25353,10 @@
         <v>804</v>
       </c>
       <c r="L205">
-        <v>8.3714999999999993</v>
+        <v>3.11445609629406</v>
       </c>
       <c r="M205">
-        <v>0.11960878593001285</v>
+        <v>0.11979202572636916</v>
       </c>
       <c r="N205">
         <v>5</v>
@@ -25427,10 +25427,10 @@
         <v>804</v>
       </c>
       <c r="L206">
-        <v>18.349499999999999</v>
+        <v>7.0004822438374905</v>
       </c>
       <c r="M206">
-        <v>0.11911206801746535</v>
+        <v>0.11899338382333939</v>
       </c>
       <c r="N206">
         <v>4</v>
@@ -25501,10 +25501,10 @@
         <v>804</v>
       </c>
       <c r="L207">
-        <v>11.780250000000001</v>
+        <v>5.1421142304303542</v>
       </c>
       <c r="M207">
-        <v>0.11901337788432378</v>
+        <v>0.11888943050617436</v>
       </c>
       <c r="N207">
         <v>2</v>
@@ -25575,10 +25575,10 @@
         <v>804</v>
       </c>
       <c r="L208">
-        <v>15.2295</v>
+        <v>5.978431307057881</v>
       </c>
       <c r="M208">
-        <v>0.1113856984224413</v>
+        <v>0.11131808139324033</v>
       </c>
       <c r="N208">
         <v>3</v>
@@ -25649,10 +25649,10 @@
         <v>804</v>
       </c>
       <c r="L209">
-        <v>12.666</v>
+        <v>4.8901982443564593</v>
       </c>
       <c r="M209">
-        <v>0.10982828905044753</v>
+        <v>0.10983946367693945</v>
       </c>
       <c r="N209">
         <v>4</v>
@@ -25723,10 +25723,10 @@
         <v>804</v>
       </c>
       <c r="L210">
-        <v>15.88575</v>
+        <v>5.8512101728553558</v>
       </c>
       <c r="M210">
-        <v>0.10980113080587695</v>
+        <v>0.1097855895104982</v>
       </c>
       <c r="N210">
         <v>5</v>
@@ -25797,10 +25797,10 @@
         <v>804</v>
       </c>
       <c r="L211">
-        <v>7.8247499999999999</v>
+        <v>3.7903440422943286</v>
       </c>
       <c r="M211">
-        <v>0.10968623702665802</v>
+        <v>0.10969834947193478</v>
       </c>
       <c r="N211">
         <v>2</v>
@@ -25871,10 +25871,10 @@
         <v>804</v>
       </c>
       <c r="L212">
-        <v>22.438500000000001</v>
+        <v>11.657319004582414</v>
       </c>
       <c r="M212">
-        <v>0.10927702270856469</v>
+        <v>0.10939811505206334</v>
       </c>
       <c r="N212">
         <v>1</v>
@@ -25945,10 +25945,10 @@
         <v>804</v>
       </c>
       <c r="L213">
-        <v>12.04275</v>
+        <v>5.2896760368524305</v>
       </c>
       <c r="M213">
-        <v>0.10030774956097119</v>
+        <v>0.10028077935914192</v>
       </c>
       <c r="N213">
         <v>2</v>
@@ -26019,10 +26019,10 @@
         <v>804</v>
       </c>
       <c r="L214">
-        <v>16.23</v>
+        <v>10.462251591165714</v>
       </c>
       <c r="M214">
-        <v>0.10002741166035592</v>
+        <v>0.10001560941696086</v>
       </c>
       <c r="N214">
         <v>1</v>
@@ -26093,10 +26093,10 @@
         <v>804</v>
       </c>
       <c r="L215">
-        <v>12.51225</v>
+        <v>5.1887894447067051</v>
       </c>
       <c r="M215">
-        <v>9.9869240941063558E-2</v>
+        <v>9.9728977006802083E-2</v>
       </c>
       <c r="N215">
         <v>3</v>
@@ -26167,10 +26167,10 @@
         <v>804</v>
       </c>
       <c r="L216">
-        <v>7.2720000000000002</v>
+        <v>2.7429633548309114</v>
       </c>
       <c r="M216">
-        <v>9.9476042988471319E-2</v>
+        <v>9.9442527168788333E-2</v>
       </c>
       <c r="N216">
         <v>4</v>
@@ -26241,10 +26241,10 @@
         <v>804</v>
       </c>
       <c r="L217">
-        <v>15.542249999999999</v>
+        <v>5.5988785936592134</v>
       </c>
       <c r="M217">
-        <v>9.8481155770883899E-2</v>
+        <v>9.8371914071425204E-2</v>
       </c>
       <c r="N217">
         <v>5</v>
@@ -26315,10 +26315,10 @@
         <v>804</v>
       </c>
       <c r="L218">
-        <v>10.68</v>
+        <v>7.6577528477362726</v>
       </c>
       <c r="M218">
-        <v>9.1345865074638197E-2</v>
+        <v>9.1536394239918953E-2</v>
       </c>
       <c r="N218">
         <v>1</v>
@@ -26389,10 +26389,10 @@
         <v>804</v>
       </c>
       <c r="L219">
-        <v>17.8215</v>
+        <v>6.479317480163858</v>
       </c>
       <c r="M219">
-        <v>9.0194822464312999E-2</v>
+        <v>9.0182634000541675E-2</v>
       </c>
       <c r="N219">
         <v>5</v>
@@ -26463,10 +26463,10 @@
         <v>804</v>
       </c>
       <c r="L220">
-        <v>18.903749999999999</v>
+        <v>9.3930770057563322</v>
       </c>
       <c r="M220">
-        <v>8.9934512796258928E-2</v>
+        <v>9.0082985671158355E-2</v>
       </c>
       <c r="N220">
         <v>2</v>
@@ -26537,10 +26537,10 @@
         <v>804</v>
       </c>
       <c r="L221">
-        <v>16.170750000000002</v>
+        <v>6.4520740730066866</v>
       </c>
       <c r="M221">
-        <v>8.9829685454894601E-2</v>
+        <v>8.9755458817273537E-2</v>
       </c>
       <c r="N221">
         <v>3</v>
@@ -26611,10 +26611,10 @@
         <v>804</v>
       </c>
       <c r="L222">
-        <v>10.827</v>
+        <v>4.0997703044912086</v>
       </c>
       <c r="M222">
-        <v>8.9582601434664441E-2</v>
+        <v>8.9617613677312802E-2</v>
       </c>
       <c r="N222">
         <v>4</v>
@@ -26685,10 +26685,10 @@
         <v>804</v>
       </c>
       <c r="L223">
-        <v>6.9787499999999998</v>
+        <v>2.4878657275200533</v>
       </c>
       <c r="M223">
-        <v>8.0675287774143206E-2</v>
+        <v>8.0656606949139759E-2</v>
       </c>
       <c r="N223">
         <v>5</v>
@@ -26759,13 +26759,13 @@
         <v>804</v>
       </c>
       <c r="L224">
-        <v>7.73325</v>
+        <v>2.640729439571841</v>
       </c>
       <c r="M224">
-        <v>8.0168168321020833E-2</v>
+        <v>8.0191391966440831E-2</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P224" t="s">
         <v>182</v>
@@ -26833,13 +26833,13 @@
         <v>804</v>
       </c>
       <c r="L225">
-        <v>7.218</v>
+        <v>3.3209338733188285</v>
       </c>
       <c r="M225">
-        <v>8.0159114650534408E-2</v>
+        <v>8.0162479030838299E-2</v>
       </c>
       <c r="N225">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P225" t="s">
         <v>182</v>
@@ -26907,10 +26907,10 @@
         <v>804</v>
       </c>
       <c r="L226">
-        <v>15.353999999999999</v>
+        <v>9.9109903165623674</v>
       </c>
       <c r="M226">
-        <v>7.9499277862507864E-2</v>
+        <v>7.9472908278644089E-2</v>
       </c>
       <c r="N226">
         <v>1</v>
@@ -26981,10 +26981,10 @@
         <v>804</v>
       </c>
       <c r="L227">
-        <v>7.8105000000000002</v>
+        <v>3.302652567304377</v>
       </c>
       <c r="M227">
-        <v>7.9491947444735658E-2</v>
+        <v>7.9393992305004477E-2</v>
       </c>
       <c r="N227">
         <v>3</v>
@@ -27055,10 +27055,10 @@
         <v>804</v>
       </c>
       <c r="L228">
-        <v>11.9415</v>
+        <v>6.8287210909871909</v>
       </c>
       <c r="M228">
-        <v>7.1282028345448292E-2</v>
+        <v>7.1214313204814597E-2</v>
       </c>
       <c r="N228">
         <v>1</v>
@@ -27093,10 +27093,10 @@
         <v>804</v>
       </c>
       <c r="L229">
-        <v>9.1769999999999996</v>
+        <v>3.6501415076229056</v>
       </c>
       <c r="M229">
-        <v>7.036940273086098E-2</v>
+        <v>7.0362333247054057E-2</v>
       </c>
       <c r="N229">
         <v>3</v>
@@ -27131,10 +27131,10 @@
         <v>804</v>
       </c>
       <c r="L230">
-        <v>8.9452499999999997</v>
+        <v>3.8036034351178301</v>
       </c>
       <c r="M230">
-        <v>7.0149457350154917E-2</v>
+        <v>7.02719787604867E-2</v>
       </c>
       <c r="N230">
         <v>2</v>
@@ -27169,10 +27169,10 @@
         <v>804</v>
       </c>
       <c r="L231">
-        <v>4.5030000000000001</v>
+        <v>1.6947667924118182</v>
       </c>
       <c r="M231">
-        <v>6.9807894782212193E-2</v>
+        <v>6.9840481093379536E-2</v>
       </c>
       <c r="N231">
         <v>4</v>
@@ -27207,10 +27207,10 @@
         <v>804</v>
       </c>
       <c r="L232">
-        <v>4.056</v>
+        <v>1.4139025089901296</v>
       </c>
       <c r="M232">
-        <v>6.8999728763299351E-2</v>
+        <v>6.8972437593252486E-2</v>
       </c>
       <c r="N232">
         <v>5</v>
@@ -27245,10 +27245,10 @@
         <v>804</v>
       </c>
       <c r="L233">
-        <v>16.7895</v>
+        <v>12.09280715487111</v>
       </c>
       <c r="M233">
-        <v>6.1539261170959925E-2</v>
+        <v>6.1523305747516993E-2</v>
       </c>
       <c r="N233">
         <v>1</v>
@@ -27283,10 +27283,10 @@
         <v>804</v>
       </c>
       <c r="L234">
-        <v>5.3144999999999998</v>
+        <v>2.1621840072548633</v>
       </c>
       <c r="M234">
-        <v>6.1151713529283572E-2</v>
+        <v>6.1218908735780876E-2</v>
       </c>
       <c r="N234">
         <v>3</v>
@@ -27321,10 +27321,10 @@
         <v>804</v>
       </c>
       <c r="L235">
-        <v>3.6427499999999999</v>
+        <v>1.3677394962644556</v>
       </c>
       <c r="M235">
-        <v>5.961824604669623E-2</v>
+        <v>5.9632046392593188E-2</v>
       </c>
       <c r="N235">
         <v>4</v>
@@ -27359,10 +27359,10 @@
         <v>804</v>
       </c>
       <c r="L236">
-        <v>3.66</v>
+        <v>1.6147135552380198</v>
       </c>
       <c r="M236">
-        <v>5.8929603690643463E-2</v>
+        <v>5.8815482747498211E-2</v>
       </c>
       <c r="N236">
         <v>2</v>
@@ -27397,10 +27397,10 @@
         <v>804</v>
       </c>
       <c r="L237">
-        <v>1.69875</v>
+        <v>0.60859508528960726</v>
       </c>
       <c r="M237">
-        <v>5.7200311624448615E-2</v>
+        <v>5.7211180345830406E-2</v>
       </c>
       <c r="N237">
         <v>5</v>
@@ -27435,10 +27435,10 @@
         <v>804</v>
       </c>
       <c r="L238">
-        <v>3.1964999999999999</v>
+        <v>1.2210230540075988</v>
       </c>
       <c r="M238">
-        <v>5.2747858769926576E-2</v>
+        <v>5.2734485644046356E-2</v>
       </c>
       <c r="N238">
         <v>4</v>
@@ -27473,10 +27473,10 @@
         <v>804</v>
       </c>
       <c r="L239">
-        <v>1.3087500000000001</v>
+        <v>0.4801289422050885</v>
       </c>
       <c r="M239">
-        <v>5.2041027767300907E-2</v>
+        <v>5.2036212396566403E-2</v>
       </c>
       <c r="N239">
         <v>5</v>
@@ -27511,13 +27511,13 @@
         <v>804</v>
       </c>
       <c r="L240">
-        <v>2.802</v>
+        <v>1.0537794971813335</v>
       </c>
       <c r="M240">
-        <v>5.1658210252926509E-2</v>
+        <v>5.164255694619397E-2</v>
       </c>
       <c r="N240">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="2:14">
@@ -27549,13 +27549,13 @@
         <v>804</v>
       </c>
       <c r="L241">
-        <v>2.3519999999999999</v>
+        <v>1.1004528264419036</v>
       </c>
       <c r="M241">
-        <v>5.1424859541942231E-2</v>
+        <v>5.163391488647421E-2</v>
       </c>
       <c r="N241">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="2:14">
@@ -27587,10 +27587,10 @@
         <v>804</v>
       </c>
       <c r="L242">
-        <v>7.0739999999999998</v>
+        <v>3.8005945949856952</v>
       </c>
       <c r="M242">
-        <v>4.8791186695149431E-2</v>
+        <v>4.8999503694397241E-2</v>
       </c>
       <c r="N242">
         <v>1</v>
@@ -27625,10 +27625,10 @@
         <v>804</v>
       </c>
       <c r="L243">
-        <v>0.86324999999999996</v>
+        <v>0.35914497783777927</v>
       </c>
       <c r="M243">
-        <v>4.2067511933710486E-2</v>
+        <v>4.2158669983938947E-2</v>
       </c>
       <c r="N243">
         <v>3</v>
@@ -27663,13 +27663,13 @@
         <v>804</v>
       </c>
       <c r="L244">
-        <v>5.5155000000000003</v>
+        <v>1.0079503920613258</v>
       </c>
       <c r="M244">
-        <v>4.1900321591963031E-2</v>
+        <v>4.1978100003140388E-2</v>
       </c>
       <c r="N244">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="2:14">
@@ -27701,13 +27701,13 @@
         <v>804</v>
       </c>
       <c r="L245">
-        <v>1.95225</v>
+        <v>3.4314955393325182</v>
       </c>
       <c r="M245">
-        <v>4.181861939414732E-2</v>
+        <v>4.1841454705057415E-2</v>
       </c>
       <c r="N245">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="2:14">
@@ -27739,10 +27739,10 @@
         <v>804</v>
       </c>
       <c r="L246">
-        <v>0.37425000000000003</v>
+        <v>0.14292154521625147</v>
       </c>
       <c r="M246">
-        <v>4.1773481236588965E-2</v>
+        <v>4.1786714515965953E-2</v>
       </c>
       <c r="N246">
         <v>4</v>
@@ -27777,10 +27777,10 @@
         <v>804</v>
       </c>
       <c r="L247">
-        <v>0.95325000000000004</v>
+        <v>0.35719261680347841</v>
       </c>
       <c r="M247">
-        <v>4.1309704577969397E-2</v>
+        <v>4.1316474580726383E-2</v>
       </c>
       <c r="N247">
         <v>5</v>
@@ -27815,10 +27815,10 @@
         <v>804</v>
       </c>
       <c r="L248">
-        <v>1.0822499999999999</v>
+        <v>0.50888877175615899</v>
       </c>
       <c r="M248">
-        <v>3.2860871878572027E-2</v>
+        <v>3.288662963608581E-2</v>
       </c>
       <c r="N248">
         <v>2</v>
@@ -27853,10 +27853,10 @@
         <v>804</v>
       </c>
       <c r="L249">
-        <v>3.8835000000000002</v>
+        <v>2.3990027007409775</v>
       </c>
       <c r="M249">
-        <v>3.2478883984713609E-2</v>
+        <v>3.2484912917136316E-2</v>
       </c>
       <c r="N249">
         <v>1</v>
@@ -27891,10 +27891,10 @@
         <v>804</v>
       </c>
       <c r="L250">
-        <v>0.33224999999999999</v>
+        <v>0.12737255485168475</v>
       </c>
       <c r="M250">
-        <v>3.1976291306059161E-2</v>
+        <v>3.1909585649099778E-2</v>
       </c>
       <c r="N250">
         <v>5</v>
@@ -27929,10 +27929,10 @@
         <v>804</v>
       </c>
       <c r="L251">
-        <v>0.92100000000000004</v>
+        <v>0.43323922701901374</v>
       </c>
       <c r="M251">
-        <v>3.0871527560902026E-2</v>
+        <v>3.0800234530574681E-2</v>
       </c>
       <c r="N251">
         <v>3</v>
@@ -27967,10 +27967,10 @@
         <v>804</v>
       </c>
       <c r="L252">
-        <v>0.19425000000000001</v>
+        <v>7.8224804821307642E-2</v>
       </c>
       <c r="M252">
-        <v>2.9123069479944474E-2</v>
+        <v>2.9091970103256336E-2</v>
       </c>
       <c r="N252">
         <v>4</v>
@@ -28005,10 +28005,10 @@
         <v>804</v>
       </c>
       <c r="L253">
-        <v>3.0000000000000001E-3</v>
+        <v>1.5857345747198989E-3</v>
       </c>
       <c r="M253">
-        <v>2.2802615221252976E-2</v>
+        <v>2.2286652457043841E-2</v>
       </c>
       <c r="N253">
         <v>4</v>
@@ -28043,10 +28043,10 @@
         <v>804</v>
       </c>
       <c r="L254">
-        <v>8.9999999999999993E-3</v>
+        <v>4.9459464853883386E-3</v>
       </c>
       <c r="M254">
-        <v>2.1518510234626951E-2</v>
+        <v>2.202838857299488E-2</v>
       </c>
       <c r="N254">
         <v>2</v>
@@ -28081,10 +28081,10 @@
         <v>804</v>
       </c>
       <c r="L255">
-        <v>1.7999999999999999E-2</v>
+        <v>7.2477663824677963E-3</v>
       </c>
       <c r="M255">
-        <v>2.1366080234748959E-2</v>
+        <v>2.1406250975097709E-2</v>
       </c>
       <c r="N255">
         <v>5</v>
@@ -28119,10 +28119,10 @@
         <v>804</v>
       </c>
       <c r="L256">
-        <v>0.2235</v>
+        <v>0.10426228215424471</v>
       </c>
       <c r="M256">
-        <v>1.6728222772742933E-2</v>
+        <v>1.6577694738215916E-2</v>
       </c>
       <c r="N256">
         <v>1</v>
@@ -28157,10 +28157,10 @@
         <v>804</v>
       </c>
       <c r="L257">
-        <v>7.3499999999999996E-2</v>
+        <v>3.9788664266046707E-2</v>
       </c>
       <c r="M257">
-        <v>1.5205402901102715E-2</v>
+        <v>1.5249256763568631E-2</v>
       </c>
       <c r="N257">
         <v>3</v>
@@ -28195,7 +28195,7 @@
         <v>804</v>
       </c>
       <c r="L258">
-        <v>6.6000000000000003E-2</v>
+        <v>3.1871588871920854E-2</v>
       </c>
       <c r="M258">
         <v>1.3361792258399801E-2</v>
@@ -28233,7 +28233,7 @@
         <v>804</v>
       </c>
       <c r="L259">
-        <v>3.2250000000000001E-2</v>
+        <v>1.3574930671103715E-2</v>
       </c>
       <c r="M259">
         <v>1.27006245350076E-2</v>
@@ -28309,7 +28309,7 @@
         <v>804</v>
       </c>
       <c r="L261">
-        <v>5.2500000000000003E-3</v>
+        <v>2.3278139783986435E-3</v>
       </c>
       <c r="M261">
         <v>6.2275441055722998E-3</v>
@@ -28347,7 +28347,7 @@
         <v>804</v>
       </c>
       <c r="L262">
-        <v>0.20324999999999999</v>
+        <v>9.164306591800632E-2</v>
       </c>
       <c r="M262">
         <v>6.2058254411223E-3</v>
@@ -28385,7 +28385,7 @@
         <v>804</v>
       </c>
       <c r="L263">
-        <v>8.9999999999999993E-3</v>
+        <v>5.7117319320852357E-3</v>
       </c>
       <c r="M263">
         <v>8.8291217713710015E-4</v>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60A11DD-7DBD-4A61-BBBD-976BC3FD4A9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80FAF24-F9BC-43F0-AB4C-0F2D0C4EFE77}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C2C3176-B459-4A0F-8CC2-E3F347B90B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5173816-9D61-49A4-A0A0-02D429BFB3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BF348C-8707-4031-88A8-91860342D3A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE1E966-A624-4204-9E49-977A1F3812FC}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC627863-8385-4420-B742-E646B908FC34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812A7BAC-F1DB-4E5D-8E29-EB4F0A4905BE}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80FAF24-F9BC-43F0-AB4C-0F2D0C4EFE77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC70E0DC-277E-4B5F-9E32-EA330CAEFE3E}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5173816-9D61-49A4-A0A0-02D429BFB3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E3E41C6-D236-417B-BD35-F45E7649D7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE1E966-A624-4204-9E49-977A1F3812FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A7A860-0975-4DAC-B683-112C7D32E4B0}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8926,7 +8926,7 @@
         <v>1.0929594088366603E-2</v>
       </c>
       <c r="M13">
-        <v>0.24553205567337943</v>
+        <v>0.24553205567337952</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -9078,7 +9078,7 @@
         <v>10.718640937029134</v>
       </c>
       <c r="M17">
-        <v>0.23724219240738095</v>
+        <v>0.23724219240738101</v>
       </c>
       <c r="N17">
         <v>2</v>
@@ -9192,7 +9192,7 @@
         <v>22.681341870782674</v>
       </c>
       <c r="M20">
-        <v>0.23119402616510437</v>
+        <v>0.23119402616510443</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -9230,7 +9230,7 @@
         <v>21.507460017618097</v>
       </c>
       <c r="M21">
-        <v>0.23116147704017584</v>
+        <v>0.23116147704017589</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -9496,7 +9496,7 @@
         <v>46.293561461418811</v>
       </c>
       <c r="M28">
-        <v>0.21861873283353284</v>
+        <v>0.21861873283353286</v>
       </c>
       <c r="N28">
         <v>4</v>
@@ -9648,7 +9648,7 @@
         <v>70.014831327549786</v>
       </c>
       <c r="M32">
-        <v>0.20971598341683259</v>
+        <v>0.20971598341683262</v>
       </c>
       <c r="N32">
         <v>4</v>
@@ -9686,7 +9686,7 @@
         <v>49.059159381090566</v>
       </c>
       <c r="M33">
-        <v>0.20916043769634082</v>
+        <v>0.20916043769634085</v>
       </c>
       <c r="N33">
         <v>2</v>
@@ -9838,7 +9838,7 @@
         <v>130.29343895452624</v>
       </c>
       <c r="M37">
-        <v>0.20023879043138662</v>
+        <v>0.20023879043138665</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -10104,7 +10104,7 @@
         <v>69.710247669542099</v>
       </c>
       <c r="M44">
-        <v>0.18909066036225713</v>
+        <v>0.18909066036225719</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -10446,7 +10446,7 @@
         <v>1.9393772345594256</v>
       </c>
       <c r="M53">
-        <v>0.17126812287478294</v>
+        <v>0.17126812287478296</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -10560,7 +10560,7 @@
         <v>4.725E-2</v>
       </c>
       <c r="M56">
-        <v>0.16204588441264586</v>
+        <v>0.16204588441264589</v>
       </c>
       <c r="N56">
         <v>4</v>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812A7BAC-F1DB-4E5D-8E29-EB4F0A4905BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAC38A3-DCB1-4357-B503-DCC59567B57F}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11000,7 +11000,7 @@
         <v>9.7398474906898388E-2</v>
       </c>
       <c r="M11">
-        <v>0.7191696570031374</v>
+        <v>0.71916965441845659</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -11074,7 +11074,7 @@
         <v>0.43757129990993693</v>
       </c>
       <c r="M12">
-        <v>0.71494200599841473</v>
+        <v>0.71494200286501919</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -11110,7 +11110,7 @@
         <v>0.10575</v>
       </c>
       <c r="AA12">
-        <v>0.62234763541750537</v>
+        <v>0.62234763541750548</v>
       </c>
       <c r="AB12">
         <v>1</v>
@@ -11148,7 +11148,7 @@
         <v>0.17620783693224129</v>
       </c>
       <c r="M13">
-        <v>0.65905157997063557</v>
+        <v>0.65905157622760291</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -11222,7 +11222,7 @@
         <v>1.1570405911633396E-2</v>
       </c>
       <c r="M14">
-        <v>0.63200140032601226</v>
+        <v>0.63200139722302551</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -11296,7 +11296,7 @@
         <v>9.1899232937238826E-2</v>
       </c>
       <c r="M15">
-        <v>0.60031961262251998</v>
+        <v>0.60031960945868879</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -11370,7 +11370,7 @@
         <v>0.24696498099564293</v>
       </c>
       <c r="M16">
-        <v>0.58089980183314383</v>
+        <v>0.58089979809137837</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -11406,7 +11406,7 @@
         <v>2.2124999999999999</v>
       </c>
       <c r="AA16">
-        <v>0.58981917691631036</v>
+        <v>0.58981917691631047</v>
       </c>
       <c r="AB16">
         <v>4</v>
@@ -11444,7 +11444,7 @@
         <v>0.11273825528143006</v>
       </c>
       <c r="M17">
-        <v>0.56457397346434446</v>
+        <v>0.5645739708666484</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -11518,7 +11518,7 @@
         <v>9.8366964416459216E-2</v>
       </c>
       <c r="M18">
-        <v>0.55267182256682024</v>
+        <v>0.55267181944463406</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -11592,7 +11592,7 @@
         <v>0.41373531514830508</v>
       </c>
       <c r="M19">
-        <v>0.53193793087411478</v>
+        <v>0.53193792790913097</v>
       </c>
       <c r="N19">
         <v>2</v>
@@ -11666,7 +11666,7 @@
         <v>7.8685874089490113E-2</v>
       </c>
       <c r="M20">
-        <v>0.52747452162553121</v>
+        <v>0.52747451884857177</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>1.9933514482280167E-3</v>
       </c>
       <c r="M21">
-        <v>0.5201606594153787</v>
+        <v>0.52016065807196155</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>0.10150759468372139</v>
       </c>
       <c r="M22">
-        <v>0.51423128005084473</v>
+        <v>0.51423127757055775</v>
       </c>
       <c r="N22">
         <v>4</v>
@@ -11888,7 +11888,7 @@
         <v>0.27187941592086667</v>
       </c>
       <c r="M23">
-        <v>0.51367633290031955</v>
+        <v>0.5136763300360393</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -11962,7 +11962,7 @@
         <v>4.8150668647845472E-2</v>
       </c>
       <c r="M24">
-        <v>0.51276676736459725</v>
+        <v>0.51276676473245109</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -12036,7 +12036,7 @@
         <v>0.10626089807026223</v>
       </c>
       <c r="M25">
-        <v>0.51082960266199562</v>
+        <v>0.5108295998019472</v>
       </c>
       <c r="N25">
         <v>3</v>
@@ -12072,7 +12072,7 @@
         <v>0.20100000000000001</v>
       </c>
       <c r="AA25">
-        <v>0.55884609519244866</v>
+        <v>0.55884609519244877</v>
       </c>
       <c r="AB25">
         <v>2</v>
@@ -12110,7 +12110,7 @@
         <v>1.4437561073655423</v>
       </c>
       <c r="M26">
-        <v>0.50968993081838243</v>
+        <v>0.50968992842667715</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -12184,7 +12184,7 @@
         <v>3.8487520958083832E-2</v>
       </c>
       <c r="M27">
-        <v>0.4991687459873973</v>
+        <v>0.49916874320809995</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -12258,7 +12258,7 @@
         <v>5.1364672364672362E-2</v>
       </c>
       <c r="M28">
-        <v>0.49763899641751419</v>
+        <v>0.49763899385911758</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -12332,7 +12332,7 @@
         <v>1.1778242912674908</v>
       </c>
       <c r="M29">
-        <v>0.49688520582565188</v>
+        <v>0.49688520586169621</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -12406,7 +12406,7 @@
         <v>2.2315534497444632E-2</v>
       </c>
       <c r="M30">
-        <v>0.49199195783716826</v>
+        <v>0.49199195581589461</v>
       </c>
       <c r="N30">
         <v>4</v>
@@ -12480,7 +12480,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="M31">
-        <v>0.49118898307332043</v>
+        <v>0.49118898163758379</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -12554,7 +12554,7 @@
         <v>5.2061911115952285E-2</v>
       </c>
       <c r="M32">
-        <v>0.48871615741329361</v>
+        <v>0.48871615541581021</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -12628,7 +12628,7 @@
         <v>0.3282007550233651</v>
       </c>
       <c r="M33">
-        <v>0.48558148622467689</v>
+        <v>0.48558148440677584</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -12702,7 +12702,7 @@
         <v>0.15269232685600401</v>
       </c>
       <c r="M34">
-        <v>0.48286546881727732</v>
+        <v>0.48286546718446122</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -12776,7 +12776,7 @@
         <v>1.7168608600240345E-2</v>
       </c>
       <c r="M35">
-        <v>0.47992193265827882</v>
+        <v>0.47992193104097963</v>
       </c>
       <c r="N35">
         <v>3</v>
@@ -12850,7 +12850,7 @@
         <v>4.780380942103276E-2</v>
       </c>
       <c r="M36">
-        <v>0.47901478939388786</v>
+        <v>0.47901478667173081</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -12886,7 +12886,7 @@
         <v>0.216</v>
       </c>
       <c r="AA36">
-        <v>0.5329939779442705</v>
+        <v>0.53299397794427061</v>
       </c>
       <c r="AB36">
         <v>3</v>
@@ -12924,7 +12924,7 @@
         <v>1.5173877380341625</v>
       </c>
       <c r="M37">
-        <v>0.4701360302477815</v>
+        <v>0.47013602646504427</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -12998,7 +12998,7 @@
         <v>7.0740646587455103E-2</v>
       </c>
       <c r="M38">
-        <v>0.46825641609185176</v>
+        <v>0.46825641473795437</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -13072,7 +13072,7 @@
         <v>1.4911879503602883E-2</v>
       </c>
       <c r="M39">
-        <v>0.46224696285045208</v>
+        <v>0.46224696076294192</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -13146,7 +13146,7 @@
         <v>1.8821979944728573</v>
       </c>
       <c r="M40">
-        <v>0.45140716122873509</v>
+        <v>0.45140715755930139</v>
       </c>
       <c r="N40">
         <v>3</v>
@@ -13182,7 +13182,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
       <c r="AA40">
-        <v>0.51985941017803972</v>
+        <v>0.51985941017803983</v>
       </c>
       <c r="AB40">
         <v>4</v>
@@ -13220,7 +13220,7 @@
         <v>3.9815773638218824E-2</v>
       </c>
       <c r="M41">
-        <v>0.44581658447224276</v>
+        <v>0.44581658223654586</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -13294,7 +13294,7 @@
         <v>1.4751660481650422</v>
       </c>
       <c r="M42">
-        <v>0.44578897053974548</v>
+        <v>0.44578896695529402</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -13368,7 +13368,7 @@
         <v>0.18580058405489297</v>
       </c>
       <c r="M43">
-        <v>0.44023779981200739</v>
+        <v>0.44023780227927684</v>
       </c>
       <c r="N43">
         <v>5</v>
@@ -13442,7 +13442,7 @@
         <v>0.12472962181708601</v>
       </c>
       <c r="M44">
-        <v>0.43973222817450658</v>
+        <v>0.4397322261761421</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -13516,7 +13516,7 @@
         <v>0.24684620229248011</v>
       </c>
       <c r="M45">
-        <v>0.43767251031908422</v>
+        <v>0.43767250756670489</v>
       </c>
       <c r="N45">
         <v>4</v>
@@ -13590,7 +13590,7 @@
         <v>0.82329252858282376</v>
       </c>
       <c r="M46">
-        <v>0.43730618239424862</v>
+        <v>0.43730618037069929</v>
       </c>
       <c r="N46">
         <v>2</v>
@@ -13664,7 +13664,7 @@
         <v>1.8322330425769342</v>
       </c>
       <c r="M47">
-        <v>0.43559116617442661</v>
+        <v>0.43559116182109692</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -13738,7 +13738,7 @@
         <v>1.6333334672098223</v>
       </c>
       <c r="M48">
-        <v>0.43351725225935689</v>
+        <v>0.43351724916345191</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -13812,7 +13812,7 @@
         <v>8.6840847538633102E-3</v>
       </c>
       <c r="M49">
-        <v>0.43251741216306838</v>
+        <v>0.43251741067616722</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -13848,7 +13848,7 @@
         <v>3.444</v>
       </c>
       <c r="AA49">
-        <v>0.49745508487024787</v>
+        <v>0.49745508487024798</v>
       </c>
       <c r="AB49">
         <v>3</v>
@@ -13886,7 +13886,7 @@
         <v>1.204412539046676</v>
       </c>
       <c r="M50">
-        <v>0.42745275386001841</v>
+        <v>0.42745274933005312</v>
       </c>
       <c r="N50">
         <v>3</v>
@@ -13960,7 +13960,7 @@
         <v>0.32094470591435881</v>
       </c>
       <c r="M51">
-        <v>0.42681353019096768</v>
+        <v>0.42681352813171775</v>
       </c>
       <c r="N51">
         <v>2</v>
@@ -14034,7 +14034,7 @@
         <v>2.0705126313131279</v>
       </c>
       <c r="M52">
-        <v>0.42627854825613187</v>
+        <v>0.4262785520574397</v>
       </c>
       <c r="N52">
         <v>4</v>
@@ -14108,7 +14108,7 @@
         <v>2.7117662395709178E-3</v>
       </c>
       <c r="M53">
-        <v>0.42492179359308624</v>
+        <v>0.42492179012900938</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -14182,7 +14182,7 @@
         <v>5.8824467846739864E-2</v>
       </c>
       <c r="M54">
-        <v>0.42122179357411937</v>
+        <v>0.42122179101032142</v>
       </c>
       <c r="N54">
         <v>4</v>
@@ -14256,7 +14256,7 @@
         <v>1.3140340423210619</v>
       </c>
       <c r="M55">
-        <v>0.41874619281978304</v>
+        <v>0.41874619057423745</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -14330,7 +14330,7 @@
         <v>0.73222198698030228</v>
       </c>
       <c r="M56">
-        <v>0.41589632149504963</v>
+        <v>0.41589632564084617</v>
       </c>
       <c r="N56">
         <v>3</v>
@@ -14404,7 +14404,7 @@
         <v>1.9769905787819222</v>
       </c>
       <c r="M57">
-        <v>0.4157248242625895</v>
+        <v>0.41572482129749666</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -14478,7 +14478,7 @@
         <v>0.49617743254292718</v>
       </c>
       <c r="M58">
-        <v>0.41280531453440872</v>
+        <v>0.41280531263315051</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -14552,7 +14552,7 @@
         <v>1.9304554204124802</v>
       </c>
       <c r="M59">
-        <v>0.41227621428626549</v>
+        <v>0.41227621101346318</v>
       </c>
       <c r="N59">
         <v>3</v>
@@ -14588,7 +14588,7 @@
         <v>14.077500000000001</v>
       </c>
       <c r="AA59">
-        <v>0.47936921656390741</v>
+        <v>0.47936921656390746</v>
       </c>
       <c r="AB59">
         <v>3</v>
@@ -14626,7 +14626,7 @@
         <v>1.2745920573055001</v>
       </c>
       <c r="M60">
-        <v>0.4096764321113423</v>
+        <v>0.40967642134984</v>
       </c>
       <c r="N60">
         <v>4</v>
@@ -14700,7 +14700,7 @@
         <v>3.3467082214841438E-2</v>
       </c>
       <c r="M61">
-        <v>0.40785739154057549</v>
+        <v>0.40785739025932211</v>
       </c>
       <c r="N61">
         <v>5</v>
@@ -14736,7 +14736,7 @@
         <v>13.86375</v>
       </c>
       <c r="AA61">
-        <v>0.47742628608327203</v>
+        <v>0.47742628608327209</v>
       </c>
       <c r="AB61">
         <v>1</v>
@@ -14774,7 +14774,7 @@
         <v>3.79008166492638</v>
       </c>
       <c r="M62">
-        <v>0.40760866605135476</v>
+        <v>0.40760866428547626</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -14848,7 +14848,7 @@
         <v>0.2218954495137187</v>
       </c>
       <c r="M63">
-        <v>0.4027192620583317</v>
+        <v>0.40271925843226541</v>
       </c>
       <c r="N63">
         <v>4</v>
@@ -14922,7 +14922,7 @@
         <v>0.63429674892825172</v>
       </c>
       <c r="M64">
-        <v>0.40237427076191407</v>
+        <v>0.40237426787238928</v>
       </c>
       <c r="N64">
         <v>2</v>
@@ -14996,7 +14996,7 @@
         <v>0.1289176682938836</v>
       </c>
       <c r="M65">
-        <v>0.40200024067814899</v>
+        <v>0.40200023759240838</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -15032,7 +15032,7 @@
         <v>13.58925</v>
       </c>
       <c r="AA65">
-        <v>0.46865823517921751</v>
+        <v>0.46865823517921756</v>
       </c>
       <c r="AB65">
         <v>3</v>
@@ -15070,7 +15070,7 @@
         <v>2.5591288683511593</v>
       </c>
       <c r="M66">
-        <v>0.39875036267177777</v>
+        <v>0.39875036395175628</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -15144,7 +15144,7 @@
         <v>1.7127849126460717E-2</v>
       </c>
       <c r="M67">
-        <v>0.39536388538264639</v>
+        <v>0.39536388262030819</v>
       </c>
       <c r="N67">
         <v>5</v>
@@ -15218,7 +15218,7 @@
         <v>3.0008174583681289</v>
       </c>
       <c r="M68">
-        <v>0.39457090034177461</v>
+        <v>0.39457089273280765</v>
       </c>
       <c r="N68">
         <v>5</v>
@@ -15292,7 +15292,7 @@
         <v>1.2105806124092169</v>
       </c>
       <c r="M69">
-        <v>0.39133665464571071</v>
+        <v>0.39133664965200993</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         <v>2.2321996074582922</v>
       </c>
       <c r="M70">
-        <v>0.39115351459958941</v>
+        <v>0.39115350797502502</v>
       </c>
       <c r="N70">
         <v>4</v>
@@ -15402,7 +15402,7 @@
         <v>12.89175</v>
       </c>
       <c r="AA70">
-        <v>0.45916158619561398</v>
+        <v>0.45916158619561404</v>
       </c>
       <c r="AB70">
         <v>4</v>
@@ -15440,7 +15440,7 @@
         <v>0.23346904773419744</v>
       </c>
       <c r="M71">
-        <v>0.39017953122356952</v>
+        <v>0.39017952900242597</v>
       </c>
       <c r="N71">
         <v>2</v>
@@ -15476,7 +15476,7 @@
         <v>1.67475</v>
       </c>
       <c r="AA71">
-        <v>0.45900715165157446</v>
+        <v>0.45900715165157457</v>
       </c>
       <c r="AB71">
         <v>5</v>
@@ -15514,7 +15514,7 @@
         <v>1.7565111987650552</v>
       </c>
       <c r="M72">
-        <v>0.39011040101959582</v>
+        <v>0.39011038926047259</v>
       </c>
       <c r="N72">
         <v>3</v>
@@ -15550,7 +15550,7 @@
         <v>9.0637500000000006</v>
       </c>
       <c r="AA72">
-        <v>0.45263855966107974</v>
+        <v>0.45263855966107985</v>
       </c>
       <c r="AB72">
         <v>4</v>
@@ -15588,7 +15588,7 @@
         <v>0.73465356632411616</v>
       </c>
       <c r="M73">
-        <v>0.3821280816273106</v>
+        <v>0.38212807677837468</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -15662,7 +15662,7 @@
         <v>2.3998098626104025E-3</v>
       </c>
       <c r="M74">
-        <v>0.38023778067157149</v>
+        <v>0.38023777872775139</v>
       </c>
       <c r="N74">
         <v>5</v>
@@ -15736,7 +15736,7 @@
         <v>0.5577856724575444</v>
       </c>
       <c r="M75">
-        <v>0.37958017434708069</v>
+        <v>0.37958017191166121</v>
       </c>
       <c r="N75">
         <v>2</v>
@@ -15810,7 +15810,7 @@
         <v>1.5771994961728515</v>
       </c>
       <c r="M76">
-        <v>0.37919883015963801</v>
+        <v>0.37919882939344879</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -15884,7 +15884,7 @@
         <v>2.3566909382631192</v>
       </c>
       <c r="M77">
-        <v>0.37600176811186109</v>
+        <v>0.37600176401919672</v>
       </c>
       <c r="N77">
         <v>4</v>
@@ -15958,7 +15958,7 @@
         <v>1.7406424458328442</v>
       </c>
       <c r="M78">
-        <v>0.37362852416084857</v>
+        <v>0.37362852168953148</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -15994,7 +15994,7 @@
         <v>2.7697500000000002</v>
       </c>
       <c r="AA78">
-        <v>0.44113880618422213</v>
+        <v>0.44113880618422219</v>
       </c>
       <c r="AB78">
         <v>4</v>
@@ -16032,7 +16032,7 @@
         <v>3.6574074074074074E-3</v>
       </c>
       <c r="M79">
-        <v>0.37050476120479747</v>
+        <v>0.3705047589334084</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -16068,7 +16068,7 @@
         <v>1.05</v>
       </c>
       <c r="AA79">
-        <v>0.44043060820074476</v>
+        <v>0.44043060820074487</v>
       </c>
       <c r="AB79">
         <v>1</v>
@@ -16106,7 +16106,7 @@
         <v>3.295532422269043</v>
       </c>
       <c r="M80">
-        <v>0.37019316405664326</v>
+        <v>0.37019316486324494</v>
       </c>
       <c r="N80">
         <v>3</v>
@@ -16180,7 +16180,7 @@
         <v>9.96495825461637E-4</v>
       </c>
       <c r="M81">
-        <v>0.36908471448379471</v>
+        <v>0.36908471137164228</v>
       </c>
       <c r="N81">
         <v>4</v>
@@ -16216,7 +16216,7 @@
         <v>8.9954999999999998</v>
       </c>
       <c r="AA81">
-        <v>0.43837885805004867</v>
+        <v>0.43837885805004878</v>
       </c>
       <c r="AB81">
         <v>2</v>
@@ -16254,7 +16254,7 @@
         <v>0.51243155036666865</v>
       </c>
       <c r="M82">
-        <v>0.36640362809288762</v>
+        <v>0.36640362586024494</v>
       </c>
       <c r="N82">
         <v>2</v>
@@ -16328,7 +16328,7 @@
         <v>0.15354120957401338</v>
       </c>
       <c r="M83">
-        <v>0.36438735151163104</v>
+        <v>0.3643873482237921</v>
       </c>
       <c r="N83">
         <v>5</v>
@@ -16364,7 +16364,7 @@
         <v>7.1122500000000004</v>
       </c>
       <c r="AA83">
-        <v>0.43181862808709598</v>
+        <v>0.43181862808709609</v>
       </c>
       <c r="AB83">
         <v>2</v>
@@ -16402,7 +16402,7 @@
         <v>1.933209740197273</v>
       </c>
       <c r="M84">
-        <v>0.3615152561679234</v>
+        <v>0.36151525568398368</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -16476,7 +16476,7 @@
         <v>2.7101889671130204</v>
       </c>
       <c r="M85">
-        <v>0.35973332891280696</v>
+        <v>0.3597333251992072</v>
       </c>
       <c r="N85">
         <v>3</v>
@@ -16550,7 +16550,7 @@
         <v>3.4575767361981664</v>
       </c>
       <c r="M86">
-        <v>0.35898831135479436</v>
+        <v>0.358988307363385</v>
       </c>
       <c r="N86">
         <v>2</v>
@@ -16586,7 +16586,7 @@
         <v>7.1122500000000004</v>
       </c>
       <c r="AA86">
-        <v>0.42557446207205929</v>
+        <v>0.4255744620720594</v>
       </c>
       <c r="AB86">
         <v>3</v>
@@ -16624,7 +16624,7 @@
         <v>4.8331881592320644E-2</v>
       </c>
       <c r="M87">
-        <v>0.35889654721421277</v>
+        <v>0.3588965443500996</v>
       </c>
       <c r="N87">
         <v>4</v>
@@ -16698,7 +16698,7 @@
         <v>4.8872709073901932</v>
       </c>
       <c r="M88">
-        <v>0.35130800052253713</v>
+        <v>0.35130800105143889</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -16772,7 +16772,7 @@
         <v>2.7609107730710458</v>
       </c>
       <c r="M89">
-        <v>0.3499932515005244</v>
+        <v>0.3499932492330674</v>
       </c>
       <c r="N89">
         <v>2</v>
@@ -16846,7 +16846,7 @@
         <v>1.0189103761562657</v>
       </c>
       <c r="M90">
-        <v>0.34652234123519837</v>
+        <v>0.3465223391044156</v>
       </c>
       <c r="N90">
         <v>4</v>
@@ -16920,7 +16920,7 @@
         <v>5.3900478641741176E-2</v>
       </c>
       <c r="M91">
-        <v>0.34598632210742603</v>
+        <v>0.345986319025198</v>
       </c>
       <c r="N91">
         <v>5</v>
@@ -16994,7 +16994,7 @@
         <v>1.8213320851645813</v>
       </c>
       <c r="M92">
-        <v>0.34592439814125536</v>
+        <v>0.3459243986148019</v>
       </c>
       <c r="N92">
         <v>3</v>
@@ -17068,7 +17068,7 @@
         <v>2.5172949114250192</v>
       </c>
       <c r="M93">
-        <v>0.34399214123132765</v>
+        <v>0.34399213860247635</v>
       </c>
       <c r="N93">
         <v>2</v>
@@ -17142,7 +17142,7 @@
         <v>1.4648842407531936E-2</v>
       </c>
       <c r="M94">
-        <v>0.34209998385531665</v>
+        <v>0.3420999815727877</v>
       </c>
       <c r="N94">
         <v>5</v>
@@ -17216,7 +17216,7 @@
         <v>2.9990126470674681</v>
       </c>
       <c r="M95">
-        <v>0.3407303535830376</v>
+        <v>0.34073035377466288</v>
       </c>
       <c r="N95">
         <v>3</v>
@@ -17290,7 +17290,7 @@
         <v>2.4108310694232142</v>
       </c>
       <c r="M96">
-        <v>0.34019944626648557</v>
+        <v>0.34019944443978345</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -17326,7 +17326,7 @@
         <v>6.7350000000000003</v>
       </c>
       <c r="AA96">
-        <v>0.40853983001721733</v>
+        <v>0.40853983001721744</v>
       </c>
       <c r="AB96">
         <v>1</v>
@@ -17364,7 +17364,7 @@
         <v>0.37336913797068721</v>
       </c>
       <c r="M97">
-        <v>0.33597551605507514</v>
+        <v>0.33597551161415024</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -17438,7 +17438,7 @@
         <v>2.2692398901185427</v>
       </c>
       <c r="M98">
-        <v>0.33363512198847051</v>
+        <v>0.33363511731561152</v>
       </c>
       <c r="N98">
         <v>2</v>
@@ -17474,7 +17474,7 @@
         <v>0.45074999999999998</v>
       </c>
       <c r="AA98">
-        <v>0.40198066639350832</v>
+        <v>0.40198066639350838</v>
       </c>
       <c r="AB98">
         <v>2</v>
@@ -17512,7 +17512,7 @@
         <v>1.4515636262280183</v>
       </c>
       <c r="M99">
-        <v>0.33076168208006679</v>
+        <v>0.33076167590529609</v>
       </c>
       <c r="N99">
         <v>3</v>
@@ -17586,7 +17586,7 @@
         <v>4.4025865463278082</v>
       </c>
       <c r="M100">
-        <v>0.32841368448459896</v>
+        <v>0.32841368287550843</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -17660,7 +17660,7 @@
         <v>1.5504845208117317</v>
       </c>
       <c r="M101">
-        <v>0.32830234167954908</v>
+        <v>0.3283023386255518</v>
       </c>
       <c r="N101">
         <v>4</v>
@@ -17696,7 +17696,7 @@
         <v>2.0369999999999999</v>
       </c>
       <c r="AA101">
-        <v>0.3985701693807665</v>
+        <v>0.39857016938076661</v>
       </c>
       <c r="AB101">
         <v>1</v>
@@ -17734,7 +17734,7 @@
         <v>1.5664629679918325</v>
       </c>
       <c r="M102">
-        <v>0.32669902880814938</v>
+        <v>0.32669902598812711</v>
       </c>
       <c r="N102">
         <v>5</v>
@@ -17808,7 +17808,7 @@
         <v>0.8909343046109206</v>
       </c>
       <c r="M103">
-        <v>0.32204753446078982</v>
+        <v>0.32204753451347018</v>
       </c>
       <c r="N103">
         <v>4</v>
@@ -17882,7 +17882,7 @@
         <v>4.7571826711999234</v>
       </c>
       <c r="M104">
-        <v>0.32159491657161282</v>
+        <v>0.32159491593770606</v>
       </c>
       <c r="N104">
         <v>3</v>
@@ -17956,7 +17956,7 @@
         <v>0.43581570479147785</v>
       </c>
       <c r="M105">
-        <v>0.32151572315137106</v>
+        <v>0.32151572098722564</v>
       </c>
       <c r="N105">
         <v>5</v>
@@ -18030,7 +18030,7 @@
         <v>4.1790301881767649</v>
       </c>
       <c r="M106">
-        <v>0.31980072625039729</v>
+        <v>0.31980072226458867</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -18104,7 +18104,7 @@
         <v>5.6646693835038624</v>
       </c>
       <c r="M107">
-        <v>0.31823526013130077</v>
+        <v>0.31823525776054246</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -18178,7 +18178,7 @@
         <v>3.847989483952559</v>
       </c>
       <c r="M108">
-        <v>0.31097614343980012</v>
+        <v>0.31097613626845722</v>
       </c>
       <c r="N108">
         <v>2</v>
@@ -18252,7 +18252,7 @@
         <v>0.30073405265474368</v>
       </c>
       <c r="M109">
-        <v>0.31095779695468823</v>
+        <v>0.31095779459434636</v>
       </c>
       <c r="N109">
         <v>5</v>
@@ -18326,7 +18326,7 @@
         <v>2.3245358721567073</v>
       </c>
       <c r="M110">
-        <v>0.31062575099279077</v>
+        <v>0.31062574852657171</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -18400,7 +18400,7 @@
         <v>8.6993697467428757E-2</v>
       </c>
       <c r="M111">
-        <v>0.30933409324147326</v>
+        <v>0.30933409111053789</v>
       </c>
       <c r="N111">
         <v>4</v>
@@ -18474,7 +18474,7 @@
         <v>3.690679009118111</v>
       </c>
       <c r="M112">
-        <v>0.30879241688360148</v>
+        <v>0.30879241623332437</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -18510,7 +18510,7 @@
         <v>6.9269999999999996</v>
       </c>
       <c r="AA112">
-        <v>0.37326034950378578</v>
+        <v>0.37326034950378589</v>
       </c>
       <c r="AB112">
         <v>3</v>
@@ -18548,7 +18548,7 @@
         <v>2.4930897512525561</v>
       </c>
       <c r="M113">
-        <v>0.30101575303543215</v>
+        <v>0.30101575105285433</v>
       </c>
       <c r="N113">
         <v>3</v>
@@ -18584,7 +18584,7 @@
         <v>6.3929999999999998</v>
       </c>
       <c r="AA113">
-        <v>0.37204103806478833</v>
+        <v>0.3720410380647885</v>
       </c>
       <c r="AB113">
         <v>1</v>
@@ -18622,7 +18622,7 @@
         <v>2.6905002792932944</v>
       </c>
       <c r="M114">
-        <v>0.30041979776435812</v>
+        <v>0.30041979607350427</v>
       </c>
       <c r="N114">
         <v>4</v>
@@ -18696,7 +18696,7 @@
         <v>3.6004221032584569</v>
       </c>
       <c r="M115">
-        <v>0.29910281009329681</v>
+        <v>0.29910280844465237</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -18732,7 +18732,7 @@
         <v>1.794</v>
       </c>
       <c r="AA115">
-        <v>0.36662290621876786</v>
+        <v>0.36662290621876792</v>
       </c>
       <c r="AB115">
         <v>2</v>
@@ -18770,7 +18770,7 @@
         <v>0.99431642548015509</v>
       </c>
       <c r="M116">
-        <v>0.29903626261444549</v>
+        <v>0.29903626045503401</v>
       </c>
       <c r="N116">
         <v>5</v>
@@ -18844,7 +18844,7 @@
         <v>6.1657447284388454</v>
       </c>
       <c r="M117">
-        <v>0.2989172821821145</v>
+        <v>0.2989172799742279</v>
       </c>
       <c r="N117">
         <v>2</v>
@@ -18880,7 +18880,7 @@
         <v>1.6147499999999999</v>
       </c>
       <c r="AA117">
-        <v>0.3638013967622955</v>
+        <v>0.36380139676229561</v>
       </c>
       <c r="AB117">
         <v>1</v>
@@ -18918,7 +18918,7 @@
         <v>2.0094738201721833</v>
       </c>
       <c r="M118">
-        <v>0.29303475634729742</v>
+        <v>0.2930347520941014</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -18992,7 +18992,7 @@
         <v>1.5272709616368749</v>
       </c>
       <c r="M119">
-        <v>0.29016255889546411</v>
+        <v>0.29016255728422363</v>
       </c>
       <c r="N119">
         <v>3</v>
@@ -19028,7 +19028,7 @@
         <v>3.7087500000000002</v>
       </c>
       <c r="AA119">
-        <v>0.35969642634032345</v>
+        <v>0.35969642634032351</v>
       </c>
       <c r="AB119">
         <v>2</v>
@@ -19066,7 +19066,7 @@
         <v>6.0663438137814643</v>
       </c>
       <c r="M120">
-        <v>0.28985862873073293</v>
+        <v>0.2898586267220567</v>
       </c>
       <c r="N120">
         <v>2</v>
@@ -19140,7 +19140,7 @@
         <v>8.0581975683936893</v>
       </c>
       <c r="M121">
-        <v>0.28931363591494424</v>
+        <v>0.28931363621990946</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -19214,7 +19214,7 @@
         <v>0.47384898931153535</v>
       </c>
       <c r="M122">
-        <v>0.28631414726570209</v>
+        <v>0.2863141461202886</v>
       </c>
       <c r="N122">
         <v>5</v>
@@ -19250,7 +19250,7 @@
         <v>5.9249999999999997E-2</v>
       </c>
       <c r="AA122">
-        <v>0.34935206141264796</v>
+        <v>0.34935206141264802</v>
       </c>
       <c r="AB122">
         <v>4</v>
@@ -19288,7 +19288,7 @@
         <v>2.896492148943449</v>
       </c>
       <c r="M123">
-        <v>0.28440602294780448</v>
+        <v>0.28440602351226402</v>
       </c>
       <c r="N123">
         <v>2</v>
@@ -19362,7 +19362,7 @@
         <v>2.2814287959259865</v>
       </c>
       <c r="M124">
-        <v>0.28106182430546611</v>
+        <v>0.28106182560989251</v>
       </c>
       <c r="N124">
         <v>3</v>
@@ -19436,7 +19436,7 @@
         <v>3.129484983818783</v>
       </c>
       <c r="M125">
-        <v>0.28067166073141731</v>
+        <v>0.28067165832942098</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -19472,7 +19472,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="AA125">
-        <v>0.34593480173508701</v>
+        <v>0.34593480173508712</v>
       </c>
       <c r="AB125">
         <v>5</v>
@@ -19510,7 +19510,7 @@
         <v>1.7982764958683246</v>
       </c>
       <c r="M126">
-        <v>0.27704478722363707</v>
+        <v>0.27704478289465878</v>
       </c>
       <c r="N126">
         <v>4</v>
@@ -19584,7 +19584,7 @@
         <v>0.18393091727789446</v>
       </c>
       <c r="M127">
-        <v>0.27672153724779708</v>
+        <v>0.2767215352757505</v>
       </c>
       <c r="N127">
         <v>5</v>
@@ -19620,7 +19620,7 @@
         <v>20.408249999999999</v>
       </c>
       <c r="AA127">
-        <v>0.34163367969615338</v>
+        <v>0.34163367969615344</v>
       </c>
       <c r="AB127">
         <v>1</v>
@@ -19658,7 +19658,7 @@
         <v>3.4018968391307434</v>
       </c>
       <c r="M128">
-        <v>0.27147260213715657</v>
+        <v>0.27147259931884532</v>
       </c>
       <c r="N128">
         <v>3</v>
@@ -19732,7 +19732,7 @@
         <v>0.67763885184540795</v>
       </c>
       <c r="M129">
-        <v>0.27051230463264214</v>
+        <v>0.27051230247162072</v>
       </c>
       <c r="N129">
         <v>5</v>
@@ -19768,7 +19768,7 @@
         <v>13.430249999999999</v>
       </c>
       <c r="AA129">
-        <v>0.34108145999720912</v>
+        <v>0.34108145999720924</v>
       </c>
       <c r="AB129">
         <v>2</v>
@@ -19806,7 +19806,7 @@
         <v>6.0093893145949382</v>
       </c>
       <c r="M130">
-        <v>0.2698000482652832</v>
+        <v>0.26980005205539698</v>
       </c>
       <c r="N130">
         <v>1</v>
@@ -19842,7 +19842,7 @@
         <v>11.169</v>
       </c>
       <c r="AA130">
-        <v>0.33796987843615411</v>
+        <v>0.33796987843615417</v>
       </c>
       <c r="AB130">
         <v>3</v>
@@ -19880,7 +19880,7 @@
         <v>4.9249364135526257</v>
       </c>
       <c r="M131">
-        <v>0.26814164018433323</v>
+        <v>0.26814164719582134</v>
       </c>
       <c r="N131">
         <v>2</v>
@@ -19916,7 +19916,7 @@
         <v>8.95425</v>
       </c>
       <c r="AA131">
-        <v>0.33669508978686891</v>
+        <v>0.33669508978686896</v>
       </c>
       <c r="AB131">
         <v>4</v>
@@ -19954,7 +19954,7 @@
         <v>2.4101467924726094</v>
       </c>
       <c r="M132">
-        <v>0.26733022626316438</v>
+        <v>0.26733022517481653</v>
       </c>
       <c r="N132">
         <v>4</v>
@@ -20028,7 +20028,7 @@
         <v>2.2039133433674141</v>
       </c>
       <c r="M133">
-        <v>0.26235378789367603</v>
+        <v>0.26235378744184923</v>
       </c>
       <c r="N133">
         <v>3</v>
@@ -20064,7 +20064,7 @@
         <v>17.1585</v>
       </c>
       <c r="AA133">
-        <v>0.32970918204301214</v>
+        <v>0.32970918204301225</v>
       </c>
       <c r="AB133">
         <v>1</v>
@@ -20102,7 +20102,7 @@
         <v>4.5916478260064322</v>
       </c>
       <c r="M134">
-        <v>0.25942481159954706</v>
+        <v>0.25942480586986433</v>
       </c>
       <c r="N134">
         <v>2</v>
@@ -20176,7 +20176,7 @@
         <v>4.0060770481123287</v>
       </c>
       <c r="M135">
-        <v>0.2586560774208444</v>
+        <v>0.25865607508713173</v>
       </c>
       <c r="N135">
         <v>1</v>
@@ -20212,7 +20212,7 @@
         <v>7.8622500000000004</v>
       </c>
       <c r="AA135">
-        <v>0.32777269671902404</v>
+        <v>0.32777269671902415</v>
       </c>
       <c r="AB135">
         <v>4</v>
@@ -20250,7 +20250,7 @@
         <v>2.2022678923833694</v>
       </c>
       <c r="M136">
-        <v>0.25824166381846347</v>
+        <v>0.25824166185278302</v>
       </c>
       <c r="N136">
         <v>4</v>
@@ -20324,7 +20324,7 @@
         <v>0.13683936706105471</v>
       </c>
       <c r="M137">
-        <v>0.25781933874316371</v>
+        <v>0.2578193369167483</v>
       </c>
       <c r="N137">
         <v>5</v>
@@ -20360,7 +20360,7 @@
         <v>4.54575</v>
       </c>
       <c r="AA137">
-        <v>0.32431508385085872</v>
+        <v>0.32431508385085878</v>
       </c>
       <c r="AB137">
         <v>4</v>
@@ -20398,7 +20398,7 @@
         <v>8.9946572804857894</v>
       </c>
       <c r="M138">
-        <v>0.25263887434809768</v>
+        <v>0.2526388759288149</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -20472,7 +20472,7 @@
         <v>1.0266178643710517</v>
       </c>
       <c r="M139">
-        <v>0.25137607245089544</v>
+        <v>0.25137606973383247</v>
       </c>
       <c r="N139">
         <v>5</v>
@@ -20546,7 +20546,7 @@
         <v>2.1066277142799832</v>
       </c>
       <c r="M140">
-        <v>0.2501659476474381</v>
+        <v>0.25016594571362138</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -20620,7 +20620,7 @@
         <v>3.8609228955867123</v>
       </c>
       <c r="M141">
-        <v>0.24939127733540964</v>
+        <v>0.24939127376979972</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -20694,7 +20694,7 @@
         <v>4.9364878688650951</v>
       </c>
       <c r="M142">
-        <v>0.24887372340308392</v>
+        <v>0.24887371652927318</v>
       </c>
       <c r="N142">
         <v>2</v>
@@ -20768,7 +20768,7 @@
         <v>3.7693651077342993</v>
       </c>
       <c r="M143">
-        <v>0.24305244123332959</v>
+        <v>0.24305243662494141</v>
       </c>
       <c r="N143">
         <v>2</v>
@@ -20804,7 +20804,7 @@
         <v>0.49125000000000002</v>
       </c>
       <c r="AA143">
-        <v>0.31155710012196075</v>
+        <v>0.31155710012196092</v>
       </c>
       <c r="AB143">
         <v>5</v>
@@ -20842,7 +20842,7 @@
         <v>1.7935471881954055</v>
       </c>
       <c r="M144">
-        <v>0.24285845305661427</v>
+        <v>0.24285845053018887</v>
       </c>
       <c r="N144">
         <v>4</v>
@@ -20878,7 +20878,7 @@
         <v>10.570499999999999</v>
       </c>
       <c r="AA144">
-        <v>0.30881824420456816</v>
+        <v>0.30881824420456822</v>
       </c>
       <c r="AB144">
         <v>2</v>
@@ -20916,7 +20916,7 @@
         <v>0.26679190256916285</v>
       </c>
       <c r="M145">
-        <v>0.24282327562791639</v>
+        <v>0.24282327436354365</v>
       </c>
       <c r="N145">
         <v>5</v>
@@ -20952,7 +20952,7 @@
         <v>16.149000000000001</v>
       </c>
       <c r="AA145">
-        <v>0.30875612668658192</v>
+        <v>0.30875612668658203</v>
       </c>
       <c r="AB145">
         <v>1</v>
@@ -20990,7 +20990,7 @@
         <v>3.7660385901929665</v>
       </c>
       <c r="M146">
-        <v>0.23974689274236355</v>
+        <v>0.23974688975631447</v>
       </c>
       <c r="N146">
         <v>3</v>
@@ -21026,7 +21026,7 @@
         <v>11.227499999999999</v>
       </c>
       <c r="AA146">
-        <v>0.30830822430346005</v>
+        <v>0.30830822430346017</v>
       </c>
       <c r="AB146">
         <v>3</v>
@@ -21064,7 +21064,7 @@
         <v>3.084778883914066</v>
       </c>
       <c r="M147">
-        <v>0.23848971833924495</v>
+        <v>0.23848971379117398</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -21138,7 +21138,7 @@
         <v>2.3762014299455796</v>
       </c>
       <c r="M148">
-        <v>0.23155863007802063</v>
+        <v>0.23155862536816757</v>
       </c>
       <c r="N148">
         <v>1</v>
@@ -21174,7 +21174,7 @@
         <v>16.659749999999999</v>
       </c>
       <c r="AA148">
-        <v>0.30082558402596893</v>
+        <v>0.30082558402596898</v>
       </c>
       <c r="AB148">
         <v>3</v>
@@ -21212,7 +21212,7 @@
         <v>3.9683857768697415</v>
       </c>
       <c r="M149">
-        <v>0.22968240471305368</v>
+        <v>0.22968240335254783</v>
       </c>
       <c r="N149">
         <v>3</v>
@@ -21286,7 +21286,7 @@
         <v>3.0997954505702627</v>
       </c>
       <c r="M150">
-        <v>0.22965945187865039</v>
+        <v>0.22965945002388827</v>
       </c>
       <c r="N150">
         <v>4</v>
@@ -21360,7 +21360,7 @@
         <v>1.8924068097431741</v>
       </c>
       <c r="M151">
-        <v>0.22936484009710512</v>
+        <v>0.22936483981861827</v>
       </c>
       <c r="N151">
         <v>2</v>
@@ -21434,7 +21434,7 @@
         <v>1.5690624660767625</v>
       </c>
       <c r="M152">
-        <v>0.22738607252081819</v>
+        <v>0.22738607247138148</v>
       </c>
       <c r="N152">
         <v>5</v>
@@ -21470,7 +21470,7 @@
         <v>3.5295000000000001</v>
       </c>
       <c r="AA152">
-        <v>0.29094712892945335</v>
+        <v>0.2909471289294534</v>
       </c>
       <c r="AB152">
         <v>2</v>
@@ -21508,7 +21508,7 @@
         <v>1.88748560300502</v>
       </c>
       <c r="M153">
-        <v>0.22148841968075822</v>
+        <v>0.22148841782851875</v>
       </c>
       <c r="N153">
         <v>5</v>
@@ -21582,7 +21582,7 @@
         <v>2.8787677843141766</v>
       </c>
       <c r="M154">
-        <v>0.22053202007202716</v>
+        <v>0.22053201756131269</v>
       </c>
       <c r="N154">
         <v>3</v>
@@ -21656,7 +21656,7 @@
         <v>3.6969196549641321</v>
       </c>
       <c r="M155">
-        <v>0.22051895282124587</v>
+        <v>0.22051895109882724</v>
       </c>
       <c r="N155">
         <v>1</v>
@@ -21730,7 +21730,7 @@
         <v>0.49581063402940323</v>
       </c>
       <c r="M156">
-        <v>0.22030030883736867</v>
+        <v>0.22030030623993341</v>
       </c>
       <c r="N156">
         <v>4</v>
@@ -21804,7 +21804,7 @@
         <v>3.6299606577739012</v>
       </c>
       <c r="M157">
-        <v>0.21791087841016241</v>
+        <v>0.21791087407312318</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -21878,7 +21878,7 @@
         <v>2.5608098938482606</v>
       </c>
       <c r="M158">
-        <v>0.2112679750647416</v>
+        <v>0.21126797298755862</v>
       </c>
       <c r="N158">
         <v>1</v>
@@ -21952,7 +21952,7 @@
         <v>1.7726081831160889</v>
       </c>
       <c r="M159">
-        <v>0.2111892141926173</v>
+        <v>0.21118921204636412</v>
       </c>
       <c r="N159">
         <v>5</v>
@@ -21988,7 +21988,7 @@
         <v>15.4605</v>
       </c>
       <c r="AA159">
-        <v>0.28101071419164625</v>
+        <v>0.2810107141916463</v>
       </c>
       <c r="AB159">
         <v>2</v>
@@ -22026,7 +22026,7 @@
         <v>2.2107012297753181</v>
       </c>
       <c r="M160">
-        <v>0.21021035171539998</v>
+        <v>0.21021035285695197</v>
       </c>
       <c r="N160">
         <v>4</v>
@@ -22100,7 +22100,7 @@
         <v>2.6893495542589045</v>
       </c>
       <c r="M161">
-        <v>0.20916274803051785</v>
+        <v>0.20916274642293298</v>
       </c>
       <c r="N161">
         <v>2</v>
@@ -22136,7 +22136,7 @@
         <v>15.83625</v>
       </c>
       <c r="AA161">
-        <v>0.27793126060367185</v>
+        <v>0.2779312606036719</v>
       </c>
       <c r="AB161">
         <v>5</v>
@@ -22174,7 +22174,7 @@
         <v>1.4646146869429781</v>
       </c>
       <c r="M162">
-        <v>0.20753581990897332</v>
+        <v>0.20753581580297559</v>
       </c>
       <c r="N162">
         <v>3</v>
@@ -22248,7 +22248,7 @@
         <v>2.2507071499037417</v>
       </c>
       <c r="M163">
-        <v>0.20109697447370189</v>
+        <v>0.20109696761009582</v>
       </c>
       <c r="N163">
         <v>3</v>
@@ -22322,7 +22322,7 @@
         <v>4.3924746781664341</v>
       </c>
       <c r="M164">
-        <v>0.20059251908592146</v>
+        <v>0.2005925151293198</v>
       </c>
       <c r="N164">
         <v>1</v>
@@ -22358,7 +22358,7 @@
         <v>0.33825</v>
       </c>
       <c r="AA164">
-        <v>0.2684913361071683</v>
+        <v>0.26849133610716841</v>
       </c>
       <c r="AB164">
         <v>2</v>
@@ -22396,7 +22396,7 @@
         <v>3.3752403267192528</v>
       </c>
       <c r="M165">
-        <v>0.2005616561102444</v>
+        <v>0.20056165423716896</v>
       </c>
       <c r="N165">
         <v>5</v>
@@ -22432,7 +22432,7 @@
         <v>0.83850000000000002</v>
       </c>
       <c r="AA165">
-        <v>0.2680007233403171</v>
+        <v>0.26800072334031722</v>
       </c>
       <c r="AB165">
         <v>3</v>
@@ -22470,7 +22470,7 @@
         <v>5.0373271607425112</v>
       </c>
       <c r="M166">
-        <v>0.19972309512474795</v>
+        <v>0.19972309279799302</v>
       </c>
       <c r="N166">
         <v>2</v>
@@ -22544,7 +22544,7 @@
         <v>3.3561473262517927</v>
       </c>
       <c r="M167">
-        <v>0.19883907779730217</v>
+        <v>0.19883907814020718</v>
       </c>
       <c r="N167">
         <v>4</v>
@@ -22580,7 +22580,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="AA167">
-        <v>0.2640512887916393</v>
+        <v>0.26405128879163942</v>
       </c>
       <c r="AB167">
         <v>2</v>
@@ -22618,7 +22618,7 @@
         <v>3.6668840500697204</v>
       </c>
       <c r="M168">
-        <v>0.19183077219587086</v>
+        <v>0.1918307704010378</v>
       </c>
       <c r="N168">
         <v>5</v>
@@ -22692,7 +22692,7 @@
         <v>5.9755337472809327</v>
       </c>
       <c r="M169">
-        <v>0.19085450335703938</v>
+        <v>0.19085449352366687</v>
       </c>
       <c r="N169">
         <v>2</v>
@@ -22728,7 +22728,7 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="AA169">
-        <v>0.26299266050370079</v>
+        <v>0.2629926605037009</v>
       </c>
       <c r="AB169">
         <v>3</v>
@@ -22766,7 +22766,7 @@
         <v>5.264045651819754</v>
       </c>
       <c r="M170">
-        <v>0.19079542060577917</v>
+        <v>0.19079541971373973</v>
       </c>
       <c r="N170">
         <v>4</v>
@@ -22840,7 +22840,7 @@
         <v>2.1579768059685258</v>
       </c>
       <c r="M171">
-        <v>0.18964556296488425</v>
+        <v>0.18964556179607972</v>
       </c>
       <c r="N171">
         <v>1</v>
@@ -22876,7 +22876,7 @@
         <v>4.24275</v>
       </c>
       <c r="AA171">
-        <v>0.25531074280828758</v>
+        <v>0.25531074280828769</v>
       </c>
       <c r="AB171">
         <v>4</v>
@@ -22914,7 +22914,7 @@
         <v>2.354440792829037</v>
       </c>
       <c r="M172">
-        <v>0.18944697471714339</v>
+        <v>0.18944697071557454</v>
       </c>
       <c r="N172">
         <v>3</v>
@@ -22988,7 +22988,7 @@
         <v>3.2441835661942187</v>
       </c>
       <c r="M173">
-        <v>0.18141403538239878</v>
+        <v>0.18141403336723089</v>
       </c>
       <c r="N173">
         <v>3</v>
@@ -23062,7 +23062,7 @@
         <v>2.3264998358534439</v>
       </c>
       <c r="M174">
-        <v>0.18083028443639262</v>
+        <v>0.18083028393064907</v>
       </c>
       <c r="N174">
         <v>2</v>
@@ -23098,7 +23098,7 @@
         <v>3.8842500000000002</v>
       </c>
       <c r="AA174">
-        <v>0.25012734645191392</v>
+        <v>0.25012734645191398</v>
       </c>
       <c r="AB174">
         <v>5</v>
@@ -23136,7 +23136,7 @@
         <v>4.4736297558902312</v>
       </c>
       <c r="M175">
-        <v>0.17974427699428858</v>
+        <v>0.17974427675513602</v>
       </c>
       <c r="N175">
         <v>4</v>
@@ -23172,7 +23172,7 @@
         <v>2.31975</v>
       </c>
       <c r="AA175">
-        <v>0.24995322401257286</v>
+        <v>0.249953224012573</v>
       </c>
       <c r="AB175">
         <v>4</v>
@@ -23210,7 +23210,7 @@
         <v>7.2543596276102171</v>
       </c>
       <c r="M176">
-        <v>0.17967800075243232</v>
+        <v>0.17967800022321545</v>
       </c>
       <c r="N176">
         <v>1</v>
@@ -23284,7 +23284,7 @@
         <v>3.4598015064326955</v>
       </c>
       <c r="M177">
-        <v>0.17900967876002397</v>
+        <v>0.17900967724411693</v>
       </c>
       <c r="N177">
         <v>5</v>
@@ -23320,7 +23320,7 @@
         <v>1.2967500000000001</v>
       </c>
       <c r="AA177">
-        <v>0.24304485771409401</v>
+        <v>0.24304485771409409</v>
       </c>
       <c r="AB177">
         <v>3</v>
@@ -23358,7 +23358,7 @@
         <v>0.52998544898918021</v>
       </c>
       <c r="M178">
-        <v>0.170591986262944</v>
+        <v>0.17059198529790243</v>
       </c>
       <c r="N178">
         <v>3</v>
@@ -23394,7 +23394,7 @@
         <v>1.6312500000000001</v>
       </c>
       <c r="AA178">
-        <v>0.24261137844025041</v>
+        <v>0.24261137844025049</v>
       </c>
       <c r="AB178">
         <v>2</v>
@@ -23432,7 +23432,7 @@
         <v>3.9827053694545995</v>
       </c>
       <c r="M179">
-        <v>0.16943011912130423</v>
+        <v>0.16943011736806798</v>
       </c>
       <c r="N179">
         <v>1</v>
@@ -23506,7 +23506,7 @@
         <v>4.3245977669154092</v>
       </c>
       <c r="M180">
-        <v>0.16902136397396184</v>
+        <v>0.1690213629952689</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -23580,7 +23580,7 @@
         <v>3.182237767624652</v>
       </c>
       <c r="M181">
-        <v>0.16877918571088454</v>
+        <v>0.16877918530445615</v>
       </c>
       <c r="N181">
         <v>2</v>
@@ -23654,7 +23654,7 @@
         <v>2.5689003198961768</v>
       </c>
       <c r="M182">
-        <v>0.1665764752137722</v>
+        <v>0.16657647442252008</v>
       </c>
       <c r="N182">
         <v>5</v>
@@ -23728,7 +23728,7 @@
         <v>5.4344414586166305</v>
       </c>
       <c r="M183">
-        <v>0.16087770748992311</v>
+        <v>0.16087770891456057</v>
       </c>
       <c r="N183">
         <v>2</v>
@@ -23802,7 +23802,7 @@
         <v>3.3808318447669268</v>
       </c>
       <c r="M184">
-        <v>0.160589256217813</v>
+        <v>0.16058925480395042</v>
       </c>
       <c r="N184">
         <v>5</v>
@@ -23876,7 +23876,7 @@
         <v>8.8013501002862071</v>
       </c>
       <c r="M185">
-        <v>0.16029247229409299</v>
+        <v>0.16029246916457429</v>
       </c>
       <c r="N185">
         <v>1</v>
@@ -23950,7 +23950,7 @@
         <v>6.2230663602342684</v>
       </c>
       <c r="M186">
-        <v>0.15990326224395754</v>
+        <v>0.15990326046240233</v>
       </c>
       <c r="N186">
         <v>3</v>
@@ -24024,7 +24024,7 @@
         <v>3.5185550276992186</v>
       </c>
       <c r="M187">
-        <v>0.15760365624400369</v>
+        <v>0.15760365594566997</v>
       </c>
       <c r="N187">
         <v>4</v>
@@ -24060,7 +24060,7 @@
         <v>1.78125</v>
       </c>
       <c r="AA187">
-        <v>0.21821710730296279</v>
+        <v>0.2182171073029629</v>
       </c>
       <c r="AB187">
         <v>1</v>
@@ -24098,7 +24098,7 @@
         <v>4.6766545166679236</v>
       </c>
       <c r="M188">
-        <v>0.15275634025212034</v>
+        <v>0.15275633889672036</v>
       </c>
       <c r="N188">
         <v>2</v>
@@ -24134,7 +24134,7 @@
         <v>0.67874999999999996</v>
       </c>
       <c r="AA188">
-        <v>0.21369711872966515</v>
+        <v>0.21369711872966526</v>
       </c>
       <c r="AB188">
         <v>1</v>
@@ -24172,7 +24172,7 @@
         <v>2.1557796047944637</v>
       </c>
       <c r="M189">
-        <v>0.15268745059158501</v>
+        <v>0.15268744994993205</v>
       </c>
       <c r="N189">
         <v>3</v>
@@ -24246,7 +24246,7 @@
         <v>0.66243867433103065</v>
       </c>
       <c r="M190">
-        <v>0.15149259435957305</v>
+        <v>0.15149259309738106</v>
       </c>
       <c r="N190">
         <v>4</v>
@@ -24282,7 +24282,7 @@
         <v>2.2094999999999998</v>
       </c>
       <c r="AA190">
-        <v>0.21147746211416507</v>
+        <v>0.2114774621141651</v>
       </c>
       <c r="AB190">
         <v>2</v>
@@ -24320,7 +24320,7 @@
         <v>2.2463448845797349</v>
       </c>
       <c r="M191">
-        <v>0.14962264220041899</v>
+        <v>0.14962264553027502</v>
       </c>
       <c r="N191">
         <v>5</v>
@@ -24394,7 +24394,7 @@
         <v>4.4779652217641122</v>
       </c>
       <c r="M192">
-        <v>0.14910525633042043</v>
+        <v>0.14910525466573454</v>
       </c>
       <c r="N192">
         <v>1</v>
@@ -24468,7 +24468,7 @@
         <v>3.5677077875551606</v>
       </c>
       <c r="M193">
-        <v>0.14023717339143832</v>
+        <v>0.14023717336856548</v>
       </c>
       <c r="N193">
         <v>4</v>
@@ -24542,7 +24542,7 @@
         <v>2.8927611242711664</v>
       </c>
       <c r="M194">
-        <v>0.13931962379662036</v>
+        <v>0.13931962563896902</v>
       </c>
       <c r="N194">
         <v>5</v>
@@ -24616,7 +24616,7 @@
         <v>6.5424583704960728</v>
       </c>
       <c r="M195">
-        <v>0.13856700866812632</v>
+        <v>0.13856700753742635</v>
       </c>
       <c r="N195">
         <v>1</v>
@@ -24690,7 +24690,7 @@
         <v>6.4203801556278055</v>
       </c>
       <c r="M196">
-        <v>0.13843064211651249</v>
+        <v>0.13843064154268597</v>
       </c>
       <c r="N196">
         <v>2</v>
@@ -24726,7 +24726,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
       <c r="AA196">
-        <v>0.19564143994910621</v>
+        <v>0.19564143994910632</v>
       </c>
       <c r="AB196">
         <v>1</v>
@@ -24764,7 +24764,7 @@
         <v>4.0303121883543458</v>
       </c>
       <c r="M197">
-        <v>0.13797856497490249</v>
+        <v>0.13797856457642885</v>
       </c>
       <c r="N197">
         <v>3</v>
@@ -24800,7 +24800,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="AA197">
-        <v>0.1945226737344663</v>
+        <v>0.19452267373446641</v>
       </c>
       <c r="AB197">
         <v>1</v>
@@ -24838,7 +24838,7 @@
         <v>5.9233546731384319</v>
       </c>
       <c r="M198">
-        <v>0.13128174871008391</v>
+        <v>0.13128174864466768</v>
       </c>
       <c r="N198">
         <v>3</v>
@@ -24912,7 +24912,7 @@
         <v>14.249013385460204</v>
       </c>
       <c r="M199">
-        <v>0.13036824781075027</v>
+        <v>0.13036824762721799</v>
       </c>
       <c r="N199">
         <v>1</v>
@@ -24986,7 +24986,7 @@
         <v>3.85243446061838</v>
       </c>
       <c r="M200">
-        <v>0.12900919416815351</v>
+        <v>0.12900919243486772</v>
       </c>
       <c r="N200">
         <v>5</v>
@@ -25060,7 +25060,7 @@
         <v>7.6025418044793396</v>
       </c>
       <c r="M201">
-        <v>0.12850694566693649</v>
+        <v>0.12850694403551668</v>
       </c>
       <c r="N201">
         <v>4</v>
@@ -25134,7 +25134,7 @@
         <v>5.952874155779682</v>
       </c>
       <c r="M202">
-        <v>0.12767290980412935</v>
+        <v>0.1276729096458602</v>
       </c>
       <c r="N202">
         <v>2</v>
@@ -25170,7 +25170,7 @@
         <v>1.5555000000000001</v>
       </c>
       <c r="AA202">
-        <v>0.1665778403230368</v>
+        <v>0.16657784032303691</v>
       </c>
       <c r="AB202">
         <v>1</v>
@@ -25208,7 +25208,7 @@
         <v>3.9927518380426199</v>
       </c>
       <c r="M203">
-        <v>0.12381978841183013</v>
+        <v>0.12381978701511304</v>
       </c>
       <c r="N203">
         <v>3</v>
@@ -25282,7 +25282,7 @@
         <v>7.527415993642907</v>
       </c>
       <c r="M204">
-        <v>0.1216728534546056</v>
+        <v>0.12167285435142317</v>
       </c>
       <c r="N204">
         <v>1</v>
@@ -25356,7 +25356,7 @@
         <v>3.11445609629406</v>
       </c>
       <c r="M205">
-        <v>0.11979202572636916</v>
+        <v>0.11979202481340501</v>
       </c>
       <c r="N205">
         <v>5</v>
@@ -25392,7 +25392,7 @@
         <v>1.2637499999999999</v>
       </c>
       <c r="AA205">
-        <v>0.1620393478959975</v>
+        <v>0.16203934789599761</v>
       </c>
       <c r="AB205">
         <v>2</v>
@@ -25430,7 +25430,7 @@
         <v>7.0004822438374905</v>
       </c>
       <c r="M206">
-        <v>0.11899338382333939</v>
+        <v>0.11899338064494863</v>
       </c>
       <c r="N206">
         <v>4</v>
@@ -25504,7 +25504,7 @@
         <v>5.1421142304303542</v>
       </c>
       <c r="M207">
-        <v>0.11888943050617436</v>
+        <v>0.11888942933603952</v>
       </c>
       <c r="N207">
         <v>2</v>
@@ -25578,7 +25578,7 @@
         <v>5.978431307057881</v>
       </c>
       <c r="M208">
-        <v>0.11131808139324033</v>
+        <v>0.1113180796955091</v>
       </c>
       <c r="N208">
         <v>3</v>
@@ -25614,7 +25614,7 @@
         <v>1.371</v>
       </c>
       <c r="AA208">
-        <v>0.15409769765752901</v>
+        <v>0.15409769765752909</v>
       </c>
       <c r="AB208">
         <v>5</v>
@@ -25652,7 +25652,7 @@
         <v>4.8901982443564593</v>
       </c>
       <c r="M209">
-        <v>0.10983946367693945</v>
+        <v>0.10983946262222642</v>
       </c>
       <c r="N209">
         <v>4</v>
@@ -25726,7 +25726,7 @@
         <v>5.8512101728553558</v>
       </c>
       <c r="M210">
-        <v>0.1097855895104982</v>
+        <v>0.10978558755619401</v>
       </c>
       <c r="N210">
         <v>5</v>
@@ -25800,7 +25800,7 @@
         <v>3.7903440422943286</v>
       </c>
       <c r="M211">
-        <v>0.10969834947193478</v>
+        <v>0.10969834788238476</v>
       </c>
       <c r="N211">
         <v>2</v>
@@ -25874,7 +25874,7 @@
         <v>11.657319004582414</v>
       </c>
       <c r="M212">
-        <v>0.10939811505206334</v>
+        <v>0.10939811542578338</v>
       </c>
       <c r="N212">
         <v>1</v>
@@ -25910,7 +25910,7 @@
         <v>5.2500000000000003E-3</v>
       </c>
       <c r="AA212">
-        <v>0.14541963288194509</v>
+        <v>0.1454196328819452</v>
       </c>
       <c r="AB212">
         <v>1</v>
@@ -25948,7 +25948,7 @@
         <v>5.2896760368524305</v>
       </c>
       <c r="M213">
-        <v>0.10028077935914192</v>
+        <v>0.10028077872821961</v>
       </c>
       <c r="N213">
         <v>2</v>
@@ -26022,7 +26022,7 @@
         <v>10.462251591165714</v>
       </c>
       <c r="M214">
-        <v>0.10001560941696086</v>
+        <v>0.1000156096943771</v>
       </c>
       <c r="N214">
         <v>1</v>
@@ -26096,7 +26096,7 @@
         <v>5.1887894447067051</v>
       </c>
       <c r="M215">
-        <v>9.9728977006802083E-2</v>
+        <v>9.9728979272933477E-2</v>
       </c>
       <c r="N215">
         <v>3</v>
@@ -26170,7 +26170,7 @@
         <v>2.7429633548309114</v>
       </c>
       <c r="M216">
-        <v>9.9442527168788333E-2</v>
+        <v>9.9442526087806141E-2</v>
       </c>
       <c r="N216">
         <v>4</v>
@@ -26244,7 +26244,7 @@
         <v>5.5988785936592134</v>
       </c>
       <c r="M217">
-        <v>9.8371914071425204E-2</v>
+        <v>9.8371913364759728E-2</v>
       </c>
       <c r="N217">
         <v>5</v>
@@ -26280,7 +26280,7 @@
         <v>0.44850000000000001</v>
       </c>
       <c r="AA217">
-        <v>0.1215062376143629</v>
+        <v>0.12150623761436299</v>
       </c>
       <c r="AB217">
         <v>1</v>
@@ -26318,7 +26318,7 @@
         <v>7.6577528477362726</v>
       </c>
       <c r="M218">
-        <v>9.1536394239918953E-2</v>
+        <v>9.153639322552018E-2</v>
       </c>
       <c r="N218">
         <v>1</v>
@@ -26354,7 +26354,7 @@
         <v>2.775E-2</v>
       </c>
       <c r="AA218">
-        <v>0.1105593582491519</v>
+        <v>0.11055935824915199</v>
       </c>
       <c r="AB218">
         <v>1</v>
@@ -26392,7 +26392,7 @@
         <v>6.479317480163858</v>
       </c>
       <c r="M219">
-        <v>9.0182634000541675E-2</v>
+        <v>9.018263269902603E-2</v>
       </c>
       <c r="N219">
         <v>5</v>
@@ -26466,7 +26466,7 @@
         <v>9.3930770057563322</v>
       </c>
       <c r="M220">
-        <v>9.0082985671158355E-2</v>
+        <v>9.0082983929206745E-2</v>
       </c>
       <c r="N220">
         <v>2</v>
@@ -26540,7 +26540,7 @@
         <v>6.4520740730066866</v>
       </c>
       <c r="M221">
-        <v>8.9755458817273537E-2</v>
+        <v>8.9755457874582556E-2</v>
       </c>
       <c r="N221">
         <v>3</v>
@@ -26614,7 +26614,7 @@
         <v>4.0997703044912086</v>
       </c>
       <c r="M222">
-        <v>8.9617613677312802E-2</v>
+        <v>8.9617614078746077E-2</v>
       </c>
       <c r="N222">
         <v>4</v>
@@ -26688,7 +26688,7 @@
         <v>2.4878657275200533</v>
       </c>
       <c r="M223">
-        <v>8.0656606949139759E-2</v>
+        <v>8.065660637892387E-2</v>
       </c>
       <c r="N223">
         <v>5</v>
@@ -26762,7 +26762,7 @@
         <v>2.640729439571841</v>
       </c>
       <c r="M224">
-        <v>8.0191391966440831E-2</v>
+        <v>8.0191390702155002E-2</v>
       </c>
       <c r="N224">
         <v>4</v>
@@ -26836,7 +26836,7 @@
         <v>3.3209338733188285</v>
       </c>
       <c r="M225">
-        <v>8.0162479030838299E-2</v>
+        <v>8.016247575170983E-2</v>
       </c>
       <c r="N225">
         <v>2</v>
@@ -26910,7 +26910,7 @@
         <v>9.9109903165623674</v>
       </c>
       <c r="M226">
-        <v>7.9472908278644089E-2</v>
+        <v>7.9472907280228267E-2</v>
       </c>
       <c r="N226">
         <v>1</v>
@@ -26984,7 +26984,7 @@
         <v>3.302652567304377</v>
       </c>
       <c r="M227">
-        <v>7.9393992305004477E-2</v>
+        <v>7.939398965296017E-2</v>
       </c>
       <c r="N227">
         <v>3</v>
@@ -27058,7 +27058,7 @@
         <v>6.8287210909871909</v>
       </c>
       <c r="M228">
-        <v>7.1214313204814597E-2</v>
+        <v>7.1214312741997521E-2</v>
       </c>
       <c r="N228">
         <v>1</v>
@@ -27096,7 +27096,7 @@
         <v>3.6501415076229056</v>
       </c>
       <c r="M229">
-        <v>7.0362333247054057E-2</v>
+        <v>7.0362331008818182E-2</v>
       </c>
       <c r="N229">
         <v>3</v>
@@ -27134,7 +27134,7 @@
         <v>3.8036034351178301</v>
       </c>
       <c r="M230">
-        <v>7.02719787604867E-2</v>
+        <v>7.0271978158308018E-2</v>
       </c>
       <c r="N230">
         <v>2</v>
@@ -27172,7 +27172,7 @@
         <v>1.6947667924118182</v>
       </c>
       <c r="M231">
-        <v>6.9840481093379536E-2</v>
+        <v>6.9840479634160013E-2</v>
       </c>
       <c r="N231">
         <v>4</v>
@@ -27210,7 +27210,7 @@
         <v>1.4139025089901296</v>
       </c>
       <c r="M232">
-        <v>6.8972437593252486E-2</v>
+        <v>6.8972436464659267E-2</v>
       </c>
       <c r="N232">
         <v>5</v>
@@ -27248,7 +27248,7 @@
         <v>12.09280715487111</v>
       </c>
       <c r="M233">
-        <v>6.1523305747516993E-2</v>
+        <v>6.1523305829583909E-2</v>
       </c>
       <c r="N233">
         <v>1</v>
@@ -27286,7 +27286,7 @@
         <v>2.1621840072548633</v>
       </c>
       <c r="M234">
-        <v>6.1218908735780876E-2</v>
+        <v>6.1218907720823633E-2</v>
       </c>
       <c r="N234">
         <v>3</v>
@@ -27324,7 +27324,7 @@
         <v>1.3677394962644556</v>
       </c>
       <c r="M235">
-        <v>5.9632046392593188E-2</v>
+        <v>5.963204470849566E-2</v>
       </c>
       <c r="N235">
         <v>4</v>
@@ -27362,7 +27362,7 @@
         <v>1.6147135552380198</v>
       </c>
       <c r="M236">
-        <v>5.8815482747498211E-2</v>
+        <v>5.8815482052610911E-2</v>
       </c>
       <c r="N236">
         <v>2</v>
@@ -27400,7 +27400,7 @@
         <v>0.60859508528960726</v>
       </c>
       <c r="M237">
-        <v>5.7211180345830406E-2</v>
+        <v>5.721117923321517E-2</v>
       </c>
       <c r="N237">
         <v>5</v>
@@ -27438,7 +27438,7 @@
         <v>1.2210230540075988</v>
       </c>
       <c r="M238">
-        <v>5.2734485644046356E-2</v>
+        <v>5.2734483845269117E-2</v>
       </c>
       <c r="N238">
         <v>4</v>
@@ -27476,7 +27476,7 @@
         <v>0.4801289422050885</v>
       </c>
       <c r="M239">
-        <v>5.2036212396566403E-2</v>
+        <v>5.2036213123473694E-2</v>
       </c>
       <c r="N239">
         <v>5</v>
@@ -27514,7 +27514,7 @@
         <v>1.0537794971813335</v>
       </c>
       <c r="M240">
-        <v>5.164255694619397E-2</v>
+        <v>5.1642556165567934E-2</v>
       </c>
       <c r="N240">
         <v>2</v>
@@ -27552,7 +27552,7 @@
         <v>1.1004528264419036</v>
       </c>
       <c r="M241">
-        <v>5.163391488647421E-2</v>
+        <v>5.1633913830282464E-2</v>
       </c>
       <c r="N241">
         <v>3</v>
@@ -27590,7 +27590,7 @@
         <v>3.8005945949856952</v>
       </c>
       <c r="M242">
-        <v>4.8999503694397241E-2</v>
+        <v>4.89995035266554E-2</v>
       </c>
       <c r="N242">
         <v>1</v>
@@ -27628,7 +27628,7 @@
         <v>0.35914497783777927</v>
       </c>
       <c r="M243">
-        <v>4.2158669983938947E-2</v>
+        <v>4.21586701870168E-2</v>
       </c>
       <c r="N243">
         <v>3</v>
@@ -27666,7 +27666,7 @@
         <v>1.0079503920613258</v>
       </c>
       <c r="M244">
-        <v>4.1978100003140388E-2</v>
+        <v>4.197809967351436E-2</v>
       </c>
       <c r="N244">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>3.4314955393325182</v>
       </c>
       <c r="M245">
-        <v>4.1841454705057415E-2</v>
+        <v>4.1841453225873411E-2</v>
       </c>
       <c r="N245">
         <v>1</v>
@@ -27742,7 +27742,7 @@
         <v>0.14292154521625147</v>
       </c>
       <c r="M246">
-        <v>4.1786714515965953E-2</v>
+        <v>4.1786714008610171E-2</v>
       </c>
       <c r="N246">
         <v>4</v>
@@ -27780,7 +27780,7 @@
         <v>0.35719261680347841</v>
       </c>
       <c r="M247">
-        <v>4.1316474580726383E-2</v>
+        <v>4.1316473820463502E-2</v>
       </c>
       <c r="N247">
         <v>5</v>
@@ -27818,7 +27818,7 @@
         <v>0.50888877175615899</v>
       </c>
       <c r="M248">
-        <v>3.288662963608581E-2</v>
+        <v>3.2886629547076954E-2</v>
       </c>
       <c r="N248">
         <v>2</v>
@@ -27856,7 +27856,7 @@
         <v>2.3990027007409775</v>
       </c>
       <c r="M249">
-        <v>3.2484912917136316E-2</v>
+        <v>3.2484912775913255E-2</v>
       </c>
       <c r="N249">
         <v>1</v>
@@ -27894,7 +27894,7 @@
         <v>0.12737255485168475</v>
       </c>
       <c r="M250">
-        <v>3.1909585649099778E-2</v>
+        <v>3.1909585388377168E-2</v>
       </c>
       <c r="N250">
         <v>5</v>
@@ -27932,7 +27932,7 @@
         <v>0.43323922701901374</v>
       </c>
       <c r="M251">
-        <v>3.0800234530574681E-2</v>
+        <v>3.0800234779353623E-2</v>
       </c>
       <c r="N251">
         <v>3</v>
@@ -27970,7 +27970,7 @@
         <v>7.8224804821307642E-2</v>
       </c>
       <c r="M252">
-        <v>2.9091970103256336E-2</v>
+        <v>2.9091969911061506E-2</v>
       </c>
       <c r="N252">
         <v>4</v>
@@ -28008,7 +28008,7 @@
         <v>1.5857345747198989E-3</v>
       </c>
       <c r="M253">
-        <v>2.2286652457043841E-2</v>
+        <v>2.2286651219234507E-2</v>
       </c>
       <c r="N253">
         <v>4</v>
@@ -28046,7 +28046,7 @@
         <v>4.9459464853883386E-3</v>
       </c>
       <c r="M254">
-        <v>2.202838857299488E-2</v>
+        <v>2.2028388368962148E-2</v>
       </c>
       <c r="N254">
         <v>2</v>
@@ -28084,7 +28084,7 @@
         <v>7.2477663824677963E-3</v>
       </c>
       <c r="M255">
-        <v>2.1406250975097709E-2</v>
+        <v>2.1406250717000395E-2</v>
       </c>
       <c r="N255">
         <v>5</v>
@@ -28122,7 +28122,7 @@
         <v>0.10426228215424471</v>
       </c>
       <c r="M256">
-        <v>1.6577694738215916E-2</v>
+        <v>1.6577694489314888E-2</v>
       </c>
       <c r="N256">
         <v>1</v>
@@ -28160,7 +28160,7 @@
         <v>3.9788664266046707E-2</v>
       </c>
       <c r="M257">
-        <v>1.5249256763568631E-2</v>
+        <v>1.5249256654513996E-2</v>
       </c>
       <c r="N257">
         <v>3</v>
@@ -28198,7 +28198,7 @@
         <v>3.1871588871920854E-2</v>
       </c>
       <c r="M258">
-        <v>1.3361792258399801E-2</v>
+        <v>1.3361792222895999E-2</v>
       </c>
       <c r="N258">
         <v>3</v>
@@ -28236,7 +28236,7 @@
         <v>1.3574930671103715E-2</v>
       </c>
       <c r="M259">
-        <v>1.27006245350076E-2</v>
+        <v>1.2700624398979499E-2</v>
       </c>
       <c r="N259">
         <v>4</v>
@@ -28274,7 +28274,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="M260">
-        <v>7.3365339860675992E-3</v>
+        <v>7.3365338256856996E-3</v>
       </c>
       <c r="N260">
         <v>1</v>
@@ -28312,7 +28312,7 @@
         <v>2.3278139783986435E-3</v>
       </c>
       <c r="M261">
-        <v>6.2275441055722998E-3</v>
+        <v>6.2275440712454997E-3</v>
       </c>
       <c r="N261">
         <v>5</v>
@@ -28350,7 +28350,7 @@
         <v>9.164306591800632E-2</v>
       </c>
       <c r="M262">
-        <v>6.2058254411223E-3</v>
+        <v>6.2058253174002995E-3</v>
       </c>
       <c r="N262">
         <v>2</v>
@@ -28388,7 +28388,7 @@
         <v>5.7117319320852357E-3</v>
       </c>
       <c r="M263">
-        <v>8.8291217713710015E-4</v>
+        <v>8.8291215606860001E-4</v>
       </c>
       <c r="N263">
         <v>1</v>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC70E0DC-277E-4B5F-9E32-EA330CAEFE3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49D24D0-4286-4767-9CB0-3A90B41CD17E}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E3E41C6-D236-417B-BD35-F45E7649D7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F77FAF38-999F-4EC3-B234-839EA1C940A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A7A860-0975-4DAC-B683-112C7D32E4B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB2B0BB-F21C-4AC6-81B1-69DF7CD8293B}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAC38A3-DCB1-4357-B503-DCC59567B57F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DBE3ACC-12D9-4621-81F8-1E110C1C535D}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49D24D0-4286-4767-9CB0-3A90B41CD17E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9546808B-329C-4321-B997-C2D730BC23EA}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F77FAF38-999F-4EC3-B234-839EA1C940A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C51771C6-82B4-4C1E-AA54-670BC3C9500D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB2B0BB-F21C-4AC6-81B1-69DF7CD8293B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FED5AB-ED55-408F-9B14-5809A0CF96AF}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DBE3ACC-12D9-4621-81F8-1E110C1C535D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76083E65-338F-4470-9A5C-6320CF406D66}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9546808B-329C-4321-B997-C2D730BC23EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B096C26C-18D5-4E5A-BD33-C0DA0FB01294}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C51771C6-82B4-4C1E-AA54-670BC3C9500D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25A5C76F-C574-4169-805E-F5FC52650135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FED5AB-ED55-408F-9B14-5809A0CF96AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABCAE8A-3674-4086-B22C-A5C59A22FA1B}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76083E65-338F-4470-9A5C-6320CF406D66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D1AF88-6C3F-4DAB-8AE9-6DE975EE0D7A}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B096C26C-18D5-4E5A-BD33-C0DA0FB01294}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0115B320-8727-43F6-8A46-76CCB16E42EA}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25A5C76F-C574-4169-805E-F5FC52650135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A9FA11-5F4C-498D-B3A8-5A4FDC16E5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABCAE8A-3674-4086-B22C-A5C59A22FA1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D836F4DA-1E54-4F1A-9278-C6175CB791BD}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D1AF88-6C3F-4DAB-8AE9-6DE975EE0D7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D73EE1-9FAD-4809-8A52-06DBC0A9C49F}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0115B320-8727-43F6-8A46-76CCB16E42EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492BC9BE-25C6-4471-8658-E862BEDDA619}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A9FA11-5F4C-498D-B3A8-5A4FDC16E5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A81C3B8-C9AE-482C-9EBF-2BF7633F234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D836F4DA-1E54-4F1A-9278-C6175CB791BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD17C855-5215-4813-BC64-985A3503C4A4}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D73EE1-9FAD-4809-8A52-06DBC0A9C49F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A724DDF-C219-4F54-8951-DD2DBEE113BC}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492BC9BE-25C6-4471-8658-E862BEDDA619}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4F8EFD-CAD0-4E92-A03E-22E79D4E3FE1}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A81C3B8-C9AE-482C-9EBF-2BF7633F234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD762BCA-A3FF-42B7-B4E3-A7F2E2C0A2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD17C855-5215-4813-BC64-985A3503C4A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38559C4D-A515-420F-8C21-E5B9BC0FF3A7}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A724DDF-C219-4F54-8951-DD2DBEE113BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C9497E-D090-4E17-A5C1-0ECF3072D382}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4F8EFD-CAD0-4E92-A03E-22E79D4E3FE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB723D6-A428-46E9-931A-83C98A81C315}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD762BCA-A3FF-42B7-B4E3-A7F2E2C0A2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE67BC0-CD25-4165-BF6D-DA19C659B6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38559C4D-A515-420F-8C21-E5B9BC0FF3A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4AB3F-0354-4CA0-A2F0-B16936BD99D3}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C9497E-D090-4E17-A5C1-0ECF3072D382}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7D12F2-77DB-4134-9068-41B8BD6E1021}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB723D6-A428-46E9-931A-83C98A81C315}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71769D25-C890-483F-BF08-E26B414475CF}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE67BC0-CD25-4165-BF6D-DA19C659B6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{322BD2EB-8A9B-4216-9099-63EB88C6E84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E4AB3F-0354-4CA0-A2F0-B16936BD99D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999C48E5-5866-4846-8030-B22AB54E8ABA}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7D12F2-77DB-4134-9068-41B8BD6E1021}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD02540-5899-4893-8668-98832A1C51D7}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71769D25-C890-483F-BF08-E26B414475CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0B21EC-4217-4ACC-B2CB-F844601BF409}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{322BD2EB-8A9B-4216-9099-63EB88C6E84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{857DC2C1-8FF4-4E7E-A871-78345AB69018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999C48E5-5866-4846-8030-B22AB54E8ABA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51576B2-2D70-4F7E-8D2D-5A89CE566E2D}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD02540-5899-4893-8668-98832A1C51D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314FA4A1-658D-49D7-A2E1-F604BF105430}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0B21EC-4217-4ACC-B2CB-F844601BF409}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF941244-AC6F-4122-A03C-D49788512BDC}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{857DC2C1-8FF4-4E7E-A871-78345AB69018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{472CDAC6-83F8-4C94-9ECD-FD9EE46282BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -8768,7 +8768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51576B2-2D70-4F7E-8D2D-5A89CE566E2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95AAD808-3052-4A11-A2BD-E5B6CF363F20}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314FA4A1-658D-49D7-A2E1-F604BF105430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0436BE9-09AC-410D-9639-9C8BDBB523F2}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF941244-AC6F-4122-A03C-D49788512BDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0609CF0E-C7AB-4DA1-A746-BD34C86710C7}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{472CDAC6-83F8-4C94-9ECD-FD9EE46282BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D27B0670-4E1A-4C61-B226-9655B8EC68FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5412" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5414" uniqueCount="1261">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -5450,7 +5450,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -5486,7 +5488,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -8768,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95AAD808-3052-4A11-A2BD-E5B6CF363F20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F400B4D-90DA-4BFC-91C8-BF306082E914}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10876,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0436BE9-09AC-410D-9639-9C8BDBB523F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3586EA31-90F7-4296-92E5-87175DBA753E}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28400,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0609CF0E-C7AB-4DA1-A746-BD34C86710C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FC8ED-B32F-4853-9085-E8E65DCFE9B8}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D27B0670-4E1A-4C61-B226-9655B8EC68FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E922CB-A3BB-4633-A14F-450D15CA98CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8772,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F400B4D-90DA-4BFC-91C8-BF306082E914}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967BC00D-3172-4551-84AB-DC4819178B34}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10880,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3586EA31-90F7-4296-92E5-87175DBA753E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B62AAA80-791D-4EB1-A3E6-8A16E613503D}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28404,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FC8ED-B32F-4853-9085-E8E65DCFE9B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521912C6-C159-4057-B655-DE82A22AAE9D}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E922CB-A3BB-4633-A14F-450D15CA98CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB1FC59-B9C2-46C3-AC75-1D190AD47D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8772,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967BC00D-3172-4551-84AB-DC4819178B34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44D4F4D-978A-4B7D-AB75-DC63F1FF9B30}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10880,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B62AAA80-791D-4EB1-A3E6-8A16E613503D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E111444-1059-457E-8530-0801F73869E3}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28404,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521912C6-C159-4057-B655-DE82A22AAE9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF9591D-90D1-4960-992C-7BE6B9769451}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB1FC59-B9C2-46C3-AC75-1D190AD47D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{207FEB6C-CB47-41C3-8C3A-0BC603BCEDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8772,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44D4F4D-978A-4B7D-AB75-DC63F1FF9B30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB094AA-F3C7-482C-8EDF-E9366F5A201D}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10880,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E111444-1059-457E-8530-0801F73869E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F8A8A2-79D8-43A4-B15F-AC53F8FAF865}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28404,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF9591D-90D1-4960-992C-7BE6B9769451}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E476E86D-6072-47C0-8B3D-E8440AAB4B82}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{207FEB6C-CB47-41C3-8C3A-0BC603BCEDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B6683C8-A297-43C0-8A3A-5A0A86CFF9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8772,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB094AA-F3C7-482C-8EDF-E9366F5A201D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9781D36-AD64-42D7-9E26-8FC9634F8B3F}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10880,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F8A8A2-79D8-43A4-B15F-AC53F8FAF865}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5921A6F9-9DBF-4A64-8DF3-F94EC5D731F8}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28404,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E476E86D-6072-47C0-8B3D-E8440AAB4B82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727CCDCA-41C4-4E27-83FB-19566382DBC2}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B6683C8-A297-43C0-8A3A-5A0A86CFF9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B58C54FC-9857-4950-A706-33D46631625B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8772,7 +8772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9781D36-AD64-42D7-9E26-8FC9634F8B3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551C3B0E-F800-484C-AD01-458A00903AD7}">
   <dimension ref="B9:N64"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10880,7 +10880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5921A6F9-9DBF-4A64-8DF3-F94EC5D731F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F46191A-5DEA-4F41-A931-C3C9E7047610}">
   <dimension ref="B9:AB263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -28404,7 +28404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727CCDCA-41C4-4E27-83FB-19566382DBC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6272F942-86D2-4DF4-AF07-2898B00D0ACC}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D0D9039-78F5-41D9-87EB-BAE0C0758BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1495B10D-3050-431A-A754-7BC09840FAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4685,7 +4685,7 @@
         <v>19</v>
       </c>
       <c r="L11">
-        <v>103.874</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -4717,7 +4717,7 @@
         <v>19</v>
       </c>
       <c r="L12">
-        <v>35.629296975962831</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -7551,7 +7551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A7F0B5-86E2-4DA1-9C65-9CFAC487BCCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC7736AE-1147-49C2-8242-A239C4D7E316}">
   <dimension ref="B9:M125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11629,7 +11629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31BB9816-0D4D-4697-8FCF-76AF3CEA6BA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E5B44B-A6CF-429A-9009-002F2D25BEEF}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15159,7 +15159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE15BD9-03DB-4064-B2B9-BD11D9C60398}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985F5B80-ACD0-4179-B156-00A54572F068}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BC934C9-5589-4DCE-9D3C-6BAFDD320948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B151E4F5-A926-453F-A45D-5DF7173A051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7368,7 +7368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5092181-7EE6-4873-9E1D-E67411D1CF9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A983A24F-42B3-49FF-AA15-860C4E346219}">
   <dimension ref="B9:M125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7444,10 +7444,10 @@
         <v>408</v>
       </c>
       <c r="L11">
-        <v>26.74724429956963</v>
+        <v>7.3197223495603936</v>
       </c>
       <c r="M11">
-        <v>0.20350084845053121</v>
+        <v>0.19561810160537049</v>
       </c>
     </row>
     <row r="12" spans="2:13">
@@ -7479,10 +7479,10 @@
         <v>409</v>
       </c>
       <c r="L12">
-        <v>21.366289952931421</v>
+        <v>3.9912529292571399</v>
       </c>
       <c r="M12">
-        <v>0.1947106712348359</v>
+        <v>0.1899800578090565</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -7514,10 +7514,10 @@
         <v>410</v>
       </c>
       <c r="L13">
-        <v>3.9145216176661872</v>
+        <v>4.2706680673701092</v>
       </c>
       <c r="M13">
-        <v>0.19095732871447141</v>
+        <v>0.188954058034423</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -7549,10 +7549,10 @@
         <v>411</v>
       </c>
       <c r="L14">
-        <v>10.584480100467061</v>
+        <v>13.981359478801604</v>
       </c>
       <c r="M14">
-        <v>0.1955186246072641</v>
+        <v>0.1936437094766659</v>
       </c>
     </row>
     <row r="15" spans="2:13">
@@ -7584,10 +7584,10 @@
         <v>412</v>
       </c>
       <c r="L15">
-        <v>3.5932182489017483</v>
+        <v>28.21764385202707</v>
       </c>
       <c r="M15">
-        <v>0.19293409646713011</v>
+        <v>0.20234236171720621</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -7619,10 +7619,10 @@
         <v>413</v>
       </c>
       <c r="L16">
-        <v>7.3197223495603936</v>
+        <v>4.8768513119274983</v>
       </c>
       <c r="M16">
-        <v>0.19561810160537049</v>
+        <v>0.19168291824194039</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -7654,10 +7654,10 @@
         <v>414</v>
       </c>
       <c r="L17">
-        <v>6.5955572568339393</v>
+        <v>13.870317588084811</v>
       </c>
       <c r="M17">
-        <v>0.18943140755189861</v>
+        <v>0.19845632226614379</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -7689,10 +7689,10 @@
         <v>415</v>
       </c>
       <c r="L18">
-        <v>1.490796752963657</v>
+        <v>1.3237102416747595</v>
       </c>
       <c r="M18">
-        <v>0.15646436566344529</v>
+        <v>0.15616948935531069</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -7724,10 +7724,10 @@
         <v>416</v>
       </c>
       <c r="L19">
-        <v>1.9378492019965576</v>
+        <v>0.95475881280981956</v>
       </c>
       <c r="M19">
-        <v>0.17716280596748141</v>
+        <v>0.1629573257982378</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -7759,10 +7759,10 @@
         <v>417</v>
       </c>
       <c r="L20">
-        <v>2.5300973808703642</v>
+        <v>3.609473356098265</v>
       </c>
       <c r="M20">
-        <v>0.16422559634387821</v>
+        <v>0.170844591510006</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -7794,10 +7794,10 @@
         <v>418</v>
       </c>
       <c r="L21">
-        <v>15.196652549346981</v>
+        <v>5.4075373048565565</v>
       </c>
       <c r="M21">
-        <v>0.20556150420322589</v>
+        <v>0.19725515194825349</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -7829,10 +7829,10 @@
         <v>419</v>
       </c>
       <c r="L22">
-        <v>6.5597482488587069</v>
+        <v>1.9378492019965576</v>
       </c>
       <c r="M22">
-        <v>0.20658065151446431</v>
+        <v>0.17716280596748141</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -7864,10 +7864,10 @@
         <v>420</v>
       </c>
       <c r="L23">
-        <v>48.135699205830811</v>
+        <v>3.5932182489017483</v>
       </c>
       <c r="M23">
-        <v>0.2036711237727431</v>
+        <v>0.19293409646713011</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -7899,10 +7899,10 @@
         <v>421</v>
       </c>
       <c r="L24">
-        <v>5.5763453532487768</v>
+        <v>17.548211545188931</v>
       </c>
       <c r="M24">
-        <v>0.20574204696870979</v>
+        <v>0.20545381979143959</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -7934,10 +7934,10 @@
         <v>422</v>
       </c>
       <c r="L25">
-        <v>1.4881792514726941</v>
+        <v>3.8211717975884008</v>
       </c>
       <c r="M25">
-        <v>0.19488790250529889</v>
+        <v>0.20608159323988301</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -7969,10 +7969,10 @@
         <v>423</v>
       </c>
       <c r="L26">
-        <v>1.3204249692280936</v>
+        <v>20.684451442302088</v>
       </c>
       <c r="M26">
-        <v>0.20552004538219579</v>
+        <v>0.205148492342488</v>
       </c>
     </row>
     <row r="27" spans="2:13">
@@ -8004,10 +8004,10 @@
         <v>424</v>
       </c>
       <c r="L27">
-        <v>3.4506289697397312</v>
+        <v>2.9424673149973128</v>
       </c>
       <c r="M27">
-        <v>0.1805585680013394</v>
+        <v>0.18964760118957211</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8039,10 +8039,10 @@
         <v>425</v>
       </c>
       <c r="L28">
-        <v>4.131699630346219</v>
+        <v>1.2120950895642146</v>
       </c>
       <c r="M28">
-        <v>0.20101223398249279</v>
+        <v>0.20016056548956479</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -8074,10 +8074,10 @@
         <v>426</v>
       </c>
       <c r="L29">
-        <v>3.3030540962828425</v>
+        <v>5.329525145496671</v>
       </c>
       <c r="M29">
-        <v>0.19535226674410949</v>
+        <v>0.2057749843939507</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -8109,10 +8109,10 @@
         <v>427</v>
       </c>
       <c r="L30">
-        <v>11.956486097626851</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="M30">
-        <v>0.19754059655134781</v>
+        <v>0.1744368403907999</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -8144,10 +8144,10 @@
         <v>428</v>
       </c>
       <c r="L31">
-        <v>18.705374089956845</v>
+        <v>2.0804999999999998</v>
       </c>
       <c r="M31">
-        <v>0.19547594320212069</v>
+        <v>0.17684069581882239</v>
       </c>
     </row>
     <row r="32" spans="2:13">
@@ -8179,10 +8179,10 @@
         <v>429</v>
       </c>
       <c r="L32">
-        <v>47.600357900164468</v>
+        <v>0.90225</v>
       </c>
       <c r="M32">
-        <v>0.2002428339996872</v>
+        <v>0.1745168327240296</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -8214,10 +8214,10 @@
         <v>430</v>
       </c>
       <c r="L33">
-        <v>12.888</v>
+        <v>0.42975000000000002</v>
       </c>
       <c r="M33">
-        <v>0.18360840981650769</v>
+        <v>0.17065936942800919</v>
       </c>
     </row>
     <row r="34" spans="2:13">
@@ -8249,10 +8249,10 @@
         <v>431</v>
       </c>
       <c r="L34">
-        <v>17.353092620536618</v>
+        <v>1.0305</v>
       </c>
       <c r="M34">
-        <v>0.19032720309577039</v>
+        <v>0.1698810046979061</v>
       </c>
     </row>
     <row r="35" spans="2:13">
@@ -8284,10 +8284,10 @@
         <v>432</v>
       </c>
       <c r="L35">
-        <v>30.125163330581923</v>
+        <v>0.156</v>
       </c>
       <c r="M35">
-        <v>0.1831879446233054</v>
+        <v>0.16788539947934419</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -8319,10 +8319,10 @@
         <v>433</v>
       </c>
       <c r="L36">
-        <v>20.737776277095385</v>
+        <v>0.14849999999999999</v>
       </c>
       <c r="M36">
-        <v>0.18727666948885041</v>
+        <v>0.1635527861912483</v>
       </c>
     </row>
     <row r="37" spans="2:13">
@@ -8354,10 +8354,10 @@
         <v>434</v>
       </c>
       <c r="L37">
-        <v>7.9500000000000001E-2</v>
+        <v>0.87944277553898109</v>
       </c>
       <c r="M37">
-        <v>0.16799176096210611</v>
+        <v>0.1749399025772358</v>
       </c>
     </row>
     <row r="38" spans="2:13">
@@ -8389,10 +8389,10 @@
         <v>435</v>
       </c>
       <c r="L38">
-        <v>0.45600000000000002</v>
+        <v>1.0237499999999999</v>
       </c>
       <c r="M38">
-        <v>0.17197323013571211</v>
+        <v>0.17087282870907899</v>
       </c>
     </row>
     <row r="39" spans="2:13">
@@ -8424,10 +8424,10 @@
         <v>436</v>
       </c>
       <c r="L39">
-        <v>3.2745000000000002</v>
+        <v>34.203659787790635</v>
       </c>
       <c r="M39">
-        <v>0.18328451263693049</v>
+        <v>0.20277787100359901</v>
       </c>
     </row>
     <row r="40" spans="2:13">
@@ -8459,10 +8459,10 @@
         <v>437</v>
       </c>
       <c r="L40">
-        <v>8.0497499999999995</v>
+        <v>4.383</v>
       </c>
       <c r="M40">
-        <v>0.1762901555861498</v>
+        <v>0.17652814756647231</v>
       </c>
     </row>
     <row r="41" spans="2:13">
@@ -8494,10 +8494,10 @@
         <v>438</v>
       </c>
       <c r="L41">
-        <v>0.24149999999999999</v>
+        <v>19.960372548613204</v>
       </c>
       <c r="M41">
-        <v>0.17650889842067891</v>
+        <v>0.1775042022863807</v>
       </c>
     </row>
     <row r="42" spans="2:13">
@@ -8529,10 +8529,10 @@
         <v>439</v>
       </c>
       <c r="L42">
-        <v>0.24149999999999999</v>
+        <v>63.682122079669604</v>
       </c>
       <c r="M42">
-        <v>0.16397426920350811</v>
+        <v>0.21228801975659189</v>
       </c>
     </row>
     <row r="43" spans="2:13">
@@ -8564,10 +8564,10 @@
         <v>440</v>
       </c>
       <c r="L43">
-        <v>2.157</v>
+        <v>58.318268922653999</v>
       </c>
       <c r="M43">
-        <v>0.18306865946146281</v>
+        <v>0.2026093216444774</v>
       </c>
     </row>
     <row r="44" spans="2:13">
@@ -8599,10 +8599,10 @@
         <v>441</v>
       </c>
       <c r="L44">
-        <v>15.215999999999999</v>
+        <v>45.783632322458843</v>
       </c>
       <c r="M44">
-        <v>0.18351140183283879</v>
+        <v>0.22140145266700439</v>
       </c>
     </row>
     <row r="45" spans="2:13">
@@ -8634,10 +8634,10 @@
         <v>442</v>
       </c>
       <c r="L45">
-        <v>3.1957499999999999</v>
+        <v>94.676676509970278</v>
       </c>
       <c r="M45">
-        <v>0.1772430818805347</v>
+        <v>0.2101752042956109</v>
       </c>
     </row>
     <row r="46" spans="2:13">
@@ -8669,10 +8669,10 @@
         <v>443</v>
       </c>
       <c r="L46">
-        <v>0.34949999999999998</v>
+        <v>51.645742424896213</v>
       </c>
       <c r="M46">
-        <v>0.1777749394439489</v>
+        <v>0.19882298850703761</v>
       </c>
     </row>
     <row r="47" spans="2:13">
@@ -8704,10 +8704,10 @@
         <v>444</v>
       </c>
       <c r="L47">
-        <v>0.156</v>
+        <v>31.338638517489738</v>
       </c>
       <c r="M47">
-        <v>0.16788539947934419</v>
+        <v>0.20604696473512721</v>
       </c>
     </row>
     <row r="48" spans="2:13">
@@ -8739,10 +8739,10 @@
         <v>445</v>
       </c>
       <c r="L48">
-        <v>0.14849999999999999</v>
+        <v>19.145251097865469</v>
       </c>
       <c r="M48">
-        <v>0.1635527861912483</v>
+        <v>0.2282812262662671</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -8774,10 +8774,10 @@
         <v>446</v>
       </c>
       <c r="L49">
-        <v>0.87944277553898109</v>
+        <v>26.661859285174934</v>
       </c>
       <c r="M49">
-        <v>0.1749399025772358</v>
+        <v>0.23163247227506359</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -8809,10 +8809,10 @@
         <v>447</v>
       </c>
       <c r="L50">
-        <v>1.0237499999999999</v>
+        <v>4.7240832790723051</v>
       </c>
       <c r="M50">
-        <v>0.17087282870907899</v>
+        <v>0.19130911733602449</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -8844,10 +8844,10 @@
         <v>448</v>
       </c>
       <c r="L51">
-        <v>33.478409787790632</v>
+        <v>12.893100432315391</v>
       </c>
       <c r="M51">
-        <v>0.20317821624175711</v>
+        <v>0.191094128148071</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -8879,10 +8879,10 @@
         <v>449</v>
       </c>
       <c r="L52">
-        <v>7.2487500000000002</v>
+        <v>15.333</v>
       </c>
       <c r="M52">
-        <v>0.18071699677685499</v>
+        <v>0.18991301593133281</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -8914,10 +8914,10 @@
         <v>450</v>
       </c>
       <c r="L53">
-        <v>16.895122548613202</v>
+        <v>30.287784706562448</v>
       </c>
       <c r="M53">
-        <v>0.17643049970261529</v>
+        <v>0.19469458211456281</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -8949,10 +8949,10 @@
         <v>451</v>
       </c>
       <c r="L54">
-        <v>1.0125</v>
+        <v>22.242000000000001</v>
       </c>
       <c r="M54">
-        <v>0.17235703288632279</v>
+        <v>0.18968339342226501</v>
       </c>
     </row>
     <row r="55" spans="2:13">
@@ -8984,10 +8984,10 @@
         <v>452</v>
       </c>
       <c r="L55">
-        <v>1.99275</v>
+        <v>12.43049589068308</v>
       </c>
       <c r="M55">
-        <v>0.17716870357485881</v>
+        <v>0.19774694895145389</v>
       </c>
     </row>
     <row r="56" spans="2:13">
@@ -9019,10 +9019,10 @@
         <v>453</v>
       </c>
       <c r="L56">
-        <v>0.70799999999999996</v>
+        <v>4.9545000000000003</v>
       </c>
       <c r="M56">
-        <v>0.1744368403907999</v>
+        <v>0.18343191505321699</v>
       </c>
     </row>
     <row r="57" spans="2:13">
@@ -9054,10 +9054,10 @@
         <v>454</v>
       </c>
       <c r="L57">
-        <v>5.4217500000000003</v>
+        <v>1.3665</v>
       </c>
       <c r="M57">
-        <v>0.1792414004798337</v>
+        <v>0.1808772482040098</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -9089,10 +9089,10 @@
         <v>455</v>
       </c>
       <c r="L58">
-        <v>7.4249999999999997E-2</v>
+        <v>8.9877547998367646</v>
       </c>
       <c r="M58">
-        <v>0.18016780280501241</v>
+        <v>0.1911068856548151</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -9159,10 +9159,10 @@
         <v>457</v>
       </c>
       <c r="L60">
-        <v>5.8747499999999997</v>
+        <v>6.7422400346620455</v>
       </c>
       <c r="M60">
-        <v>0.18316250309891019</v>
+        <v>0.18162469862157599</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -9194,10 +9194,10 @@
         <v>458</v>
       </c>
       <c r="L61">
-        <v>1.7655000000000001</v>
+        <v>19.329927537704947</v>
       </c>
       <c r="M61">
-        <v>0.17957405082600819</v>
+        <v>0.1837164749039073</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -9229,10 +9229,10 @@
         <v>459</v>
       </c>
       <c r="L62">
-        <v>8.4090000000000007</v>
+        <v>4.9695</v>
       </c>
       <c r="M62">
-        <v>0.1811797527363237</v>
+        <v>0.1822092693183002</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -9264,10 +9264,10 @@
         <v>460</v>
       </c>
       <c r="L63">
-        <v>44.301749999999998</v>
+        <v>20.959218324874239</v>
       </c>
       <c r="M63">
-        <v>0.1895733903197121</v>
+        <v>0.23015774746645831</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -9299,10 +9299,10 @@
         <v>461</v>
       </c>
       <c r="L64">
-        <v>19.429500000000001</v>
+        <v>31.014696934585121</v>
       </c>
       <c r="M64">
-        <v>0.17825140137848799</v>
+        <v>0.2140287598254875</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -9334,10 +9334,10 @@
         <v>462</v>
       </c>
       <c r="L65">
-        <v>1.3919999999999999</v>
+        <v>39.393078287984075</v>
       </c>
       <c r="M65">
-        <v>0.16972993180359461</v>
+        <v>0.22636170586922449</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -9369,10 +9369,10 @@
         <v>463</v>
       </c>
       <c r="L66">
-        <v>7.9995000000000003</v>
+        <v>21.329513703273719</v>
       </c>
       <c r="M66">
-        <v>0.1703687629704132</v>
+        <v>0.2170178645743317</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -9404,10 +9404,10 @@
         <v>464</v>
       </c>
       <c r="L67">
-        <v>0.90225</v>
+        <v>44.915634639686459</v>
       </c>
       <c r="M67">
-        <v>0.1745168327240296</v>
+        <v>0.2026938283731273</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -9439,10 +9439,10 @@
         <v>465</v>
       </c>
       <c r="L68">
-        <v>0.42975000000000002</v>
+        <v>7.78340431694087</v>
       </c>
       <c r="M68">
-        <v>0.17065936942800919</v>
+        <v>0.2160576463236453</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -9474,10 +9474,10 @@
         <v>466</v>
       </c>
       <c r="L69">
-        <v>1.0305</v>
+        <v>8.2717940638731591</v>
       </c>
       <c r="M69">
-        <v>0.1698810046979061</v>
+        <v>0.18512318990115609</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -9509,10 +9509,10 @@
         <v>467</v>
       </c>
       <c r="L70">
-        <v>14.859845549854393</v>
+        <v>12.604071732513232</v>
       </c>
       <c r="M70">
-        <v>0.1916163980629671</v>
+        <v>0.1953641199022971</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -9544,10 +9544,10 @@
         <v>468</v>
       </c>
       <c r="L71">
-        <v>8.9960047998367649</v>
+        <v>5.6530945566751054</v>
       </c>
       <c r="M71">
-        <v>0.1911086212848076</v>
+        <v>0.18438337043001871</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -9579,10 +9579,10 @@
         <v>469</v>
       </c>
       <c r="L72">
-        <v>21.799755733900287</v>
+        <v>7.4235702996807422</v>
       </c>
       <c r="M72">
-        <v>0.1852257625018861</v>
+        <v>0.2012886107692069</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -9614,10 +9614,10 @@
         <v>470</v>
       </c>
       <c r="L73">
-        <v>12.75749589068308</v>
+        <v>7.0481364824239572</v>
       </c>
       <c r="M73">
-        <v>0.1975359241843983</v>
+        <v>0.18325028495971579</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -9649,10 +9649,10 @@
         <v>471</v>
       </c>
       <c r="L74">
-        <v>33.06</v>
+        <v>5.4109929761160274</v>
       </c>
       <c r="M74">
-        <v>0.19030151695207151</v>
+        <v>0.17851828392540839</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -9684,10 +9684,10 @@
         <v>472</v>
       </c>
       <c r="L75">
-        <v>17.390999999999998</v>
+        <v>1.5182791605088741</v>
       </c>
       <c r="M75">
-        <v>0.19161488059043461</v>
+        <v>0.18064984020562261</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -9719,10 +9719,10 @@
         <v>473</v>
       </c>
       <c r="L76">
-        <v>58.868130730367454</v>
+        <v>2.4526493307316448</v>
       </c>
       <c r="M76">
-        <v>0.19820629810362739</v>
+        <v>0.17961844664020429</v>
       </c>
     </row>
     <row r="77" spans="2:13">
@@ -9754,10 +9754,10 @@
         <v>474</v>
       </c>
       <c r="L77">
-        <v>16.217822681745979</v>
+        <v>30.929580262702071</v>
       </c>
       <c r="M77">
-        <v>0.18962485807836471</v>
+        <v>0.23340041584314489</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -9789,10 +9789,10 @@
         <v>475</v>
       </c>
       <c r="L78">
-        <v>5.3497500000000002</v>
+        <v>9.2133418027367053</v>
       </c>
       <c r="M78">
-        <v>0.1800658316403764</v>
+        <v>0.21903384104979179</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -9824,10 +9824,10 @@
         <v>476</v>
       </c>
       <c r="L79">
-        <v>86.375249811136669</v>
+        <v>45.030225755041762</v>
       </c>
       <c r="M79">
-        <v>0.21022469549478739</v>
+        <v>0.22315800231900221</v>
       </c>
     </row>
     <row r="80" spans="2:13">
@@ -9859,10 +9859,10 @@
         <v>477</v>
       </c>
       <c r="L80">
-        <v>62.800024661918386</v>
+        <v>37.907022428713496</v>
       </c>
       <c r="M80">
-        <v>0.20379387434686799</v>
+        <v>0.2077303517310197</v>
       </c>
     </row>
     <row r="81" spans="2:13">
@@ -9894,10 +9894,10 @@
         <v>478</v>
       </c>
       <c r="L81">
-        <v>49.426269136309841</v>
+        <v>48.641605728516204</v>
       </c>
       <c r="M81">
-        <v>0.221070867410913</v>
+        <v>0.2136408086419864</v>
       </c>
     </row>
     <row r="82" spans="2:13">
@@ -9929,10 +9929,10 @@
         <v>479</v>
       </c>
       <c r="L82">
-        <v>54.459170078392368</v>
+        <v>15.897437272368096</v>
       </c>
       <c r="M82">
-        <v>0.20724230040458469</v>
+        <v>0.20795010350353249</v>
       </c>
     </row>
     <row r="83" spans="2:13">
@@ -9964,10 +9964,10 @@
         <v>480</v>
       </c>
       <c r="L83">
-        <v>50.467084116314695</v>
+        <v>7.6350252914597281</v>
       </c>
       <c r="M83">
-        <v>0.215248347278057</v>
+        <v>0.2022067969997674</v>
       </c>
     </row>
     <row r="84" spans="2:13">
@@ -9999,10 +9999,10 @@
         <v>481</v>
       </c>
       <c r="L84">
-        <v>25.808580420591536</v>
+        <v>14.684868844937309</v>
       </c>
       <c r="M84">
-        <v>0.1981576487517612</v>
+        <v>0.20599907341787929</v>
       </c>
     </row>
     <row r="85" spans="2:13">
@@ -10034,10 +10034,10 @@
         <v>482</v>
       </c>
       <c r="L85">
-        <v>64.011225710383826</v>
+        <v>23.825875134446761</v>
       </c>
       <c r="M85">
-        <v>0.20226508674861729</v>
+        <v>0.2138107184384998</v>
       </c>
     </row>
     <row r="86" spans="2:13">
@@ -10069,10 +10069,10 @@
         <v>483</v>
       </c>
       <c r="L86">
-        <v>14.984176386042574</v>
+        <v>29.638500000000001</v>
       </c>
       <c r="M86">
-        <v>0.229007708360497</v>
+        <v>0.19033342281512841</v>
       </c>
     </row>
     <row r="87" spans="2:13">
@@ -10104,10 +10104,10 @@
         <v>484</v>
       </c>
       <c r="L87">
-        <v>16.019099682661761</v>
+        <v>5.8140000000000001</v>
       </c>
       <c r="M87">
-        <v>0.21677641280796789</v>
+        <v>0.1814608528789548</v>
       </c>
     </row>
     <row r="88" spans="2:13">
@@ -10139,10 +10139,10 @@
         <v>485</v>
       </c>
       <c r="L88">
-        <v>14.69942322072523</v>
+        <v>23.389500000000002</v>
       </c>
       <c r="M88">
-        <v>0.2305328559526845</v>
+        <v>0.18656279129484471</v>
       </c>
     </row>
     <row r="89" spans="2:13">
@@ -10174,10 +10174,10 @@
         <v>486</v>
       </c>
       <c r="L89">
-        <v>21.663744697439149</v>
+        <v>12.526218104221192</v>
       </c>
       <c r="M89">
-        <v>0.2335254953975428</v>
+        <v>0.1944006210832441</v>
       </c>
     </row>
     <row r="90" spans="2:13">
@@ -10209,10 +10209,10 @@
         <v>487</v>
       </c>
       <c r="L90">
-        <v>71.870066479494469</v>
+        <v>8.7494999999999994</v>
       </c>
       <c r="M90">
-        <v>0.22138870489146409</v>
+        <v>0.17011448820127009</v>
       </c>
     </row>
     <row r="91" spans="2:13">
@@ -10244,10 +10244,10 @@
         <v>488</v>
       </c>
       <c r="L91">
-        <v>38.191105007559514</v>
+        <v>19.429500000000001</v>
       </c>
       <c r="M91">
-        <v>0.22003034016004669</v>
+        <v>0.17825140137848799</v>
       </c>
     </row>
     <row r="92" spans="2:13">
@@ -10279,10 +10279,10 @@
         <v>489</v>
       </c>
       <c r="L92">
-        <v>18.860724008558098</v>
+        <v>13.204499999999999</v>
       </c>
       <c r="M92">
-        <v>0.20861797011763261</v>
+        <v>0.18298457797568271</v>
       </c>
     </row>
     <row r="93" spans="2:13">
@@ -10314,10 +10314,10 @@
         <v>490</v>
       </c>
       <c r="L93">
-        <v>31.952216568027502</v>
+        <v>22.705750387019794</v>
       </c>
       <c r="M93">
-        <v>0.19539980186918621</v>
+        <v>0.18988285307846151</v>
       </c>
     </row>
     <row r="94" spans="2:13">
@@ -10349,10 +10349,10 @@
         <v>491</v>
       </c>
       <c r="L94">
-        <v>7.1756882252313936</v>
+        <v>39.734003271901024</v>
       </c>
       <c r="M94">
-        <v>0.18437328856166901</v>
+        <v>0.18385411049004069</v>
       </c>
     </row>
     <row r="95" spans="2:13">
@@ -10384,10 +10384,10 @@
         <v>492</v>
       </c>
       <c r="L95">
-        <v>7.8965874118777952</v>
+        <v>1.6890000000000001</v>
       </c>
       <c r="M95">
-        <v>0.19905058901527081</v>
+        <v>0.18324082787545401</v>
       </c>
     </row>
     <row r="96" spans="2:13">
@@ -10419,10 +10419,10 @@
         <v>493</v>
       </c>
       <c r="L96">
-        <v>2.5926982198291761</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="M96">
-        <v>0.1804631403121196</v>
+        <v>0.16362926153910051</v>
       </c>
     </row>
     <row r="97" spans="2:13">
@@ -10454,10 +10454,10 @@
         <v>494</v>
       </c>
       <c r="L97">
-        <v>2.3086123420754094</v>
+        <v>0.23774999999999999</v>
       </c>
       <c r="M97">
-        <v>0.17810584179604749</v>
+        <v>0.17665881785013701</v>
       </c>
     </row>
     <row r="98" spans="2:13">
@@ -10489,10 +10489,10 @@
         <v>495</v>
       </c>
       <c r="L98">
-        <v>10.286947753315458</v>
+        <v>0.33150000000000002</v>
       </c>
       <c r="M98">
-        <v>0.19779798050223249</v>
+        <v>0.17752736088208571</v>
       </c>
     </row>
     <row r="99" spans="2:13">
@@ -10524,10 +10524,10 @@
         <v>496</v>
       </c>
       <c r="L99">
-        <v>7.3731093695170999</v>
+        <v>2.4464999999999999</v>
       </c>
       <c r="M99">
-        <v>0.1808156676032478</v>
+        <v>0.17261068680339819</v>
       </c>
     </row>
     <row r="100" spans="2:13">
@@ -10559,10 +10559,10 @@
         <v>497</v>
       </c>
       <c r="L100">
-        <v>7.7682073930015179</v>
+        <v>0.2145</v>
       </c>
       <c r="M100">
-        <v>0.20089344606517359</v>
+        <v>0.17021717738047659</v>
       </c>
     </row>
     <row r="101" spans="2:13">
@@ -10594,10 +10594,10 @@
         <v>498</v>
       </c>
       <c r="L101">
-        <v>38.707045784497502</v>
+        <v>15.69525</v>
       </c>
       <c r="M101">
-        <v>0.23247215542614791</v>
+        <v>0.18347770348108219</v>
       </c>
     </row>
     <row r="102" spans="2:13">
@@ -10629,10 +10629,10 @@
         <v>499</v>
       </c>
       <c r="L102">
-        <v>6.1320660597404846</v>
+        <v>7.3815</v>
       </c>
       <c r="M102">
-        <v>0.21969062333598119</v>
+        <v>0.1805371732071149</v>
       </c>
     </row>
     <row r="103" spans="2:13">
@@ -10664,10 +10664,10 @@
         <v>500</v>
       </c>
       <c r="L103">
-        <v>41.479463841919411</v>
+        <v>5.0339999999999998</v>
       </c>
       <c r="M103">
-        <v>0.22105013693654971</v>
+        <v>0.17673696410513001</v>
       </c>
     </row>
     <row r="104" spans="2:13">
@@ -10699,10 +10699,10 @@
         <v>501</v>
       </c>
       <c r="L104">
-        <v>23.610749999999999</v>
+        <v>42.147206133399365</v>
       </c>
       <c r="M104">
-        <v>0.19087284182219411</v>
+        <v>0.19457876399727669</v>
       </c>
     </row>
     <row r="105" spans="2:13">
@@ -10734,10 +10734,10 @@
         <v>502</v>
       </c>
       <c r="L105">
-        <v>19.50375</v>
+        <v>41.726273386122017</v>
       </c>
       <c r="M105">
-        <v>0.18767109483933619</v>
+        <v>0.1972752366886657</v>
       </c>
     </row>
     <row r="106" spans="2:13">
@@ -10769,10 +10769,10 @@
         <v>503</v>
       </c>
       <c r="L106">
-        <v>66.950064377864791</v>
+        <v>1.3303012307087763</v>
       </c>
       <c r="M106">
-        <v>0.19645406746394109</v>
+        <v>0.20265857068007281</v>
       </c>
     </row>
     <row r="107" spans="2:13">
@@ -10804,10 +10804,10 @@
         <v>504</v>
       </c>
       <c r="L107">
-        <v>35.389738091051498</v>
+        <v>21.037914020583063</v>
       </c>
       <c r="M107">
-        <v>0.19818079997273849</v>
+        <v>0.1994237557677917</v>
       </c>
     </row>
     <row r="108" spans="2:13">
@@ -10839,10 +10839,10 @@
         <v>505</v>
       </c>
       <c r="L108">
-        <v>44.716752386549238</v>
+        <v>14.702249999999999</v>
       </c>
       <c r="M108">
-        <v>0.19926264410000541</v>
+        <v>0.18779408495945729</v>
       </c>
     </row>
     <row r="109" spans="2:13">
@@ -10874,10 +10874,10 @@
         <v>506</v>
       </c>
       <c r="L109">
-        <v>18.862172753030631</v>
+        <v>15.534000000000001</v>
       </c>
       <c r="M109">
-        <v>0.19455907359141009</v>
+        <v>0.1897345894459537</v>
       </c>
     </row>
     <row r="110" spans="2:13">
@@ -10909,10 +10909,10 @@
         <v>507</v>
       </c>
       <c r="L110">
-        <v>12.748218104221191</v>
+        <v>68.042105186701164</v>
       </c>
       <c r="M110">
-        <v>0.19433964797545189</v>
+        <v>0.19694006243892601</v>
       </c>
     </row>
     <row r="111" spans="2:13">
@@ -10944,10 +10944,10 @@
         <v>508</v>
       </c>
       <c r="L111">
-        <v>13.428147873514895</v>
+        <v>43.43652270216927</v>
       </c>
       <c r="M111">
-        <v>0.20356469232746771</v>
+        <v>0.19568535232108891</v>
       </c>
     </row>
     <row r="112" spans="2:13">
@@ -10979,10 +10979,10 @@
         <v>509</v>
       </c>
       <c r="L112">
-        <v>1.5370228088720619</v>
+        <v>63.902786745830014</v>
       </c>
       <c r="M112">
-        <v>0.2077523181883269</v>
+        <v>0.20163604169662949</v>
       </c>
     </row>
     <row r="113" spans="2:13">
@@ -11014,10 +11014,10 @@
         <v>510</v>
       </c>
       <c r="L113">
-        <v>5.8693399186588291</v>
+        <v>24.919216820057812</v>
       </c>
       <c r="M113">
-        <v>0.2009704779348209</v>
+        <v>0.19617641660771079</v>
       </c>
     </row>
     <row r="114" spans="2:13">
@@ -11049,10 +11049,10 @@
         <v>511</v>
       </c>
       <c r="L114">
-        <v>1.1532607266374395</v>
+        <v>17.442599831437619</v>
       </c>
       <c r="M114">
-        <v>0.1596943947718672</v>
+        <v>0.19746026341411449</v>
       </c>
     </row>
     <row r="115" spans="2:13">
@@ -11084,10 +11084,10 @@
         <v>512</v>
       </c>
       <c r="L115">
-        <v>6.955061804170598E-2</v>
+        <v>1.9011734607434354</v>
       </c>
       <c r="M115">
-        <v>0.16870498304975501</v>
+        <v>0.20757865467249431</v>
       </c>
     </row>
     <row r="116" spans="2:13">
@@ -11119,10 +11119,10 @@
         <v>513</v>
       </c>
       <c r="L116">
-        <v>3.3944125271035701</v>
+        <v>0.79446578034560333</v>
       </c>
       <c r="M116">
-        <v>0.20284219553050409</v>
+        <v>0.2051820092932628</v>
       </c>
     </row>
     <row r="117" spans="2:13">
@@ -11154,10 +11154,10 @@
         <v>514</v>
       </c>
       <c r="L117">
-        <v>3.6004209042317972</v>
+        <v>8.6046425413806524</v>
       </c>
       <c r="M117">
-        <v>0.19092585103959611</v>
+        <v>0.20478548547266431</v>
       </c>
     </row>
     <row r="118" spans="2:13">
@@ -11189,10 +11189,10 @@
         <v>515</v>
       </c>
       <c r="L118">
-        <v>5.2981836188673936</v>
+        <v>31.326120090267271</v>
       </c>
       <c r="M118">
-        <v>0.1785896449641472</v>
+        <v>0.20080866738482561</v>
       </c>
     </row>
     <row r="119" spans="2:13">
@@ -11224,10 +11224,10 @@
         <v>516</v>
       </c>
       <c r="L119">
-        <v>9.5701371149225025</v>
+        <v>6.6613548520415211</v>
       </c>
       <c r="M119">
-        <v>0.18675098962924591</v>
+        <v>0.1755567625829097</v>
       </c>
     </row>
     <row r="120" spans="2:13">
@@ -11259,10 +11259,10 @@
         <v>517</v>
       </c>
       <c r="L120">
-        <v>6.6613548520415211</v>
+        <v>3.2182916630974701</v>
       </c>
       <c r="M120">
-        <v>0.1755567625829097</v>
+        <v>0.19809347445011299</v>
       </c>
     </row>
     <row r="121" spans="2:13">
@@ -11294,10 +11294,10 @@
         <v>518</v>
       </c>
       <c r="L121">
-        <v>9.0385247812983174</v>
+        <v>9.5701371149225025</v>
       </c>
       <c r="M121">
-        <v>0.2071893729402273</v>
+        <v>0.18675098962924591</v>
       </c>
     </row>
     <row r="122" spans="2:13">
@@ -11329,10 +11329,10 @@
         <v>519</v>
       </c>
       <c r="L122">
-        <v>3.630299387788281</v>
+        <v>1.1532607266374395</v>
       </c>
       <c r="M122">
-        <v>0.19878335068620209</v>
+        <v>0.1596943947718672</v>
       </c>
     </row>
     <row r="123" spans="2:13">
@@ -11364,10 +11364,10 @@
         <v>520</v>
       </c>
       <c r="L123">
-        <v>39.664065892506009</v>
+        <v>6.955061804170598E-2</v>
       </c>
       <c r="M123">
-        <v>0.2129564305417242</v>
+        <v>0.16870498304975501</v>
       </c>
     </row>
     <row r="124" spans="2:13">
@@ -11399,10 +11399,10 @@
         <v>521</v>
       </c>
       <c r="L124">
-        <v>14.684868844937309</v>
+        <v>3.3944125271035701</v>
       </c>
       <c r="M124">
-        <v>0.20599907341787929</v>
+        <v>0.20284219553050409</v>
       </c>
     </row>
     <row r="125" spans="2:13">
@@ -11434,10 +11434,10 @@
         <v>522</v>
       </c>
       <c r="L125">
-        <v>18.389071242107757</v>
+        <v>3.6004209042317972</v>
       </c>
       <c r="M125">
-        <v>0.2136912037958752</v>
+        <v>0.19092585103959611</v>
       </c>
     </row>
   </sheetData>
@@ -11446,7 +11446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B020B30A-42FD-4A9F-900F-1358D4E8C46F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D0C7B4-7750-42F8-BC4B-E78CF3579D08}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11594,10 +11594,10 @@
         <v>792</v>
       </c>
       <c r="Y11">
-        <v>47.240250000000003</v>
+        <v>54.979500000000002</v>
       </c>
       <c r="Z11">
-        <v>0.46942157387883998</v>
+        <v>0.4682008873118963</v>
       </c>
     </row>
     <row r="12" spans="2:26">
@@ -11629,10 +11629,10 @@
         <v>662</v>
       </c>
       <c r="L12">
-        <v>9.1089937926910061</v>
+        <v>12.404103898825962</v>
       </c>
       <c r="M12">
-        <v>9.8847483176049994E-2</v>
+        <v>0.112128823851027</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -11662,10 +11662,10 @@
         <v>793</v>
       </c>
       <c r="Y12">
-        <v>38.134500000000003</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="Z12">
-        <v>0.4760862042906871</v>
+        <v>0.35144418181618881</v>
       </c>
     </row>
     <row r="13" spans="2:26">
@@ -11697,10 +11697,10 @@
         <v>663</v>
       </c>
       <c r="L13">
-        <v>9.5926767059877864</v>
+        <v>6.1276234637439133</v>
       </c>
       <c r="M13">
-        <v>0.1129113579926567</v>
+        <v>9.4081669365557702E-2</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -11730,10 +11730,10 @@
         <v>794</v>
       </c>
       <c r="Y13">
-        <v>46.530749999999998</v>
+        <v>36.586500000000001</v>
       </c>
       <c r="Z13">
-        <v>0.46278855538482139</v>
+        <v>0.4759976278834937</v>
       </c>
     </row>
     <row r="14" spans="2:26">
@@ -11765,10 +11765,10 @@
         <v>664</v>
       </c>
       <c r="L14">
-        <v>7.4816578037471135</v>
+        <v>0.85621181691755843</v>
       </c>
       <c r="M14">
-        <v>0.12851292841627501</v>
+        <v>9.0668099088234103E-2</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -11798,10 +11798,10 @@
         <v>795</v>
       </c>
       <c r="Y14">
-        <v>21.307500000000001</v>
+        <v>53.094000000000001</v>
       </c>
       <c r="Z14">
-        <v>0.41711974501825511</v>
+        <v>0.46237715489702708</v>
       </c>
     </row>
     <row r="15" spans="2:26">
@@ -11833,10 +11833,10 @@
         <v>665</v>
       </c>
       <c r="L15">
-        <v>0.68626868080864378</v>
+        <v>2.2628760328229185</v>
       </c>
       <c r="M15">
-        <v>8.9560344305505094E-2</v>
+        <v>0.1238708109113873</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -11866,10 +11866,10 @@
         <v>796</v>
       </c>
       <c r="Y15">
-        <v>47.747999999999998</v>
+        <v>55.56</v>
       </c>
       <c r="Z15">
-        <v>0.47257717662294479</v>
+        <v>0.45627760502955012</v>
       </c>
     </row>
     <row r="16" spans="2:26">
@@ -11901,10 +11901,10 @@
         <v>666</v>
       </c>
       <c r="L16">
-        <v>2.2628760328229185</v>
+        <v>0.43370118574988076</v>
       </c>
       <c r="M16">
-        <v>0.1238708109113873</v>
+        <v>0.10138851292069349</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -11934,10 +11934,10 @@
         <v>797</v>
       </c>
       <c r="Y16">
-        <v>40.677</v>
+        <v>43.858499999999999</v>
       </c>
       <c r="Z16">
-        <v>0.49212043621524448</v>
+        <v>0.36156165762891301</v>
       </c>
     </row>
     <row r="17" spans="2:26">
@@ -11969,10 +11969,10 @@
         <v>667</v>
       </c>
       <c r="L17">
-        <v>0.43370118574988076</v>
+        <v>2.5150267058852811</v>
       </c>
       <c r="M17">
-        <v>0.10138851292069349</v>
+        <v>8.7681833650751606E-2</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -12002,10 +12002,10 @@
         <v>798</v>
       </c>
       <c r="Y17">
-        <v>60.146250000000002</v>
+        <v>42.080249999999999</v>
       </c>
       <c r="Z17">
-        <v>0.43953008578306552</v>
+        <v>0.34203679621906968</v>
       </c>
     </row>
     <row r="18" spans="2:26">
@@ -12037,10 +12037,10 @@
         <v>668</v>
       </c>
       <c r="L18">
-        <v>2.5150267058852811</v>
+        <v>2.885493974180005</v>
       </c>
       <c r="M18">
-        <v>8.7681833650751606E-2</v>
+        <v>0.14764341619346269</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -12070,10 +12070,10 @@
         <v>799</v>
       </c>
       <c r="Y18">
-        <v>39.273000000000003</v>
+        <v>19.922999999999998</v>
       </c>
       <c r="Z18">
-        <v>0.29409377231263367</v>
+        <v>0.26434489688175378</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -12105,10 +12105,10 @@
         <v>669</v>
       </c>
       <c r="L19">
-        <v>1.2387965264903888</v>
+        <v>10.563746678268352</v>
       </c>
       <c r="M19">
-        <v>0.17511604804729169</v>
+        <v>0.1762422335004816</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -12138,10 +12138,10 @@
         <v>800</v>
       </c>
       <c r="Y19">
-        <v>44.889749999999999</v>
+        <v>51.427500000000002</v>
       </c>
       <c r="Z19">
-        <v>0.36237444194151858</v>
+        <v>0.2836738817128282</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -12173,10 +12173,10 @@
         <v>670</v>
       </c>
       <c r="L20">
-        <v>4.5447948235000659</v>
+        <v>7.4816578037471135</v>
       </c>
       <c r="M20">
-        <v>0.1766345367644237</v>
+        <v>0.12851292841627501</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -12206,10 +12206,10 @@
         <v>801</v>
       </c>
       <c r="Y20">
-        <v>27.66375</v>
+        <v>40.677</v>
       </c>
       <c r="Z20">
-        <v>0.30284661864143841</v>
+        <v>0.49212043621524448</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -12241,10 +12241,10 @@
         <v>671</v>
       </c>
       <c r="L21">
-        <v>10.563746678268352</v>
+        <v>1.6691823226567941</v>
       </c>
       <c r="M21">
-        <v>0.1762422335004816</v>
+        <v>0.15723508939914779</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -12274,10 +12274,10 @@
         <v>802</v>
       </c>
       <c r="Y21">
-        <v>21.581250000000001</v>
+        <v>60.146250000000002</v>
       </c>
       <c r="Z21">
-        <v>0.31421957894729519</v>
+        <v>0.43953008578306552</v>
       </c>
     </row>
     <row r="22" spans="2:26">
@@ -12309,10 +12309,10 @@
         <v>672</v>
       </c>
       <c r="L22">
-        <v>2.885493974180005</v>
+        <v>3.7614311754340659</v>
       </c>
       <c r="M22">
-        <v>0.14764341619346269</v>
+        <v>0.21587774284891351</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -12342,10 +12342,10 @@
         <v>803</v>
       </c>
       <c r="Y22">
-        <v>43.858499999999999</v>
+        <v>39.273000000000003</v>
       </c>
       <c r="Z22">
-        <v>0.36156165762891301</v>
+        <v>0.29409377231263367</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -12377,10 +12377,10 @@
         <v>673</v>
       </c>
       <c r="L23">
-        <v>3.8581854917370815</v>
+        <v>7.6463375414566821</v>
       </c>
       <c r="M23">
-        <v>0.15556037151470789</v>
+        <v>0.22284490118078781</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -12410,10 +12410,10 @@
         <v>804</v>
       </c>
       <c r="Y23">
-        <v>42.080249999999999</v>
+        <v>44.889749999999999</v>
       </c>
       <c r="Z23">
-        <v>0.34203679621906968</v>
+        <v>0.36237444194151858</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -12445,10 +12445,10 @@
         <v>674</v>
       </c>
       <c r="L24">
-        <v>2.4836923620575391</v>
+        <v>11.221871479411517</v>
       </c>
       <c r="M24">
-        <v>0.16311252525788919</v>
+        <v>0.34329463129026588</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -12478,10 +12478,10 @@
         <v>805</v>
       </c>
       <c r="Y24">
-        <v>19.922999999999998</v>
+        <v>27.66375</v>
       </c>
       <c r="Z24">
-        <v>0.26434489688175378</v>
+        <v>0.30284661864143841</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -12513,10 +12513,10 @@
         <v>675</v>
       </c>
       <c r="L25">
-        <v>0.34625959029864795</v>
+        <v>18.008891115565412</v>
       </c>
       <c r="M25">
-        <v>0.16712424320989541</v>
+        <v>0.2474712287536284</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -12546,10 +12546,10 @@
         <v>806</v>
       </c>
       <c r="Y25">
-        <v>51.427500000000002</v>
+        <v>21.581250000000001</v>
       </c>
       <c r="Z25">
-        <v>0.2836738817128282</v>
+        <v>0.31421957894729519</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -12581,10 +12581,10 @@
         <v>676</v>
       </c>
       <c r="L26">
-        <v>0.65440271382024695</v>
+        <v>24.891089921419841</v>
       </c>
       <c r="M26">
-        <v>0.1270319550249287</v>
+        <v>0.3055932594772704</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -12649,10 +12649,10 @@
         <v>677</v>
       </c>
       <c r="L27">
-        <v>0.35051099632091098</v>
+        <v>30.317738700900584</v>
       </c>
       <c r="M27">
-        <v>9.6656114851391806E-2</v>
+        <v>0.30507645183795778</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -12717,10 +12717,10 @@
         <v>678</v>
       </c>
       <c r="L28">
-        <v>5.5005105319204732</v>
+        <v>0.34625959029864795</v>
       </c>
       <c r="M28">
-        <v>0.1032555480201208</v>
+        <v>0.16712424320989541</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -12750,10 +12750,10 @@
         <v>809</v>
       </c>
       <c r="Y28">
-        <v>2.6655000000000002</v>
+        <v>3.4402499999999998</v>
       </c>
       <c r="Z28">
-        <v>0.216099010559541</v>
+        <v>0.25959278503990429</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -12785,10 +12785,10 @@
         <v>679</v>
       </c>
       <c r="L29">
-        <v>1.6757541426674882</v>
+        <v>0.65440271382024695</v>
       </c>
       <c r="M29">
-        <v>0.1650429037380152</v>
+        <v>0.1270319550249287</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -12818,10 +12818,10 @@
         <v>810</v>
       </c>
       <c r="Y29">
-        <v>8.8432499999999994</v>
+        <v>13.389749999999999</v>
       </c>
       <c r="Z29">
-        <v>0.24069927265958951</v>
+        <v>0.2859142138357344</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -12853,10 +12853,10 @@
         <v>680</v>
       </c>
       <c r="L30">
-        <v>0.39959553615654331</v>
+        <v>2.2677057834637031</v>
       </c>
       <c r="M30">
-        <v>0.1072096692643303</v>
+        <v>0.13270702416333019</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -12886,10 +12886,10 @@
         <v>811</v>
       </c>
       <c r="Y30">
-        <v>3.4402499999999998</v>
+        <v>6.9757499999999997</v>
       </c>
       <c r="Z30">
-        <v>0.25959278503990429</v>
+        <v>0.32134323151488431</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -12921,10 +12921,10 @@
         <v>681</v>
       </c>
       <c r="L31">
-        <v>1.7832075556426605</v>
+        <v>2.4836923620575391</v>
       </c>
       <c r="M31">
-        <v>0.17291513693338831</v>
+        <v>0.16311252525788919</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -12954,10 +12954,10 @@
         <v>812</v>
       </c>
       <c r="Y31">
-        <v>13.389749999999999</v>
+        <v>38.154000000000003</v>
       </c>
       <c r="Z31">
-        <v>0.2859142138357344</v>
+        <v>0.3277877869879024</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -12989,10 +12989,10 @@
         <v>682</v>
       </c>
       <c r="L32">
-        <v>2.2195844391122765</v>
+        <v>4.0763322608214585</v>
       </c>
       <c r="M32">
-        <v>0.1603834390284819</v>
+        <v>0.17777395285655839</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -13022,10 +13022,10 @@
         <v>813</v>
       </c>
       <c r="Y32">
-        <v>6.9757499999999997</v>
+        <v>26.765999999999998</v>
       </c>
       <c r="Z32">
-        <v>0.32134323151488431</v>
+        <v>0.44231071876838968</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -13057,10 +13057,10 @@
         <v>683</v>
       </c>
       <c r="L33">
-        <v>5.5304311809856452</v>
+        <v>2.5731779960501728</v>
       </c>
       <c r="M33">
-        <v>0.2123572416473124</v>
+        <v>0.19326289879692229</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -13090,10 +13090,10 @@
         <v>814</v>
       </c>
       <c r="Y33">
-        <v>38.154000000000003</v>
+        <v>35.325000000000003</v>
       </c>
       <c r="Z33">
-        <v>0.3277877869879024</v>
+        <v>0.43449987376462901</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -13125,10 +13125,10 @@
         <v>684</v>
       </c>
       <c r="L34">
-        <v>3.7614311754340659</v>
+        <v>4.0509443596880574</v>
       </c>
       <c r="M34">
-        <v>0.21587774284891351</v>
+        <v>0.18682452602484509</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -13158,10 +13158,10 @@
         <v>815</v>
       </c>
       <c r="Y34">
-        <v>26.765999999999998</v>
+        <v>38.589750000000002</v>
       </c>
       <c r="Z34">
-        <v>0.44231071876838968</v>
+        <v>0.3180495664751426</v>
       </c>
     </row>
     <row r="35" spans="2:26">
@@ -13193,10 +13193,10 @@
         <v>685</v>
       </c>
       <c r="L35">
-        <v>1.9040172385939969</v>
+        <v>2.4544193550494788</v>
       </c>
       <c r="M35">
-        <v>0.1572998090862405</v>
+        <v>0.16013241630924799</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -13226,10 +13226,10 @@
         <v>816</v>
       </c>
       <c r="Y35">
-        <v>35.325000000000003</v>
+        <v>28.707000000000001</v>
       </c>
       <c r="Z35">
-        <v>0.43449987376462901</v>
+        <v>0.37980101398892369</v>
       </c>
     </row>
     <row r="36" spans="2:26">
@@ -13261,10 +13261,10 @@
         <v>686</v>
       </c>
       <c r="L36">
-        <v>11.884376191048085</v>
+        <v>0.35051099632091098</v>
       </c>
       <c r="M36">
-        <v>0.2732889293422246</v>
+        <v>9.6656114851391806E-2</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -13294,10 +13294,10 @@
         <v>817</v>
       </c>
       <c r="Y36">
-        <v>26.259</v>
+        <v>2.6655000000000002</v>
       </c>
       <c r="Z36">
-        <v>0.373169235387384</v>
+        <v>0.216099010559541</v>
       </c>
     </row>
     <row r="37" spans="2:26">
@@ -13329,10 +13329,10 @@
         <v>687</v>
       </c>
       <c r="L37">
-        <v>10.042628949933583</v>
+        <v>5.5005105319204732</v>
       </c>
       <c r="M37">
-        <v>0.23820220806482659</v>
+        <v>0.1032555480201208</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -13362,10 +13362,10 @@
         <v>818</v>
       </c>
       <c r="Y37">
-        <v>38.589750000000002</v>
+        <v>11.651999999999999</v>
       </c>
       <c r="Z37">
-        <v>0.3180495664751426</v>
+        <v>0.2381177314344618</v>
       </c>
     </row>
     <row r="38" spans="2:26">
@@ -13397,10 +13397,10 @@
         <v>688</v>
       </c>
       <c r="L38">
-        <v>11.221871479411517</v>
+        <v>1.6757541426674882</v>
       </c>
       <c r="M38">
-        <v>0.34329463129026588</v>
+        <v>0.1650429037380152</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -13430,10 +13430,10 @@
         <v>819</v>
       </c>
       <c r="Y38">
-        <v>13.428000000000001</v>
+        <v>10.619249999999999</v>
       </c>
       <c r="Z38">
-        <v>0.30947763066506601</v>
+        <v>0.33050183966316582</v>
       </c>
     </row>
     <row r="39" spans="2:26">
@@ -13465,10 +13465,10 @@
         <v>689</v>
       </c>
       <c r="L39">
-        <v>7.6463375414566821</v>
+        <v>0.39959553615654331</v>
       </c>
       <c r="M39">
-        <v>0.22284490118078781</v>
+        <v>0.1072096692643303</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -13498,10 +13498,10 @@
         <v>820</v>
       </c>
       <c r="Y39">
-        <v>23.709</v>
+        <v>21.260999999999999</v>
       </c>
       <c r="Z39">
-        <v>0.53340010550729644</v>
+        <v>0.54289480010017288</v>
       </c>
     </row>
     <row r="40" spans="2:26">
@@ -13533,10 +13533,10 @@
         <v>690</v>
       </c>
       <c r="L40">
-        <v>49.086666974214374</v>
+        <v>1.7832075556426605</v>
       </c>
       <c r="M40">
-        <v>0.308797255699787</v>
+        <v>0.17291513693338831</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -13601,10 +13601,10 @@
         <v>691</v>
       </c>
       <c r="L41">
-        <v>14.176079891703212</v>
+        <v>33.414563514376454</v>
       </c>
       <c r="M41">
-        <v>0.1221312740068858</v>
+        <v>0.30971299533872781</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -13669,10 +13669,10 @@
         <v>692</v>
       </c>
       <c r="L42">
-        <v>2.3372365278937242</v>
+        <v>2.8320779450600302</v>
       </c>
       <c r="M42">
-        <v>0.1157811350779776</v>
+        <v>0.19139890752231881</v>
       </c>
     </row>
     <row r="43" spans="2:26">
@@ -13704,10 +13704,10 @@
         <v>693</v>
       </c>
       <c r="L43">
-        <v>4.2648673086521249</v>
+        <v>24.434551684764973</v>
       </c>
       <c r="M43">
-        <v>0.1018524220358768</v>
+        <v>0.19028064145394111</v>
       </c>
     </row>
     <row r="44" spans="2:26">
@@ -13739,10 +13739,10 @@
         <v>694</v>
       </c>
       <c r="L44">
-        <v>2.8571480649629004</v>
+        <v>18.904558868579112</v>
       </c>
       <c r="M44">
-        <v>0.28915876947611158</v>
+        <v>0.29452200235220533</v>
       </c>
     </row>
     <row r="45" spans="2:26">
@@ -13774,10 +13774,10 @@
         <v>695</v>
       </c>
       <c r="L45">
-        <v>33.414563514376454</v>
+        <v>15.478330347836801</v>
       </c>
       <c r="M45">
-        <v>0.30971299533872781</v>
+        <v>0.222177819888773</v>
       </c>
     </row>
     <row r="46" spans="2:26">
@@ -13809,10 +13809,10 @@
         <v>696</v>
       </c>
       <c r="L46">
-        <v>2.8320779450600302</v>
+        <v>1.4999429400795936</v>
       </c>
       <c r="M46">
-        <v>0.19139890752231881</v>
+        <v>0.21843142318229231</v>
       </c>
     </row>
     <row r="47" spans="2:26">
@@ -13844,10 +13844,10 @@
         <v>697</v>
       </c>
       <c r="L47">
-        <v>24.434551684764973</v>
+        <v>55.863958629218203</v>
       </c>
       <c r="M47">
-        <v>0.19028064145394111</v>
+        <v>0.34785235138275827</v>
       </c>
     </row>
     <row r="48" spans="2:26">
@@ -13879,10 +13879,10 @@
         <v>698</v>
       </c>
       <c r="L48">
-        <v>18.904558868579112</v>
+        <v>17.068804920122925</v>
       </c>
       <c r="M48">
-        <v>0.29452200235220533</v>
+        <v>0.1097075246412334</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -13914,10 +13914,10 @@
         <v>699</v>
       </c>
       <c r="L49">
-        <v>15.478330347836801</v>
+        <v>3.0756142181007986</v>
       </c>
       <c r="M49">
-        <v>0.222177819888773</v>
+        <v>0.1400841935812667</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -13949,10 +13949,10 @@
         <v>700</v>
       </c>
       <c r="L50">
-        <v>0.80973624203950822</v>
+        <v>13.001084297219549</v>
       </c>
       <c r="M50">
-        <v>0.1402179322845909</v>
+        <v>0.16897605417432451</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -13984,10 +13984,10 @@
         <v>701</v>
       </c>
       <c r="L51">
-        <v>3.2067222321080848</v>
+        <v>0.80973624203950822</v>
       </c>
       <c r="M51">
-        <v>0.1065607310314662</v>
+        <v>0.1402179322845909</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -14019,10 +14019,10 @@
         <v>702</v>
       </c>
       <c r="L52">
-        <v>0.66271354737797783</v>
+        <v>3.2067222321080848</v>
       </c>
       <c r="M52">
-        <v>0.16309819780041621</v>
+        <v>0.1065607310314662</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -14054,10 +14054,10 @@
         <v>703</v>
       </c>
       <c r="L53">
-        <v>1.8183767824138508</v>
+        <v>0.66271354737797783</v>
       </c>
       <c r="M53">
-        <v>0.21095850339443861</v>
+        <v>0.16309819780041621</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -14089,10 +14089,10 @@
         <v>704</v>
       </c>
       <c r="L54">
-        <v>0.24904319237866104</v>
+        <v>1.8183767824138508</v>
       </c>
       <c r="M54">
-        <v>0.25748619553898999</v>
+        <v>0.21095850339443861</v>
       </c>
     </row>
     <row r="55" spans="2:13">
@@ -14124,10 +14124,10 @@
         <v>705</v>
       </c>
       <c r="L55">
-        <v>8.2047875916663029E-2</v>
+        <v>0.24904319237866104</v>
       </c>
       <c r="M55">
-        <v>0.13592110504470081</v>
+        <v>0.25748619553898999</v>
       </c>
     </row>
     <row r="56" spans="2:13">
@@ -14159,10 +14159,10 @@
         <v>706</v>
       </c>
       <c r="L56">
-        <v>11.861012832193515</v>
+        <v>8.2047875916663029E-2</v>
       </c>
       <c r="M56">
-        <v>0.1087933355996048</v>
+        <v>0.13592110504470081</v>
       </c>
     </row>
     <row r="57" spans="2:13">
@@ -14194,10 +14194,10 @@
         <v>707</v>
       </c>
       <c r="L57">
-        <v>0.74143826937354373</v>
+        <v>14.176079891703212</v>
       </c>
       <c r="M57">
-        <v>8.8201244876213003E-2</v>
+        <v>0.1221312740068858</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -14229,10 +14229,10 @@
         <v>708</v>
       </c>
       <c r="L58">
-        <v>5.5201095579611916</v>
+        <v>2.3372365278937242</v>
       </c>
       <c r="M58">
-        <v>0.1283226559519017</v>
+        <v>0.1157811350779776</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -14264,10 +14264,10 @@
         <v>709</v>
       </c>
       <c r="L59">
-        <v>6.8285247240880329</v>
+        <v>4.2648673086521249</v>
       </c>
       <c r="M59">
-        <v>9.8264036008851294E-2</v>
+        <v>0.1018524220358768</v>
       </c>
     </row>
     <row r="60" spans="2:13">
@@ -14299,10 +14299,10 @@
         <v>710</v>
       </c>
       <c r="L60">
-        <v>14.065249575687433</v>
+        <v>2.8571480649629004</v>
       </c>
       <c r="M60">
-        <v>0.1320696072360909</v>
+        <v>0.28915876947611158</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -14334,10 +14334,10 @@
         <v>711</v>
       </c>
       <c r="L61">
-        <v>23.754587797332221</v>
+        <v>11.861012832193515</v>
       </c>
       <c r="M61">
-        <v>0.2346271116098167</v>
+        <v>0.1087933355996048</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -14369,10 +14369,10 @@
         <v>712</v>
       </c>
       <c r="L62">
-        <v>9.3799037679336319</v>
+        <v>0.74143826937354373</v>
       </c>
       <c r="M62">
-        <v>0.12698739870760559</v>
+        <v>8.8201244876213003E-2</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -14404,10 +14404,10 @@
         <v>713</v>
       </c>
       <c r="L63">
-        <v>3.5275797249830152</v>
+        <v>5.5201095579611916</v>
       </c>
       <c r="M63">
-        <v>9.5677447841151203E-2</v>
+        <v>0.1283226559519017</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -14439,10 +14439,10 @@
         <v>714</v>
       </c>
       <c r="L64">
-        <v>0.89663971235601181</v>
+        <v>6.8285247240880329</v>
       </c>
       <c r="M64">
-        <v>9.3606642611398602E-2</v>
+        <v>9.8264036008851294E-2</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -14474,10 +14474,10 @@
         <v>715</v>
       </c>
       <c r="L65">
-        <v>5.9305458091691294</v>
+        <v>14.065249575687433</v>
       </c>
       <c r="M65">
-        <v>9.6567218538318997E-2</v>
+        <v>0.1320696072360909</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -14509,10 +14509,10 @@
         <v>716</v>
       </c>
       <c r="L66">
-        <v>0.78969451031655336</v>
+        <v>9.3799037679336319</v>
       </c>
       <c r="M66">
-        <v>8.5651825963848904E-2</v>
+        <v>0.12698739870760559</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -14544,10 +14544,10 @@
         <v>717</v>
       </c>
       <c r="L67">
-        <v>0.5190595734350465</v>
+        <v>42.785830383290261</v>
       </c>
       <c r="M67">
-        <v>0.10857562776850541</v>
+        <v>0.27336739424382489</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -14579,10 +14579,10 @@
         <v>718</v>
       </c>
       <c r="L68">
-        <v>0.29505146981926272</v>
+        <v>11.412035826311723</v>
       </c>
       <c r="M68">
-        <v>0.1235068952905013</v>
+        <v>0.11866286907907619</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -14614,10 +14614,10 @@
         <v>719</v>
       </c>
       <c r="L69">
-        <v>0.28737649325389003</v>
+        <v>16.249041763152853</v>
       </c>
       <c r="M69">
-        <v>0.1208623014671094</v>
+        <v>0.12558896879944331</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -14649,10 +14649,10 @@
         <v>720</v>
       </c>
       <c r="L70">
-        <v>7.8693705940085819</v>
+        <v>18.319832830101969</v>
       </c>
       <c r="M70">
-        <v>0.1194525598481516</v>
+        <v>0.1300705694164489</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -14684,10 +14684,10 @@
         <v>721</v>
       </c>
       <c r="L71">
-        <v>19.787589902082505</v>
+        <v>23.427729543154012</v>
       </c>
       <c r="M71">
-        <v>0.1240437231884286</v>
+        <v>0.25027188308965431</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -14719,10 +14719,10 @@
         <v>722</v>
       </c>
       <c r="L72">
-        <v>18.319832830101969</v>
+        <v>6.7510585544323067</v>
       </c>
       <c r="M72">
-        <v>0.1300705694164489</v>
+        <v>0.15514978062049739</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -14754,10 +14754,10 @@
         <v>723</v>
       </c>
       <c r="L73">
-        <v>6.7551756478058005</v>
+        <v>3.5275797249830152</v>
       </c>
       <c r="M73">
-        <v>0.15510592681409949</v>
+        <v>9.5677447841151203E-2</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -14789,10 +14789,10 @@
         <v>724</v>
       </c>
       <c r="L74">
-        <v>42.458972129112055</v>
+        <v>0.89663971235601181</v>
       </c>
       <c r="M74">
-        <v>0.2822979932934005</v>
+        <v>9.3606642611398602E-2</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -14824,10 +14824,10 @@
         <v>725</v>
       </c>
       <c r="L75">
-        <v>1.4999429400795936</v>
+        <v>5.9305458091691294</v>
       </c>
       <c r="M75">
-        <v>0.21843142318229231</v>
+        <v>9.6567218538318997E-2</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -14859,10 +14859,10 @@
         <v>726</v>
       </c>
       <c r="L76">
-        <v>55.863958629218203</v>
+        <v>0.78969451031655336</v>
       </c>
       <c r="M76">
-        <v>0.34785235138275827</v>
+        <v>8.5651825963848904E-2</v>
       </c>
     </row>
     <row r="77" spans="2:13">
@@ -14894,10 +14894,10 @@
         <v>727</v>
       </c>
       <c r="L77">
-        <v>17.068804920122925</v>
+        <v>0.5190595734350465</v>
       </c>
       <c r="M77">
-        <v>0.1097075246412334</v>
+        <v>0.10857562776850541</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -14929,10 +14929,10 @@
         <v>728</v>
       </c>
       <c r="L78">
-        <v>3.0756142181007986</v>
+        <v>0.29505146981926272</v>
       </c>
       <c r="M78">
-        <v>0.1400841935812667</v>
+        <v>0.1235068952905013</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -14964,10 +14964,10 @@
         <v>729</v>
       </c>
       <c r="L79">
-        <v>13.001084297219549</v>
+        <v>0.28737649325389003</v>
       </c>
       <c r="M79">
-        <v>0.16897605417432451</v>
+        <v>0.1208623014671094</v>
       </c>
     </row>
   </sheetData>
@@ -14976,7 +14976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86345DD-9DA2-41B6-AB50-57D8BA4A7819}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E41CBF-FE6F-469B-B741-BA37888D72D5}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B151E4F5-A926-453F-A45D-5DF7173A051D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AE53C37-4EE5-450F-9290-D95C1AC2EC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="844">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -2673,7 +2673,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2821,8 +2821,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2914,6 +2921,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -3128,7 +3140,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3148,8 +3160,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -3541,6 +3554,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3560,8 +3574,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3954,423 +3969,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -4378,32 +4066,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -4411,37 +4099,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -4453,120 +4141,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -6112,25 +6135,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -6176,7 +6199,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -6221,7 +6244,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -6263,7 +6286,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -7368,7 +7391,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A983A24F-42B3-49FF-AA15-860C4E346219}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7B0286-670D-403A-B273-CD897B262E99}">
   <dimension ref="B9:M125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7444,10 +7467,10 @@
         <v>408</v>
       </c>
       <c r="L11">
-        <v>7.3197223495603936</v>
+        <v>3.7459236117550638</v>
       </c>
       <c r="M11">
-        <v>0.19561810160537049</v>
+        <v>0.1908316926321921</v>
       </c>
     </row>
     <row r="12" spans="2:13">
@@ -7479,10 +7502,10 @@
         <v>409</v>
       </c>
       <c r="L12">
-        <v>3.9912529292571399</v>
+        <v>7.3197223495603936</v>
       </c>
       <c r="M12">
-        <v>0.1899800578090565</v>
+        <v>0.19561810160537049</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -7514,10 +7537,10 @@
         <v>410</v>
       </c>
       <c r="L13">
-        <v>4.2706680673701092</v>
+        <v>8.0728012038744801</v>
       </c>
       <c r="M13">
-        <v>0.188954058034423</v>
+        <v>0.18952650169607679</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -7549,10 +7572,10 @@
         <v>411</v>
       </c>
       <c r="L14">
-        <v>13.981359478801604</v>
+        <v>16.490046365977989</v>
       </c>
       <c r="M14">
-        <v>0.1936437094766659</v>
+        <v>0.19347449709232589</v>
       </c>
     </row>
     <row r="15" spans="2:13">
@@ -7584,10 +7607,10 @@
         <v>412</v>
       </c>
       <c r="L15">
-        <v>28.21764385202707</v>
+        <v>22.832160716244008</v>
       </c>
       <c r="M15">
-        <v>0.20234236171720621</v>
+        <v>0.2040441742750202</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -7619,10 +7642,10 @@
         <v>413</v>
       </c>
       <c r="L16">
-        <v>4.8768513119274983</v>
+        <v>18.067161329616688</v>
       </c>
       <c r="M16">
-        <v>0.19168291824194039</v>
+        <v>0.19791063228745551</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -7654,10 +7677,10 @@
         <v>414</v>
       </c>
       <c r="L17">
-        <v>13.870317588084811</v>
+        <v>3.5932182489017483</v>
       </c>
       <c r="M17">
-        <v>0.19845632226614379</v>
+        <v>0.19293409646713011</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -7689,10 +7712,10 @@
         <v>415</v>
       </c>
       <c r="L18">
-        <v>1.3237102416747595</v>
+        <v>3.985968590704092</v>
       </c>
       <c r="M18">
-        <v>0.15616948935531069</v>
+        <v>0.19577011065941391</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -7724,10 +7747,10 @@
         <v>416</v>
       </c>
       <c r="L19">
-        <v>0.95475881280981956</v>
+        <v>3.4506289697397312</v>
       </c>
       <c r="M19">
-        <v>0.1629573257982378</v>
+        <v>0.1805585680013394</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -7759,10 +7782,10 @@
         <v>417</v>
       </c>
       <c r="L20">
-        <v>3.609473356098265</v>
+        <v>1.490796752963657</v>
       </c>
       <c r="M20">
-        <v>0.170844591510006</v>
+        <v>0.15646436566344529</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -7794,10 +7817,10 @@
         <v>418</v>
       </c>
       <c r="L21">
-        <v>5.4075373048565565</v>
+        <v>1.9378492019965576</v>
       </c>
       <c r="M21">
-        <v>0.19725515194825349</v>
+        <v>0.17716280596748141</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -7829,10 +7852,10 @@
         <v>419</v>
       </c>
       <c r="L22">
-        <v>1.9378492019965576</v>
+        <v>2.5300973808703642</v>
       </c>
       <c r="M22">
-        <v>0.17716280596748141</v>
+        <v>0.16422559634387821</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -7864,10 +7887,10 @@
         <v>420</v>
       </c>
       <c r="L23">
-        <v>3.5932182489017483</v>
+        <v>1.1532607266374395</v>
       </c>
       <c r="M23">
-        <v>0.19293409646713011</v>
+        <v>0.1596943947718672</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -7899,10 +7922,10 @@
         <v>421</v>
       </c>
       <c r="L24">
-        <v>17.548211545188931</v>
+        <v>6.955061804170598E-2</v>
       </c>
       <c r="M24">
-        <v>0.20545381979143959</v>
+        <v>0.16870498304975501</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -7934,10 +7957,10 @@
         <v>422</v>
       </c>
       <c r="L25">
-        <v>3.8211717975884008</v>
+        <v>3.7884735526498567</v>
       </c>
       <c r="M25">
-        <v>0.20608159323988301</v>
+        <v>0.1914778634952122</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -7969,10 +7992,10 @@
         <v>423</v>
       </c>
       <c r="L26">
-        <v>20.684451442302088</v>
+        <v>2.8028101240283756</v>
       </c>
       <c r="M26">
-        <v>0.205148492342488</v>
+        <v>0.20351988166761151</v>
       </c>
     </row>
     <row r="27" spans="2:13">
@@ -8004,10 +8027,10 @@
         <v>424</v>
       </c>
       <c r="L27">
-        <v>2.9424673149973128</v>
+        <v>2.5831163169050639</v>
       </c>
       <c r="M27">
-        <v>0.18964760118957211</v>
+        <v>0.1838555882863443</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8039,10 +8062,10 @@
         <v>425</v>
       </c>
       <c r="L28">
-        <v>1.2120950895642146</v>
+        <v>58.500936737321986</v>
       </c>
       <c r="M28">
-        <v>0.20016056548956479</v>
+        <v>0.20052074186776009</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -8074,10 +8097,10 @@
         <v>426</v>
       </c>
       <c r="L29">
-        <v>5.329525145496671</v>
+        <v>13.435769518183669</v>
       </c>
       <c r="M29">
-        <v>0.2057749843939507</v>
+        <v>0.19692815728264379</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -8109,10 +8132,10 @@
         <v>427</v>
       </c>
       <c r="L30">
-        <v>0.70799999999999996</v>
+        <v>22.418974247207004</v>
       </c>
       <c r="M30">
-        <v>0.1744368403907999</v>
+        <v>0.1950293299164246</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -8144,10 +8167,10 @@
         <v>428</v>
       </c>
       <c r="L31">
-        <v>2.0804999999999998</v>
+        <v>23.99114283098428</v>
       </c>
       <c r="M31">
-        <v>0.17684069581882239</v>
+        <v>0.2048651770601369</v>
       </c>
     </row>
     <row r="32" spans="2:13">
@@ -8179,10 +8202,10 @@
         <v>429</v>
       </c>
       <c r="L32">
-        <v>0.90225</v>
+        <v>13.739305832837374</v>
       </c>
       <c r="M32">
-        <v>0.1745168327240296</v>
+        <v>0.2053752917268552</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -8214,10 +8237,10 @@
         <v>430</v>
       </c>
       <c r="L33">
-        <v>0.42975000000000002</v>
+        <v>3.8211717975884008</v>
       </c>
       <c r="M33">
-        <v>0.17065936942800919</v>
+        <v>0.20608159323988301</v>
       </c>
     </row>
     <row r="34" spans="2:13">
@@ -8249,10 +8272,10 @@
         <v>431</v>
       </c>
       <c r="L34">
-        <v>1.0305</v>
+        <v>20.187145174959106</v>
       </c>
       <c r="M34">
-        <v>0.1698810046979061</v>
+        <v>0.20398532462148219</v>
       </c>
     </row>
     <row r="35" spans="2:13">
@@ -8284,10 +8307,10 @@
         <v>432</v>
       </c>
       <c r="L35">
-        <v>0.156</v>
+        <v>6.3983970485686443</v>
       </c>
       <c r="M35">
-        <v>0.16788539947934419</v>
+        <v>0.2067117282987424</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -8319,10 +8342,10 @@
         <v>433</v>
       </c>
       <c r="L36">
-        <v>0.14849999999999999</v>
+        <v>3.3045988621099531</v>
       </c>
       <c r="M36">
-        <v>0.1635527861912483</v>
+        <v>0.20209643287426199</v>
       </c>
     </row>
     <row r="37" spans="2:13">
@@ -8354,10 +8377,10 @@
         <v>434</v>
       </c>
       <c r="L37">
-        <v>0.87944277553898109</v>
+        <v>1.4881792514726941</v>
       </c>
       <c r="M37">
-        <v>0.1749399025772358</v>
+        <v>0.19488790250529889</v>
       </c>
     </row>
     <row r="38" spans="2:13">
@@ -8389,10 +8412,10 @@
         <v>435</v>
       </c>
       <c r="L38">
-        <v>1.0237499999999999</v>
+        <v>1.5367165103638039</v>
       </c>
       <c r="M38">
-        <v>0.17087282870907899</v>
+        <v>0.20572502610731419</v>
       </c>
     </row>
     <row r="39" spans="2:13">
@@ -8424,10 +8447,10 @@
         <v>436</v>
       </c>
       <c r="L39">
-        <v>34.203659787790635</v>
+        <v>11.335033212319731</v>
       </c>
       <c r="M39">
-        <v>0.20277787100359901</v>
+        <v>0.18908223839922031</v>
       </c>
     </row>
     <row r="40" spans="2:13">
@@ -8459,10 +8482,10 @@
         <v>437</v>
       </c>
       <c r="L40">
-        <v>4.383</v>
+        <v>14.684868844937309</v>
       </c>
       <c r="M40">
-        <v>0.17652814756647231</v>
+        <v>0.20599907341787929</v>
       </c>
     </row>
     <row r="41" spans="2:13">
@@ -8494,10 +8517,10 @@
         <v>438</v>
       </c>
       <c r="L41">
-        <v>19.960372548613204</v>
+        <v>18.389071242107757</v>
       </c>
       <c r="M41">
-        <v>0.1775042022863807</v>
+        <v>0.2136912037958752</v>
       </c>
     </row>
     <row r="42" spans="2:13">
@@ -8529,10 +8552,10 @@
         <v>439</v>
       </c>
       <c r="L42">
-        <v>63.682122079669604</v>
+        <v>3.0669828363833558</v>
       </c>
       <c r="M42">
-        <v>0.21228801975659189</v>
+        <v>0.20576148027584359</v>
       </c>
     </row>
     <row r="43" spans="2:13">
@@ -8564,10 +8587,10 @@
         <v>440</v>
       </c>
       <c r="L43">
-        <v>58.318268922653999</v>
+        <v>17.157906051521838</v>
       </c>
       <c r="M43">
-        <v>0.2026093216444774</v>
+        <v>0.20859471527342779</v>
       </c>
     </row>
     <row r="44" spans="2:13">
@@ -8599,10 +8622,10 @@
         <v>441</v>
       </c>
       <c r="L44">
-        <v>45.783632322458843</v>
+        <v>1.6310885177575092</v>
       </c>
       <c r="M44">
-        <v>0.22140145266700439</v>
+        <v>0.18027061898393701</v>
       </c>
     </row>
     <row r="45" spans="2:13">
@@ -8634,10 +8657,10 @@
         <v>442</v>
       </c>
       <c r="L45">
-        <v>94.676676509970278</v>
+        <v>2.4526493307316448</v>
       </c>
       <c r="M45">
-        <v>0.2101752042956109</v>
+        <v>0.17961844664020429</v>
       </c>
     </row>
     <row r="46" spans="2:13">
@@ -8669,10 +8692,10 @@
         <v>443</v>
       </c>
       <c r="L46">
-        <v>51.645742424896213</v>
+        <v>6.3626000209859885</v>
       </c>
       <c r="M46">
-        <v>0.19882298850703761</v>
+        <v>0.1819311327525607</v>
       </c>
     </row>
     <row r="47" spans="2:13">
@@ -8704,10 +8727,10 @@
         <v>444</v>
       </c>
       <c r="L47">
-        <v>31.338638517489738</v>
+        <v>7.8965874118777952</v>
       </c>
       <c r="M47">
-        <v>0.20604696473512721</v>
+        <v>0.19905058901527081</v>
       </c>
     </row>
     <row r="48" spans="2:13">
@@ -8739,10 +8762,10 @@
         <v>445</v>
       </c>
       <c r="L48">
-        <v>19.145251097865469</v>
+        <v>5.3525253443059002</v>
       </c>
       <c r="M48">
-        <v>0.2282812262662671</v>
+        <v>0.17512296488543699</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -8774,10 +8797,10 @@
         <v>446</v>
       </c>
       <c r="L49">
-        <v>26.661859285174934</v>
+        <v>5.2981836188673936</v>
       </c>
       <c r="M49">
-        <v>0.23163247227506359</v>
+        <v>0.1785896449641472</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -8809,10 +8832,10 @@
         <v>447</v>
       </c>
       <c r="L50">
-        <v>4.7240832790723051</v>
+        <v>13.560579149762697</v>
       </c>
       <c r="M50">
-        <v>0.19130911733602449</v>
+        <v>0.19675453122836969</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -8844,10 +8867,10 @@
         <v>448</v>
       </c>
       <c r="L51">
-        <v>12.893100432315391</v>
+        <v>7.7682073930015179</v>
       </c>
       <c r="M51">
-        <v>0.191094128148071</v>
+        <v>0.20089344606517359</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -8879,10 +8902,10 @@
         <v>449</v>
       </c>
       <c r="L52">
-        <v>15.333</v>
+        <v>9.0037702871779342</v>
       </c>
       <c r="M52">
-        <v>0.18991301593133281</v>
+        <v>0.18249125142117731</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -8914,10 +8937,10 @@
         <v>450</v>
       </c>
       <c r="L53">
-        <v>30.287784706562448</v>
+        <v>37.570794103363134</v>
       </c>
       <c r="M53">
-        <v>0.19469458211456281</v>
+        <v>0.21188353859049711</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -8949,10 +8972,10 @@
         <v>451</v>
       </c>
       <c r="L54">
-        <v>22.242000000000001</v>
+        <v>39.714937784733756</v>
       </c>
       <c r="M54">
-        <v>0.18968339342226501</v>
+        <v>0.23344212305107589</v>
       </c>
     </row>
     <row r="55" spans="2:13">
@@ -8984,10 +9007,10 @@
         <v>452</v>
       </c>
       <c r="L55">
-        <v>12.43049589068308</v>
+        <v>35.292241860973398</v>
       </c>
       <c r="M55">
-        <v>0.19774694895145389</v>
+        <v>0.2200887536800917</v>
       </c>
     </row>
     <row r="56" spans="2:13">
@@ -9019,10 +9042,10 @@
         <v>453</v>
       </c>
       <c r="L56">
-        <v>4.9545000000000003</v>
+        <v>24.969275234166346</v>
       </c>
       <c r="M56">
-        <v>0.18343191505321699</v>
+        <v>0.21136947465830891</v>
       </c>
     </row>
     <row r="57" spans="2:13">
@@ -9054,10 +9077,10 @@
         <v>454</v>
       </c>
       <c r="L57">
-        <v>1.3665</v>
+        <v>29.051453871933358</v>
       </c>
       <c r="M57">
-        <v>0.1808772482040098</v>
+        <v>0.1959839244283772</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -9089,10 +9112,10 @@
         <v>455</v>
       </c>
       <c r="L58">
-        <v>8.9877547998367646</v>
+        <v>74.526996853461398</v>
       </c>
       <c r="M58">
-        <v>0.1911068856548151</v>
+        <v>0.20992573401803699</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -9124,10 +9147,10 @@
         <v>456</v>
       </c>
       <c r="L59">
-        <v>2.5447500000000001</v>
+        <v>52.981218678346053</v>
       </c>
       <c r="M59">
-        <v>0.17726319822747269</v>
+        <v>0.2152518357023907</v>
       </c>
     </row>
     <row r="60" spans="2:13">
@@ -9159,10 +9182,10 @@
         <v>457</v>
       </c>
       <c r="L60">
-        <v>6.7422400346620455</v>
+        <v>18.860120435725289</v>
       </c>
       <c r="M60">
-        <v>0.18162469862157599</v>
+        <v>0.22305009092480441</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -9194,10 +9217,10 @@
         <v>458</v>
       </c>
       <c r="L61">
-        <v>19.329927537704947</v>
+        <v>61.930598406514726</v>
       </c>
       <c r="M61">
-        <v>0.1837164749039073</v>
+        <v>0.22088636940845571</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -9229,10 +9252,10 @@
         <v>459</v>
       </c>
       <c r="L62">
-        <v>4.9695</v>
+        <v>38.707045784497502</v>
       </c>
       <c r="M62">
-        <v>0.1822092693183002</v>
+        <v>0.23247215542614791</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -9264,10 +9287,10 @@
         <v>460</v>
       </c>
       <c r="L63">
-        <v>20.959218324874239</v>
+        <v>59.045652575229148</v>
       </c>
       <c r="M63">
-        <v>0.23015774746645831</v>
+        <v>0.20769926724341761</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -9299,10 +9322,10 @@
         <v>461</v>
       </c>
       <c r="L64">
-        <v>31.014696934585121</v>
+        <v>43.496173040060349</v>
       </c>
       <c r="M64">
-        <v>0.2140287598254875</v>
+        <v>0.2038474642017355</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -9334,10 +9357,10 @@
         <v>462</v>
       </c>
       <c r="L65">
-        <v>39.393078287984075</v>
+        <v>53.474241241720129</v>
       </c>
       <c r="M65">
-        <v>0.22636170586922449</v>
+        <v>0.21501399536721411</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -9369,10 +9392,10 @@
         <v>463</v>
       </c>
       <c r="L66">
-        <v>21.329513703273719</v>
+        <v>36.593055076714478</v>
       </c>
       <c r="M66">
-        <v>0.2170178645743317</v>
+        <v>0.20774241654080719</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -9404,10 +9427,10 @@
         <v>464</v>
       </c>
       <c r="L67">
-        <v>44.915634639686459</v>
+        <v>15.326607621007465</v>
       </c>
       <c r="M67">
-        <v>0.2026938283731273</v>
+        <v>0.23316600364958959</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -9439,10 +9462,10 @@
         <v>465</v>
       </c>
       <c r="L68">
-        <v>7.78340431694087</v>
+        <v>14.984176386042574</v>
       </c>
       <c r="M68">
-        <v>0.2160576463236453</v>
+        <v>0.229007708360497</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -9474,10 +9497,10 @@
         <v>466</v>
       </c>
       <c r="L69">
-        <v>8.2717940638731591</v>
+        <v>18.587087633724469</v>
       </c>
       <c r="M69">
-        <v>0.18512318990115609</v>
+        <v>0.22420242427234521</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -9509,10 +9532,10 @@
         <v>467</v>
       </c>
       <c r="L70">
-        <v>12.604071732513232</v>
+        <v>24.551096439142999</v>
       </c>
       <c r="M70">
-        <v>0.1953641199022971</v>
+        <v>0.19793742147975091</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -9544,10 +9567,10 @@
         <v>468</v>
       </c>
       <c r="L71">
-        <v>5.6530945566751054</v>
+        <v>54.442699269687061</v>
       </c>
       <c r="M71">
-        <v>0.18438337043001871</v>
+        <v>0.20140148283084999</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -9579,10 +9602,10 @@
         <v>469</v>
       </c>
       <c r="L72">
-        <v>7.4235702996807422</v>
+        <v>27.546161976350611</v>
       </c>
       <c r="M72">
-        <v>0.2012886107692069</v>
+        <v>0.19731988005560699</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -9614,10 +9637,10 @@
         <v>470</v>
       </c>
       <c r="L73">
-        <v>7.0481364824239572</v>
+        <v>35.981111221589849</v>
       </c>
       <c r="M73">
-        <v>0.18325028495971579</v>
+        <v>0.1977080973120946</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -9649,10 +9672,10 @@
         <v>471</v>
       </c>
       <c r="L74">
-        <v>5.4109929761160274</v>
+        <v>5.8693399186588291</v>
       </c>
       <c r="M74">
-        <v>0.17851828392540839</v>
+        <v>0.2009704779348209</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -9684,10 +9707,10 @@
         <v>472</v>
       </c>
       <c r="L75">
-        <v>1.5182791605088741</v>
+        <v>11.323769250256232</v>
       </c>
       <c r="M75">
-        <v>0.18064984020562261</v>
+        <v>0.2032972917147147</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -9719,10 +9742,10 @@
         <v>473</v>
       </c>
       <c r="L76">
-        <v>2.4526493307316448</v>
+        <v>44.716752386549238</v>
       </c>
       <c r="M76">
-        <v>0.17961844664020429</v>
+        <v>0.19926264410000541</v>
       </c>
     </row>
     <row r="77" spans="2:13">
@@ -9754,10 +9777,10 @@
         <v>474</v>
       </c>
       <c r="L77">
-        <v>30.929580262702071</v>
+        <v>18.862172753030631</v>
       </c>
       <c r="M77">
-        <v>0.23340041584314489</v>
+        <v>0.19455907359141009</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -9789,10 +9812,10 @@
         <v>475</v>
       </c>
       <c r="L78">
-        <v>9.2133418027367053</v>
+        <v>10.416225728892211</v>
       </c>
       <c r="M78">
-        <v>0.21903384104979179</v>
+        <v>0.19487698508275531</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -9824,10 +9847,10 @@
         <v>476</v>
       </c>
       <c r="L79">
-        <v>45.030225755041762</v>
+        <v>14.859845549854393</v>
       </c>
       <c r="M79">
-        <v>0.22315800231900221</v>
+        <v>0.1916163980629671</v>
       </c>
     </row>
     <row r="80" spans="2:13">
@@ -9859,10 +9882,10 @@
         <v>477</v>
       </c>
       <c r="L80">
-        <v>37.907022428713496</v>
+        <v>12.75749589068308</v>
       </c>
       <c r="M80">
-        <v>0.2077303517310197</v>
+        <v>0.1975359241843983</v>
       </c>
     </row>
     <row r="81" spans="2:13">
@@ -9894,10 +9917,10 @@
         <v>478</v>
       </c>
       <c r="L81">
-        <v>48.641605728516204</v>
+        <v>38.716517043706595</v>
       </c>
       <c r="M81">
-        <v>0.2136408086419864</v>
+        <v>0.1916560717687667</v>
       </c>
     </row>
     <row r="82" spans="2:13">
@@ -9929,10 +9952,10 @@
         <v>479</v>
       </c>
       <c r="L82">
-        <v>15.897437272368096</v>
+        <v>6.2970356064498896</v>
       </c>
       <c r="M82">
-        <v>0.20795010350353249</v>
+        <v>0.186273978929412</v>
       </c>
     </row>
     <row r="83" spans="2:13">
@@ -9964,10 +9987,10 @@
         <v>480</v>
       </c>
       <c r="L83">
-        <v>7.6350252914597281</v>
+        <v>13.391077682802527</v>
       </c>
       <c r="M83">
-        <v>0.2022067969997674</v>
+        <v>0.1803300723340219</v>
       </c>
     </row>
     <row r="84" spans="2:13">
@@ -9999,10 +10022,10 @@
         <v>481</v>
       </c>
       <c r="L84">
-        <v>14.684868844937309</v>
+        <v>5.5931424446478806</v>
       </c>
       <c r="M84">
-        <v>0.20599907341787929</v>
+        <v>0.1925766664138695</v>
       </c>
     </row>
     <row r="85" spans="2:13">
@@ -10034,10 +10057,10 @@
         <v>482</v>
       </c>
       <c r="L85">
-        <v>23.825875134446761</v>
+        <v>9.0012547998367669</v>
       </c>
       <c r="M85">
-        <v>0.2138107184384998</v>
+        <v>0.1911058720159349</v>
       </c>
     </row>
     <row r="86" spans="2:13">
@@ -10069,10 +10092,10 @@
         <v>483</v>
       </c>
       <c r="L86">
-        <v>29.638500000000001</v>
+        <v>23.610749999999999</v>
       </c>
       <c r="M86">
-        <v>0.19033342281512841</v>
+        <v>0.19087284182219411</v>
       </c>
     </row>
     <row r="87" spans="2:13">
@@ -10104,10 +10127,10 @@
         <v>484</v>
       </c>
       <c r="L87">
-        <v>5.8140000000000001</v>
+        <v>19.50375</v>
       </c>
       <c r="M87">
-        <v>0.1814608528789548</v>
+        <v>0.18767109483933619</v>
       </c>
     </row>
     <row r="88" spans="2:13">
@@ -10139,10 +10162,10 @@
         <v>485</v>
       </c>
       <c r="L88">
-        <v>23.389500000000002</v>
+        <v>52.157675274357565</v>
       </c>
       <c r="M88">
-        <v>0.18656279129484471</v>
+        <v>0.19731656417400389</v>
       </c>
     </row>
     <row r="89" spans="2:13">
@@ -10174,10 +10197,10 @@
         <v>486</v>
       </c>
       <c r="L89">
-        <v>12.526218104221192</v>
+        <v>38.351467683279147</v>
       </c>
       <c r="M89">
-        <v>0.1944006210832441</v>
+        <v>0.19794432637091891</v>
       </c>
     </row>
     <row r="90" spans="2:13">
@@ -10209,10 +10232,10 @@
         <v>487</v>
       </c>
       <c r="L90">
-        <v>8.7494999999999994</v>
+        <v>17.390999999999998</v>
       </c>
       <c r="M90">
-        <v>0.17011448820127009</v>
+        <v>0.19161488059043461</v>
       </c>
     </row>
     <row r="91" spans="2:13">
@@ -10244,10 +10267,10 @@
         <v>488</v>
       </c>
       <c r="L91">
-        <v>19.429500000000001</v>
+        <v>33.706499999999998</v>
       </c>
       <c r="M91">
-        <v>0.17825140137848799</v>
+        <v>0.1903172077016424</v>
       </c>
     </row>
     <row r="92" spans="2:13">
@@ -10279,10 +10302,10 @@
         <v>489</v>
       </c>
       <c r="L92">
-        <v>13.204499999999999</v>
+        <v>6.35025</v>
       </c>
       <c r="M92">
-        <v>0.18298457797568271</v>
+        <v>0.18311718913633079</v>
       </c>
     </row>
     <row r="93" spans="2:13">
@@ -10314,10 +10337,10 @@
         <v>490</v>
       </c>
       <c r="L93">
-        <v>22.705750387019794</v>
+        <v>2.907</v>
       </c>
       <c r="M93">
-        <v>0.18988285307846151</v>
+        <v>0.1821327312964286</v>
       </c>
     </row>
     <row r="94" spans="2:13">
@@ -10349,10 +10372,10 @@
         <v>491</v>
       </c>
       <c r="L94">
-        <v>39.734003271901024</v>
+        <v>3.75</v>
       </c>
       <c r="M94">
-        <v>0.18385411049004069</v>
+        <v>0.18096759982099611</v>
       </c>
     </row>
     <row r="95" spans="2:13">
@@ -10384,10 +10407,10 @@
         <v>492</v>
       </c>
       <c r="L95">
-        <v>1.6890000000000001</v>
+        <v>16.217822681745979</v>
       </c>
       <c r="M95">
-        <v>0.18324082787545401</v>
+        <v>0.18962485807836471</v>
       </c>
     </row>
     <row r="96" spans="2:13">
@@ -10419,10 +10442,10 @@
         <v>493</v>
       </c>
       <c r="L96">
-        <v>0.23100000000000001</v>
+        <v>0.93374999999999997</v>
       </c>
       <c r="M96">
-        <v>0.16362926153910051</v>
+        <v>0.17441193558869639</v>
       </c>
     </row>
     <row r="97" spans="2:13">
@@ -10454,10 +10477,10 @@
         <v>494</v>
       </c>
       <c r="L97">
-        <v>0.23774999999999999</v>
+        <v>0.89175000000000004</v>
       </c>
       <c r="M97">
-        <v>0.17665881785013701</v>
+        <v>0.169483831776715</v>
       </c>
     </row>
     <row r="98" spans="2:13">
@@ -10489,10 +10512,10 @@
         <v>495</v>
       </c>
       <c r="L98">
-        <v>0.33150000000000002</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="M98">
-        <v>0.17752736088208571</v>
+        <v>0.17122366551990459</v>
       </c>
     </row>
     <row r="99" spans="2:13">
@@ -10524,10 +10547,10 @@
         <v>496</v>
       </c>
       <c r="L99">
-        <v>2.4464999999999999</v>
+        <v>7.5945</v>
       </c>
       <c r="M99">
-        <v>0.17261068680339819</v>
+        <v>0.1781166963223694</v>
       </c>
     </row>
     <row r="100" spans="2:13">
@@ -10559,10 +10582,10 @@
         <v>497</v>
       </c>
       <c r="L100">
-        <v>0.2145</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="M100">
-        <v>0.17021717738047659</v>
+        <v>0.1755792286671686</v>
       </c>
     </row>
     <row r="101" spans="2:13">
@@ -10594,10 +10617,10 @@
         <v>498</v>
       </c>
       <c r="L101">
-        <v>15.69525</v>
+        <v>0.53025</v>
       </c>
       <c r="M101">
-        <v>0.18347770348108219</v>
+        <v>0.1758251796637752</v>
       </c>
     </row>
     <row r="102" spans="2:13">
@@ -10629,10 +10652,10 @@
         <v>499</v>
       </c>
       <c r="L102">
-        <v>7.3815</v>
+        <v>1.8322499999999999</v>
       </c>
       <c r="M102">
-        <v>0.1805371732071149</v>
+        <v>0.17664766805013471</v>
       </c>
     </row>
     <row r="103" spans="2:13">
@@ -10664,10 +10687,10 @@
         <v>500</v>
       </c>
       <c r="L103">
-        <v>5.0339999999999998</v>
+        <v>0.156</v>
       </c>
       <c r="M103">
-        <v>0.17673696410513001</v>
+        <v>0.16788539947934419</v>
       </c>
     </row>
     <row r="104" spans="2:13">
@@ -10699,10 +10722,10 @@
         <v>501</v>
       </c>
       <c r="L104">
-        <v>42.147206133399365</v>
+        <v>0.14849999999999999</v>
       </c>
       <c r="M104">
-        <v>0.19457876399727669</v>
+        <v>0.1635527861912483</v>
       </c>
     </row>
     <row r="105" spans="2:13">
@@ -10734,10 +10757,10 @@
         <v>502</v>
       </c>
       <c r="L105">
-        <v>41.726273386122017</v>
+        <v>0.87944277553898109</v>
       </c>
       <c r="M105">
-        <v>0.1972752366886657</v>
+        <v>0.1749399025772358</v>
       </c>
     </row>
     <row r="106" spans="2:13">
@@ -10769,10 +10792,10 @@
         <v>503</v>
       </c>
       <c r="L106">
-        <v>1.3303012307087763</v>
+        <v>1.0237499999999999</v>
       </c>
       <c r="M106">
-        <v>0.20265857068007281</v>
+        <v>0.17087282870907899</v>
       </c>
     </row>
     <row r="107" spans="2:13">
@@ -10804,10 +10827,10 @@
         <v>504</v>
       </c>
       <c r="L107">
-        <v>21.037914020583063</v>
+        <v>34.203659787790635</v>
       </c>
       <c r="M107">
-        <v>0.1994237557677917</v>
+        <v>0.20277787100359901</v>
       </c>
     </row>
     <row r="108" spans="2:13">
@@ -10839,10 +10862,10 @@
         <v>505</v>
       </c>
       <c r="L108">
-        <v>14.702249999999999</v>
+        <v>4.383</v>
       </c>
       <c r="M108">
-        <v>0.18779408495945729</v>
+        <v>0.17652814756647231</v>
       </c>
     </row>
     <row r="109" spans="2:13">
@@ -10874,10 +10897,10 @@
         <v>506</v>
       </c>
       <c r="L109">
-        <v>15.534000000000001</v>
+        <v>19.960372548613204</v>
       </c>
       <c r="M109">
-        <v>0.1897345894459537</v>
+        <v>0.1775042022863807</v>
       </c>
     </row>
     <row r="110" spans="2:13">
@@ -10909,10 +10932,10 @@
         <v>507</v>
       </c>
       <c r="L110">
-        <v>68.042105186701164</v>
+        <v>6.1364999999999998</v>
       </c>
       <c r="M110">
-        <v>0.19694006243892601</v>
+        <v>0.18017031168863731</v>
       </c>
     </row>
     <row r="111" spans="2:13">
@@ -10944,10 +10967,10 @@
         <v>508</v>
       </c>
       <c r="L111">
-        <v>43.43652270216927</v>
+        <v>8.7494999999999994</v>
       </c>
       <c r="M111">
-        <v>0.19568535232108891</v>
+        <v>0.17011448820127009</v>
       </c>
     </row>
     <row r="112" spans="2:13">
@@ -10979,10 +11002,10 @@
         <v>509</v>
       </c>
       <c r="L112">
-        <v>63.902786745830014</v>
+        <v>29.337984838615441</v>
       </c>
       <c r="M112">
-        <v>0.20163604169662949</v>
+        <v>0.18787751665049621</v>
       </c>
     </row>
     <row r="113" spans="2:13">
@@ -11014,10 +11037,10 @@
         <v>510</v>
       </c>
       <c r="L113">
-        <v>24.919216820057812</v>
+        <v>26.870992856538564</v>
       </c>
       <c r="M113">
-        <v>0.19617641660771079</v>
+        <v>0.1856430053345354</v>
       </c>
     </row>
     <row r="114" spans="2:13">
@@ -11049,10 +11072,10 @@
         <v>511</v>
       </c>
       <c r="L114">
-        <v>17.442599831437619</v>
+        <v>19.429500000000001</v>
       </c>
       <c r="M114">
-        <v>0.19746026341411449</v>
+        <v>0.17825140137848799</v>
       </c>
     </row>
     <row r="115" spans="2:13">
@@ -11084,10 +11107,10 @@
         <v>512</v>
       </c>
       <c r="L115">
-        <v>1.9011734607434354</v>
+        <v>34.001163330581925</v>
       </c>
       <c r="M115">
-        <v>0.20757865467249431</v>
+        <v>0.1836707032869685</v>
       </c>
     </row>
     <row r="116" spans="2:13">
@@ -11119,10 +11142,10 @@
         <v>513</v>
       </c>
       <c r="L116">
-        <v>0.79446578034560333</v>
+        <v>1.6890000000000001</v>
       </c>
       <c r="M116">
-        <v>0.2051820092932628</v>
+        <v>0.18324082787545401</v>
       </c>
     </row>
     <row r="117" spans="2:13">
@@ -11154,10 +11177,10 @@
         <v>514</v>
       </c>
       <c r="L117">
-        <v>8.6046425413806524</v>
+        <v>0.23924999999999999</v>
       </c>
       <c r="M117">
-        <v>0.20478548547266431</v>
+        <v>0.1638006404161976</v>
       </c>
     </row>
     <row r="118" spans="2:13">
@@ -11189,10 +11212,10 @@
         <v>515</v>
       </c>
       <c r="L118">
-        <v>31.326120090267271</v>
+        <v>0.23774999999999999</v>
       </c>
       <c r="M118">
-        <v>0.20080866738482561</v>
+        <v>0.17665881785013701</v>
       </c>
     </row>
     <row r="119" spans="2:13">
@@ -11224,10 +11247,10 @@
         <v>516</v>
       </c>
       <c r="L119">
-        <v>6.6613548520415211</v>
+        <v>0.32324999999999998</v>
       </c>
       <c r="M119">
-        <v>0.1755567625829097</v>
+        <v>0.17775522452704831</v>
       </c>
     </row>
     <row r="120" spans="2:13">
@@ -11259,10 +11282,10 @@
         <v>517</v>
       </c>
       <c r="L120">
-        <v>3.2182916630974701</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="M120">
-        <v>0.19809347445011299</v>
+        <v>0.16799176096210611</v>
       </c>
     </row>
     <row r="121" spans="2:13">
@@ -11294,10 +11317,10 @@
         <v>518</v>
       </c>
       <c r="L121">
-        <v>9.5701371149225025</v>
+        <v>0.45600000000000002</v>
       </c>
       <c r="M121">
-        <v>0.18675098962924591</v>
+        <v>0.17197323013571211</v>
       </c>
     </row>
     <row r="122" spans="2:13">
@@ -11329,10 +11352,10 @@
         <v>519</v>
       </c>
       <c r="L122">
-        <v>1.1532607266374395</v>
+        <v>15.69525</v>
       </c>
       <c r="M122">
-        <v>0.1596943947718672</v>
+        <v>0.18347770348108219</v>
       </c>
     </row>
     <row r="123" spans="2:13">
@@ -11364,10 +11387,10 @@
         <v>520</v>
       </c>
       <c r="L123">
-        <v>6.955061804170598E-2</v>
+        <v>5.0339999999999998</v>
       </c>
       <c r="M123">
-        <v>0.16870498304975501</v>
+        <v>0.17673696410513001</v>
       </c>
     </row>
     <row r="124" spans="2:13">
@@ -11399,10 +11422,10 @@
         <v>521</v>
       </c>
       <c r="L124">
-        <v>3.3944125271035701</v>
+        <v>2.7690000000000001</v>
       </c>
       <c r="M124">
-        <v>0.20284219553050409</v>
+        <v>0.18378765559672039</v>
       </c>
     </row>
     <row r="125" spans="2:13">
@@ -11434,10 +11457,10 @@
         <v>522</v>
       </c>
       <c r="L125">
-        <v>3.6004209042317972</v>
+        <v>6.7380000000000004</v>
       </c>
       <c r="M125">
-        <v>0.19092585103959611</v>
+        <v>0.17672241281615511</v>
       </c>
     </row>
   </sheetData>
@@ -11446,7 +11469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5D0C7B4-7750-42F8-BC4B-E78CF3579D08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6422976D-8D1C-4229-8CD0-FAE58573AA11}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11561,10 +11584,10 @@
         <v>661</v>
       </c>
       <c r="L11">
-        <v>4.7713910333636482</v>
+        <v>10.563746678268352</v>
       </c>
       <c r="M11">
-        <v>0.11142888197414</v>
+        <v>0.1762422335004816</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -11629,10 +11652,10 @@
         <v>662</v>
       </c>
       <c r="L12">
-        <v>12.404103898825962</v>
+        <v>7.4816578037471135</v>
       </c>
       <c r="M12">
-        <v>0.112128823851027</v>
+        <v>0.12851292841627501</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -11697,10 +11720,10 @@
         <v>663</v>
       </c>
       <c r="L13">
-        <v>6.1276234637439133</v>
+        <v>4.7713910333636482</v>
       </c>
       <c r="M13">
-        <v>9.4081669365557702E-2</v>
+        <v>0.11142888197414</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -11765,10 +11788,10 @@
         <v>664</v>
       </c>
       <c r="L14">
-        <v>0.85621181691755843</v>
+        <v>12.404103898825962</v>
       </c>
       <c r="M14">
-        <v>9.0668099088234103E-2</v>
+        <v>0.112128823851027</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -11833,10 +11856,10 @@
         <v>665</v>
       </c>
       <c r="L15">
-        <v>2.2628760328229185</v>
+        <v>6.1276234637439133</v>
       </c>
       <c r="M15">
-        <v>0.1238708109113873</v>
+        <v>9.4081669365557702E-2</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -11901,10 +11924,10 @@
         <v>666</v>
       </c>
       <c r="L16">
-        <v>0.43370118574988076</v>
+        <v>2.2195844391122765</v>
       </c>
       <c r="M16">
-        <v>0.10138851292069349</v>
+        <v>0.1603834390284819</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -11969,10 +11992,10 @@
         <v>667</v>
       </c>
       <c r="L17">
-        <v>2.5150267058852811</v>
+        <v>3.7614311754340659</v>
       </c>
       <c r="M17">
-        <v>8.7681833650751606E-2</v>
+        <v>0.21587774284891351</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -12037,10 +12060,10 @@
         <v>668</v>
       </c>
       <c r="L18">
-        <v>2.885493974180005</v>
+        <v>2.5731779960501728</v>
       </c>
       <c r="M18">
-        <v>0.14764341619346269</v>
+        <v>0.19326289879692229</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -12105,10 +12128,10 @@
         <v>669</v>
       </c>
       <c r="L19">
-        <v>10.563746678268352</v>
+        <v>1.9040172385939969</v>
       </c>
       <c r="M19">
-        <v>0.1762422335004816</v>
+        <v>0.1572998090862405</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -12173,10 +12196,10 @@
         <v>670</v>
       </c>
       <c r="L20">
-        <v>7.4816578037471135</v>
+        <v>11.884376191048085</v>
       </c>
       <c r="M20">
-        <v>0.12851292841627501</v>
+        <v>0.2732889293422246</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -12241,10 +12264,10 @@
         <v>671</v>
       </c>
       <c r="L21">
-        <v>1.6691823226567941</v>
+        <v>12.246676572623375</v>
       </c>
       <c r="M21">
-        <v>0.15723508939914779</v>
+        <v>0.23735119883611849</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -12309,10 +12332,10 @@
         <v>672</v>
       </c>
       <c r="L22">
-        <v>3.7614311754340659</v>
+        <v>11.221871479411517</v>
       </c>
       <c r="M22">
-        <v>0.21587774284891351</v>
+        <v>0.34329463129026588</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -12445,10 +12468,10 @@
         <v>674</v>
       </c>
       <c r="L24">
-        <v>11.221871479411517</v>
+        <v>49.086666974214374</v>
       </c>
       <c r="M24">
-        <v>0.34329463129026588</v>
+        <v>0.308797255699787</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -12513,10 +12536,10 @@
         <v>675</v>
       </c>
       <c r="L25">
-        <v>18.008891115565412</v>
+        <v>1.6757541426674882</v>
       </c>
       <c r="M25">
-        <v>0.2474712287536284</v>
+        <v>0.1650429037380152</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -12581,10 +12604,10 @@
         <v>676</v>
       </c>
       <c r="L26">
-        <v>24.891089921419841</v>
+        <v>0.39959553615654331</v>
       </c>
       <c r="M26">
-        <v>0.3055932594772704</v>
+        <v>0.1072096692643303</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -12649,10 +12672,10 @@
         <v>677</v>
       </c>
       <c r="L27">
-        <v>30.317738700900584</v>
+        <v>1.7832075556426605</v>
       </c>
       <c r="M27">
-        <v>0.30507645183795778</v>
+        <v>0.17291513693338831</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -12717,10 +12740,10 @@
         <v>678</v>
       </c>
       <c r="L28">
-        <v>0.34625959029864795</v>
+        <v>0.35051099632091098</v>
       </c>
       <c r="M28">
-        <v>0.16712424320989541</v>
+        <v>9.6656114851391806E-2</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -12785,10 +12808,10 @@
         <v>679</v>
       </c>
       <c r="L29">
-        <v>0.65440271382024695</v>
+        <v>5.5005105319204732</v>
       </c>
       <c r="M29">
-        <v>0.1270319550249287</v>
+        <v>0.1032555480201208</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -12853,10 +12876,10 @@
         <v>680</v>
       </c>
       <c r="L30">
-        <v>2.2677057834637031</v>
+        <v>0.34625959029864795</v>
       </c>
       <c r="M30">
-        <v>0.13270702416333019</v>
+        <v>0.16712424320989541</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -12921,10 +12944,10 @@
         <v>681</v>
       </c>
       <c r="L31">
-        <v>2.4836923620575391</v>
+        <v>0.65440271382024695</v>
       </c>
       <c r="M31">
-        <v>0.16311252525788919</v>
+        <v>0.1270319550249287</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -12989,10 +13012,10 @@
         <v>682</v>
       </c>
       <c r="L32">
-        <v>4.0763322608214585</v>
+        <v>0.5190595734350465</v>
       </c>
       <c r="M32">
-        <v>0.17777395285655839</v>
+        <v>0.10857562776850541</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -13057,10 +13080,10 @@
         <v>683</v>
       </c>
       <c r="L33">
-        <v>2.5731779960501728</v>
+        <v>0.29505146981926272</v>
       </c>
       <c r="M33">
-        <v>0.19326289879692229</v>
+        <v>0.1235068952905013</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -13125,10 +13148,10 @@
         <v>684</v>
       </c>
       <c r="L34">
-        <v>4.0509443596880574</v>
+        <v>0.28737649325389003</v>
       </c>
       <c r="M34">
-        <v>0.18682452602484509</v>
+        <v>0.1208623014671094</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -13193,10 +13216,10 @@
         <v>685</v>
       </c>
       <c r="L35">
-        <v>2.4544193550494788</v>
+        <v>0.85621181691755843</v>
       </c>
       <c r="M35">
-        <v>0.16013241630924799</v>
+        <v>9.0668099088234103E-2</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -13261,10 +13284,10 @@
         <v>686</v>
       </c>
       <c r="L36">
-        <v>0.35051099632091098</v>
+        <v>2.2628760328229185</v>
       </c>
       <c r="M36">
-        <v>9.6656114851391806E-2</v>
+        <v>0.1238708109113873</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -13329,10 +13352,10 @@
         <v>687</v>
       </c>
       <c r="L37">
-        <v>5.5005105319204732</v>
+        <v>0.43370118574988076</v>
       </c>
       <c r="M37">
-        <v>0.1032555480201208</v>
+        <v>0.10138851292069349</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -13397,10 +13420,10 @@
         <v>688</v>
       </c>
       <c r="L38">
-        <v>1.6757541426674882</v>
+        <v>2.5150267058852811</v>
       </c>
       <c r="M38">
-        <v>0.1650429037380152</v>
+        <v>8.7681833650751606E-2</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -13465,10 +13488,10 @@
         <v>689</v>
       </c>
       <c r="L39">
-        <v>0.39959553615654331</v>
+        <v>2.2677057834637031</v>
       </c>
       <c r="M39">
-        <v>0.1072096692643303</v>
+        <v>0.13270702416333019</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -13533,10 +13556,10 @@
         <v>690</v>
       </c>
       <c r="L40">
-        <v>1.7832075556426605</v>
+        <v>4.0509443596880574</v>
       </c>
       <c r="M40">
-        <v>0.17291513693338831</v>
+        <v>0.18682452602484509</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -13601,10 +13624,10 @@
         <v>691</v>
       </c>
       <c r="L41">
-        <v>33.414563514376454</v>
+        <v>2.4836923620575391</v>
       </c>
       <c r="M41">
-        <v>0.30971299533872781</v>
+        <v>0.16311252525788919</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -13669,10 +13692,10 @@
         <v>692</v>
       </c>
       <c r="L42">
-        <v>2.8320779450600302</v>
+        <v>2.885493974180005</v>
       </c>
       <c r="M42">
-        <v>0.19139890752231881</v>
+        <v>0.14764341619346269</v>
       </c>
     </row>
     <row r="43" spans="2:26">
@@ -13704,10 +13727,10 @@
         <v>693</v>
       </c>
       <c r="L43">
-        <v>24.434551684764973</v>
+        <v>4.0763322608214585</v>
       </c>
       <c r="M43">
-        <v>0.19028064145394111</v>
+        <v>0.17777395285655839</v>
       </c>
     </row>
     <row r="44" spans="2:26">
@@ -13739,10 +13762,10 @@
         <v>694</v>
       </c>
       <c r="L44">
-        <v>18.904558868579112</v>
+        <v>23.427729543154012</v>
       </c>
       <c r="M44">
-        <v>0.29452200235220533</v>
+        <v>0.25027188308965431</v>
       </c>
     </row>
     <row r="45" spans="2:26">
@@ -13774,10 +13797,10 @@
         <v>695</v>
       </c>
       <c r="L45">
-        <v>15.478330347836801</v>
+        <v>1.4999429400795936</v>
       </c>
       <c r="M45">
-        <v>0.222177819888773</v>
+        <v>0.21843142318229231</v>
       </c>
     </row>
     <row r="46" spans="2:26">
@@ -13809,10 +13832,10 @@
         <v>696</v>
       </c>
       <c r="L46">
-        <v>1.4999429400795936</v>
+        <v>55.863958629218203</v>
       </c>
       <c r="M46">
-        <v>0.21843142318229231</v>
+        <v>0.34785235138275827</v>
       </c>
     </row>
     <row r="47" spans="2:26">
@@ -13844,10 +13867,10 @@
         <v>697</v>
       </c>
       <c r="L47">
-        <v>55.863958629218203</v>
+        <v>17.068804920122925</v>
       </c>
       <c r="M47">
-        <v>0.34785235138275827</v>
+        <v>0.1097075246412334</v>
       </c>
     </row>
     <row r="48" spans="2:26">
@@ -13879,10 +13902,10 @@
         <v>698</v>
       </c>
       <c r="L48">
-        <v>17.068804920122925</v>
+        <v>13.001084297219549</v>
       </c>
       <c r="M48">
-        <v>0.1097075246412334</v>
+        <v>0.16897605417432451</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -13949,10 +13972,10 @@
         <v>700</v>
       </c>
       <c r="L50">
-        <v>13.001084297219549</v>
+        <v>17.749707845203876</v>
       </c>
       <c r="M50">
-        <v>0.16897605417432451</v>
+        <v>0.2004256815418958</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -13984,10 +14007,10 @@
         <v>701</v>
       </c>
       <c r="L51">
-        <v>0.80973624203950822</v>
+        <v>2.3372365278937242</v>
       </c>
       <c r="M51">
-        <v>0.1402179322845909</v>
+        <v>0.1157811350779776</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -14019,10 +14042,10 @@
         <v>702</v>
       </c>
       <c r="L52">
-        <v>3.2067222321080848</v>
+        <v>4.2648673086521249</v>
       </c>
       <c r="M52">
-        <v>0.1065607310314662</v>
+        <v>0.1018524220358768</v>
       </c>
     </row>
     <row r="53" spans="2:13">
@@ -14054,10 +14077,10 @@
         <v>703</v>
       </c>
       <c r="L53">
-        <v>0.66271354737797783</v>
+        <v>2.8571480649629004</v>
       </c>
       <c r="M53">
-        <v>0.16309819780041621</v>
+        <v>0.28915876947611158</v>
       </c>
     </row>
     <row r="54" spans="2:13">
@@ -14089,10 +14112,10 @@
         <v>704</v>
       </c>
       <c r="L54">
-        <v>1.8183767824138508</v>
+        <v>9.5169217846211289</v>
       </c>
       <c r="M54">
-        <v>0.21095850339443861</v>
+        <v>0.1716922275766741</v>
       </c>
     </row>
     <row r="55" spans="2:13">
@@ -14124,10 +14147,10 @@
         <v>705</v>
       </c>
       <c r="L55">
-        <v>0.24904319237866104</v>
+        <v>33.414563514376454</v>
       </c>
       <c r="M55">
-        <v>0.25748619553898999</v>
+        <v>0.30971299533872781</v>
       </c>
     </row>
     <row r="56" spans="2:13">
@@ -14159,10 +14182,10 @@
         <v>706</v>
       </c>
       <c r="L56">
-        <v>8.2047875916663029E-2</v>
+        <v>18.904558868579112</v>
       </c>
       <c r="M56">
-        <v>0.13592110504470081</v>
+        <v>0.29452200235220533</v>
       </c>
     </row>
     <row r="57" spans="2:13">
@@ -14194,10 +14217,10 @@
         <v>707</v>
       </c>
       <c r="L57">
-        <v>14.176079891703212</v>
+        <v>15.478330347836801</v>
       </c>
       <c r="M57">
-        <v>0.1221312740068858</v>
+        <v>0.222177819888773</v>
       </c>
     </row>
     <row r="58" spans="2:13">
@@ -14229,10 +14252,10 @@
         <v>708</v>
       </c>
       <c r="L58">
-        <v>2.3372365278937242</v>
+        <v>14.176079891703212</v>
       </c>
       <c r="M58">
-        <v>0.1157811350779776</v>
+        <v>0.1221312740068858</v>
       </c>
     </row>
     <row r="59" spans="2:13">
@@ -14264,10 +14287,10 @@
         <v>709</v>
       </c>
       <c r="L59">
-        <v>4.2648673086521249</v>
+        <v>0.80973624203950822</v>
       </c>
       <c r="M59">
-        <v>0.1018524220358768</v>
+        <v>0.1402179322845909</v>
       </c>
     </row>
     <row r="60" spans="2:13">
@@ -14299,10 +14322,10 @@
         <v>710</v>
       </c>
       <c r="L60">
-        <v>2.8571480649629004</v>
+        <v>3.2067222321080848</v>
       </c>
       <c r="M60">
-        <v>0.28915876947611158</v>
+        <v>0.1065607310314662</v>
       </c>
     </row>
     <row r="61" spans="2:13">
@@ -14334,10 +14357,10 @@
         <v>711</v>
       </c>
       <c r="L61">
-        <v>11.861012832193515</v>
+        <v>0.66271354737797783</v>
       </c>
       <c r="M61">
-        <v>0.1087933355996048</v>
+        <v>0.16309819780041621</v>
       </c>
     </row>
     <row r="62" spans="2:13">
@@ -14369,10 +14392,10 @@
         <v>712</v>
       </c>
       <c r="L62">
-        <v>0.74143826937354373</v>
+        <v>1.8183767824138508</v>
       </c>
       <c r="M62">
-        <v>8.8201244876213003E-2</v>
+        <v>0.21095850339443861</v>
       </c>
     </row>
     <row r="63" spans="2:13">
@@ -14404,10 +14427,10 @@
         <v>713</v>
       </c>
       <c r="L63">
-        <v>5.5201095579611916</v>
+        <v>0.24904319237866104</v>
       </c>
       <c r="M63">
-        <v>0.1283226559519017</v>
+        <v>0.25748619553898999</v>
       </c>
     </row>
     <row r="64" spans="2:13">
@@ -14439,10 +14462,10 @@
         <v>714</v>
       </c>
       <c r="L64">
-        <v>6.8285247240880329</v>
+        <v>8.2047875916663029E-2</v>
       </c>
       <c r="M64">
-        <v>9.8264036008851294E-2</v>
+        <v>0.13592110504470081</v>
       </c>
     </row>
     <row r="65" spans="2:13">
@@ -14474,10 +14497,10 @@
         <v>715</v>
       </c>
       <c r="L65">
-        <v>14.065249575687433</v>
+        <v>11.861012832193515</v>
       </c>
       <c r="M65">
-        <v>0.1320696072360909</v>
+        <v>0.1087933355996048</v>
       </c>
     </row>
     <row r="66" spans="2:13">
@@ -14509,10 +14532,10 @@
         <v>716</v>
       </c>
       <c r="L66">
-        <v>9.3799037679336319</v>
+        <v>0.74143826937354373</v>
       </c>
       <c r="M66">
-        <v>0.12698739870760559</v>
+        <v>8.8201244876213003E-2</v>
       </c>
     </row>
     <row r="67" spans="2:13">
@@ -14544,10 +14567,10 @@
         <v>717</v>
       </c>
       <c r="L67">
-        <v>42.785830383290261</v>
+        <v>5.5201095579611916</v>
       </c>
       <c r="M67">
-        <v>0.27336739424382489</v>
+        <v>0.1283226559519017</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -14579,10 +14602,10 @@
         <v>718</v>
       </c>
       <c r="L68">
-        <v>11.412035826311723</v>
+        <v>6.8285247240880329</v>
       </c>
       <c r="M68">
-        <v>0.11866286907907619</v>
+        <v>9.8264036008851294E-2</v>
       </c>
     </row>
     <row r="69" spans="2:13">
@@ -14614,10 +14637,10 @@
         <v>719</v>
       </c>
       <c r="L69">
-        <v>16.249041763152853</v>
+        <v>14.065249575687433</v>
       </c>
       <c r="M69">
-        <v>0.12558896879944331</v>
+        <v>0.1320696072360909</v>
       </c>
     </row>
     <row r="70" spans="2:13">
@@ -14649,10 +14672,10 @@
         <v>720</v>
       </c>
       <c r="L70">
-        <v>18.319832830101969</v>
+        <v>9.3799037679336319</v>
       </c>
       <c r="M70">
-        <v>0.1300705694164489</v>
+        <v>0.12698739870760559</v>
       </c>
     </row>
     <row r="71" spans="2:13">
@@ -14684,10 +14707,10 @@
         <v>721</v>
       </c>
       <c r="L71">
-        <v>23.427729543154012</v>
+        <v>42.785830383290261</v>
       </c>
       <c r="M71">
-        <v>0.25027188308965431</v>
+        <v>0.27336739424382489</v>
       </c>
     </row>
     <row r="72" spans="2:13">
@@ -14719,10 +14742,10 @@
         <v>722</v>
       </c>
       <c r="L72">
-        <v>6.7510585544323067</v>
+        <v>7.8693705940085819</v>
       </c>
       <c r="M72">
-        <v>0.15514978062049739</v>
+        <v>0.1194525598481516</v>
       </c>
     </row>
     <row r="73" spans="2:13">
@@ -14754,10 +14777,10 @@
         <v>723</v>
       </c>
       <c r="L73">
-        <v>3.5275797249830152</v>
+        <v>19.787589902082505</v>
       </c>
       <c r="M73">
-        <v>9.5677447841151203E-2</v>
+        <v>0.1240437231884286</v>
       </c>
     </row>
     <row r="74" spans="2:13">
@@ -14789,10 +14812,10 @@
         <v>724</v>
       </c>
       <c r="L74">
-        <v>0.89663971235601181</v>
+        <v>18.319832830101969</v>
       </c>
       <c r="M74">
-        <v>9.3606642611398602E-2</v>
+        <v>0.1300705694164489</v>
       </c>
     </row>
     <row r="75" spans="2:13">
@@ -14824,10 +14847,10 @@
         <v>725</v>
       </c>
       <c r="L75">
-        <v>5.9305458091691294</v>
+        <v>6.7551756478058005</v>
       </c>
       <c r="M75">
-        <v>9.6567218538318997E-2</v>
+        <v>0.15510592681409949</v>
       </c>
     </row>
     <row r="76" spans="2:13">
@@ -14894,10 +14917,10 @@
         <v>727</v>
       </c>
       <c r="L77">
-        <v>0.5190595734350465</v>
+        <v>3.5275797249830152</v>
       </c>
       <c r="M77">
-        <v>0.10857562776850541</v>
+        <v>9.5677447841151203E-2</v>
       </c>
     </row>
     <row r="78" spans="2:13">
@@ -14929,10 +14952,10 @@
         <v>728</v>
       </c>
       <c r="L78">
-        <v>0.29505146981926272</v>
+        <v>0.89663971235601181</v>
       </c>
       <c r="M78">
-        <v>0.1235068952905013</v>
+        <v>9.3606642611398602E-2</v>
       </c>
     </row>
     <row r="79" spans="2:13">
@@ -14964,10 +14987,10 @@
         <v>729</v>
       </c>
       <c r="L79">
-        <v>0.28737649325389003</v>
+        <v>5.9305458091691294</v>
       </c>
       <c r="M79">
-        <v>0.1208623014671094</v>
+        <v>9.6567218538318997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -14976,7 +14999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E41CBF-FE6F-469B-B741-BA37888D72D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29438B4A-9C9D-4CEC-BE97-0A2B34DBFF1B}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
